--- a/research/traditional_assets/database/data/luxembourg/luxembourg_air_transport.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_air_transport.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="nyse_caap" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -587,32 +589,38 @@
           <t>Air Transport</t>
         </is>
       </c>
+      <c r="D2">
+        <v>-0.0429</v>
+      </c>
+      <c r="E2">
+        <v>0.181</v>
+      </c>
       <c r="G2">
-        <v>0.08323699421965318</v>
+        <v>0.1050040355125101</v>
       </c>
       <c r="H2">
-        <v>0.08323699421965318</v>
+        <v>0.1050040355125101</v>
       </c>
       <c r="I2">
-        <v>-0.1225433526011561</v>
+        <v>0.183454398708636</v>
       </c>
       <c r="J2">
-        <v>-0.1225433526011561</v>
+        <v>0.1441677970731346</v>
       </c>
       <c r="K2">
-        <v>-133.9</v>
+        <v>137.4</v>
       </c>
       <c r="L2">
-        <v>-0.221139554087531</v>
+        <v>0.1108958837772397</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0007338795867474171</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.007496360989810771</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,79 +629,82 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.03</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>218.1</v>
+        <v>348.4</v>
       </c>
       <c r="V2">
-        <v>0.2353512463580447</v>
+        <v>0.2482365514784467</v>
       </c>
       <c r="W2">
-        <v>-0.250749063670412</v>
+        <v>0.2992812023524287</v>
       </c>
       <c r="X2">
-        <v>0.09301022849101932</v>
+        <v>0.1206333947577118</v>
       </c>
       <c r="Y2">
-        <v>-0.3437592921614313</v>
+        <v>0.1786478075947168</v>
       </c>
       <c r="Z2">
-        <v>0.3900839437454501</v>
+        <v>0.7982990238716535</v>
       </c>
       <c r="AA2">
-        <v>-0.04780219426244822</v>
+        <v>0.11508901167721</v>
       </c>
       <c r="AB2">
-        <v>0.05068556814749355</v>
+        <v>0.07666504869206206</v>
       </c>
       <c r="AC2">
-        <v>-0.09848776240994177</v>
+        <v>0.03842396298514793</v>
       </c>
       <c r="AD2">
-        <v>1320.8</v>
+        <v>1499.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1320.8</v>
+        <v>1499.2</v>
       </c>
       <c r="AG2">
-        <v>1102.7</v>
+        <v>1150.8</v>
       </c>
       <c r="AH2">
-        <v>0.5876751946607341</v>
+        <v>0.5164846522203467</v>
       </c>
       <c r="AI2">
-        <v>0.6407296012418744</v>
+        <v>0.6375776133367356</v>
       </c>
       <c r="AJ2">
-        <v>0.5433625702177983</v>
+        <v>0.4505343929843793</v>
       </c>
       <c r="AK2">
-        <v>0.5982205826506808</v>
+        <v>0.5745381927109336</v>
       </c>
       <c r="AL2">
-        <v>125.6</v>
+        <v>168.5</v>
       </c>
       <c r="AM2">
-        <v>107.4</v>
+        <v>133</v>
       </c>
       <c r="AN2">
-        <v>14.54625550660793</v>
+        <v>3.813787840244212</v>
       </c>
       <c r="AO2">
-        <v>-0.5907643312101911</v>
+        <v>1.348961424332344</v>
       </c>
       <c r="AP2">
-        <v>12.1442731277533</v>
+        <v>2.927499364029509</v>
       </c>
       <c r="AQ2">
-        <v>-0.6908752327746742</v>
+        <v>1.709022556390978</v>
       </c>
     </row>
     <row r="3">
@@ -712,32 +723,38 @@
           <t>Air Transport</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.0429</v>
+      </c>
+      <c r="E3">
+        <v>0.181</v>
+      </c>
       <c r="G3">
-        <v>0.08323699421965318</v>
+        <v>0.1050040355125101</v>
       </c>
       <c r="H3">
-        <v>0.08323699421965318</v>
+        <v>0.1050040355125101</v>
       </c>
       <c r="I3">
-        <v>-0.1225433526011561</v>
+        <v>0.183454398708636</v>
       </c>
       <c r="J3">
-        <v>-0.1225433526011561</v>
+        <v>0.1441677970731346</v>
       </c>
       <c r="K3">
-        <v>-133.9</v>
+        <v>137.4</v>
       </c>
       <c r="L3">
-        <v>-0.221139554087531</v>
+        <v>0.1108958837772397</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1.03</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0007338795867474171</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.007496360989810771</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -746,79 +763,8794 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.03</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>218.1</v>
+        <v>348.4</v>
       </c>
       <c r="V3">
-        <v>0.2353512463580447</v>
+        <v>0.2482365514784467</v>
       </c>
       <c r="W3">
-        <v>-0.250749063670412</v>
+        <v>0.2992812023524287</v>
       </c>
       <c r="X3">
-        <v>0.09301022849101932</v>
+        <v>0.1206333947577118</v>
       </c>
       <c r="Y3">
-        <v>-0.3437592921614313</v>
+        <v>0.1786478075947168</v>
       </c>
       <c r="Z3">
-        <v>0.3900839437454501</v>
+        <v>0.7982990238716535</v>
       </c>
       <c r="AA3">
-        <v>-0.04780219426244822</v>
+        <v>0.11508901167721</v>
       </c>
       <c r="AB3">
-        <v>0.05068556814749355</v>
+        <v>0.07666504869206206</v>
       </c>
       <c r="AC3">
-        <v>-0.09848776240994177</v>
+        <v>0.03842396298514793</v>
       </c>
       <c r="AD3">
-        <v>1320.8</v>
+        <v>1499.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1320.8</v>
+        <v>1499.2</v>
       </c>
       <c r="AG3">
-        <v>1102.7</v>
+        <v>1150.8</v>
       </c>
       <c r="AH3">
-        <v>0.5876751946607341</v>
+        <v>0.5164846522203467</v>
       </c>
       <c r="AI3">
-        <v>0.6407296012418744</v>
+        <v>0.6375776133367356</v>
       </c>
       <c r="AJ3">
-        <v>0.5433625702177983</v>
+        <v>0.4505343929843793</v>
       </c>
       <c r="AK3">
-        <v>0.5982205826506808</v>
+        <v>0.5745381927109336</v>
       </c>
       <c r="AL3">
-        <v>125.6</v>
+        <v>168.5</v>
       </c>
       <c r="AM3">
-        <v>107.4</v>
+        <v>133</v>
       </c>
       <c r="AN3">
-        <v>14.54625550660793</v>
+        <v>3.813787840244212</v>
       </c>
       <c r="AO3">
-        <v>-0.5907643312101911</v>
+        <v>1.348961424332344</v>
       </c>
       <c r="AP3">
-        <v>12.1442731277533</v>
+        <v>2.927499364029509</v>
       </c>
       <c r="AQ3">
-        <v>-0.6908752327746742</v>
+        <v>1.709022556390978</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Corporación América Airports S.A. (NYSE:CAAP)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NYSE:CAAP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air Transport</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.516484652220347</v>
+      </c>
+      <c r="F2">
+        <v>0.31</v>
+      </c>
+      <c r="G2">
+        <v>1403.5</v>
+      </c>
+      <c r="H2">
+        <v>1824.9127899113</v>
+      </c>
+      <c r="I2">
+        <v>2554.3</v>
+      </c>
+      <c r="J2">
+        <v>2376.3497899113</v>
+      </c>
+      <c r="K2">
+        <v>1499.2</v>
+      </c>
+      <c r="L2">
+        <v>899.837</v>
+      </c>
+      <c r="M2">
+        <v>0.0766650486920621</v>
+      </c>
+      <c r="N2">
+        <v>0.0814763385525213</v>
+      </c>
+      <c r="O2">
+        <v>0.03550338</v>
+      </c>
+      <c r="P2">
+        <v>0.041283</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.120633394757712</v>
+      </c>
+      <c r="T2">
+        <v>0.0995342152935091</v>
+      </c>
+      <c r="U2">
+        <v>1.38366705537045</v>
+      </c>
+      <c r="V2">
+        <v>1.02691490539057</v>
+      </c>
+      <c r="W2">
+        <v>4.592750990154076</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>1403.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.0591424031092525</v>
+      </c>
+      <c r="AC2">
+        <v>0.0473</v>
+      </c>
+      <c r="AD2">
+        <v>0.2494</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>393.1</v>
+      </c>
+      <c r="AH2">
+        <v>165.8</v>
+      </c>
+      <c r="AI2">
+        <v>174.31</v>
+      </c>
+      <c r="AJ2">
+        <v>1499.2</v>
+      </c>
+      <c r="AK2">
+        <v>1499.2</v>
+      </c>
+      <c r="AL2">
+        <v>168.5</v>
+      </c>
+      <c r="AM2">
+        <v>1499.2</v>
+      </c>
+      <c r="AN2">
+        <v>348.4</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08421806048051153</v>
+      </c>
+      <c r="C2">
+        <v>2634.011438219081</v>
+      </c>
+      <c r="D2">
+        <v>2285.611438219081</v>
+      </c>
+      <c r="E2">
+        <v>-1499.2</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>348.4</v>
+      </c>
+      <c r="H2">
+        <v>1403.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>393.1</v>
+      </c>
+      <c r="K2">
+        <v>165.8</v>
+      </c>
+      <c r="L2">
+        <v>227.3</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>227.3</v>
+      </c>
+      <c r="O2">
+        <v>56.68861999999999</v>
+      </c>
+      <c r="P2">
+        <v>170.61138</v>
+      </c>
+      <c r="Q2">
+        <v>336.41138</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08421806048051153</v>
+      </c>
+      <c r="T2">
+        <v>0.767944116112626</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.2494</v>
+      </c>
+      <c r="W2">
+        <v>0.03430242000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08405981203767314</v>
+      </c>
+      <c r="C3">
+        <v>2610.032877846149</v>
+      </c>
+      <c r="D3">
+        <v>2290.659877846149</v>
+      </c>
+      <c r="E3">
+        <v>-1470.173</v>
+      </c>
+      <c r="F3">
+        <v>29.027</v>
+      </c>
+      <c r="G3">
+        <v>348.4</v>
+      </c>
+      <c r="H3">
+        <v>1403.5</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>393.1</v>
+      </c>
+      <c r="K3">
+        <v>165.8</v>
+      </c>
+      <c r="L3">
+        <v>227.3</v>
+      </c>
+      <c r="M3">
+        <v>1.3265339</v>
+      </c>
+      <c r="N3">
+        <v>225.9734661</v>
+      </c>
+      <c r="O3">
+        <v>56.35778244533999</v>
+      </c>
+      <c r="P3">
+        <v>169.61568365466</v>
+      </c>
+      <c r="Q3">
+        <v>335.41568365466</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08456241195724559</v>
+      </c>
+      <c r="T3">
+        <v>0.773766528774789</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.2494</v>
+      </c>
+      <c r="W3">
+        <v>0.03430242000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>171.3488060878052</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08390156359483474</v>
+      </c>
+      <c r="C4">
+        <v>2586.076668745849</v>
+      </c>
+      <c r="D4">
+        <v>2295.730668745849</v>
+      </c>
+      <c r="E4">
+        <v>-1441.146</v>
+      </c>
+      <c r="F4">
+        <v>58.05399999999999</v>
+      </c>
+      <c r="G4">
+        <v>348.4</v>
+      </c>
+      <c r="H4">
+        <v>1403.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>393.1</v>
+      </c>
+      <c r="K4">
+        <v>165.8</v>
+      </c>
+      <c r="L4">
+        <v>227.3</v>
+      </c>
+      <c r="M4">
+        <v>2.6530678</v>
+      </c>
+      <c r="N4">
+        <v>224.6469322</v>
+      </c>
+      <c r="O4">
+        <v>56.02694489067999</v>
+      </c>
+      <c r="P4">
+        <v>168.61998730932</v>
+      </c>
+      <c r="Q4">
+        <v>334.41998730932</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08491379101513749</v>
+      </c>
+      <c r="T4">
+        <v>0.7797077661851595</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.2494</v>
+      </c>
+      <c r="W4">
+        <v>0.03430242000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>85.67440304390261</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08374331515199634</v>
+      </c>
+      <c r="C5">
+        <v>2562.142959683282</v>
+      </c>
+      <c r="D5">
+        <v>2300.823959683282</v>
+      </c>
+      <c r="E5">
+        <v>-1412.119</v>
+      </c>
+      <c r="F5">
+        <v>87.08099999999999</v>
+      </c>
+      <c r="G5">
+        <v>348.4</v>
+      </c>
+      <c r="H5">
+        <v>1403.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>393.1</v>
+      </c>
+      <c r="K5">
+        <v>165.8</v>
+      </c>
+      <c r="L5">
+        <v>227.3</v>
+      </c>
+      <c r="M5">
+        <v>3.9796017</v>
+      </c>
+      <c r="N5">
+        <v>223.3203983</v>
+      </c>
+      <c r="O5">
+        <v>55.69610733602</v>
+      </c>
+      <c r="P5">
+        <v>167.62429096398</v>
+      </c>
+      <c r="Q5">
+        <v>333.4242909639801</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08527241500205809</v>
+      </c>
+      <c r="T5">
+        <v>0.7857715033359498</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.2494</v>
+      </c>
+      <c r="W5">
+        <v>0.03430242000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>57.11626869593508</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08358506670915795</v>
+      </c>
+      <c r="C6">
+        <v>2538.231900746679</v>
+      </c>
+      <c r="D6">
+        <v>2305.939900746679</v>
+      </c>
+      <c r="E6">
+        <v>-1383.092</v>
+      </c>
+      <c r="F6">
+        <v>116.108</v>
+      </c>
+      <c r="G6">
+        <v>348.4</v>
+      </c>
+      <c r="H6">
+        <v>1403.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>393.1</v>
+      </c>
+      <c r="K6">
+        <v>165.8</v>
+      </c>
+      <c r="L6">
+        <v>227.3</v>
+      </c>
+      <c r="M6">
+        <v>5.3061356</v>
+      </c>
+      <c r="N6">
+        <v>221.9938644</v>
+      </c>
+      <c r="O6">
+        <v>55.36526978135999</v>
+      </c>
+      <c r="P6">
+        <v>166.62859461864</v>
+      </c>
+      <c r="Q6">
+        <v>332.42859461864</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08563851032203953</v>
+      </c>
+      <c r="T6">
+        <v>0.7919615683440484</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.2494</v>
+      </c>
+      <c r="W6">
+        <v>0.03430242000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>42.83720152195131</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08342681826631956</v>
+      </c>
+      <c r="C7">
+        <v>2514.343643362148</v>
+      </c>
+      <c r="D7">
+        <v>2311.078643362148</v>
+      </c>
+      <c r="E7">
+        <v>-1354.065</v>
+      </c>
+      <c r="F7">
+        <v>145.135</v>
+      </c>
+      <c r="G7">
+        <v>348.4</v>
+      </c>
+      <c r="H7">
+        <v>1403.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>393.1</v>
+      </c>
+      <c r="K7">
+        <v>165.8</v>
+      </c>
+      <c r="L7">
+        <v>227.3</v>
+      </c>
+      <c r="M7">
+        <v>6.6326695</v>
+      </c>
+      <c r="N7">
+        <v>220.6673305</v>
+      </c>
+      <c r="O7">
+        <v>55.0344322267</v>
+      </c>
+      <c r="P7">
+        <v>165.6328982733</v>
+      </c>
+      <c r="Q7">
+        <v>331.4328982733</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08601231291191533</v>
+      </c>
+      <c r="T7">
+        <v>0.7982819505102122</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.2494</v>
+      </c>
+      <c r="W7">
+        <v>0.03430242000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>34.26976121756105</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08326856982348114</v>
+      </c>
+      <c r="C8">
+        <v>2490.478340308613</v>
+      </c>
+      <c r="D8">
+        <v>2316.240340308612</v>
+      </c>
+      <c r="E8">
+        <v>-1325.038</v>
+      </c>
+      <c r="F8">
+        <v>174.162</v>
+      </c>
+      <c r="G8">
+        <v>348.4</v>
+      </c>
+      <c r="H8">
+        <v>1403.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>393.1</v>
+      </c>
+      <c r="K8">
+        <v>165.8</v>
+      </c>
+      <c r="L8">
+        <v>227.3</v>
+      </c>
+      <c r="M8">
+        <v>7.9592034</v>
+      </c>
+      <c r="N8">
+        <v>219.3407966</v>
+      </c>
+      <c r="O8">
+        <v>54.70359467203999</v>
+      </c>
+      <c r="P8">
+        <v>164.63720192796</v>
+      </c>
+      <c r="Q8">
+        <v>330.43720192796</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08639406874838421</v>
+      </c>
+      <c r="T8">
+        <v>0.8047368088926773</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.2494</v>
+      </c>
+      <c r="W8">
+        <v>0.03430242000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>28.55813434796754</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08311032138064277</v>
+      </c>
+      <c r="C9">
+        <v>2466.636145732949</v>
+      </c>
+      <c r="D9">
+        <v>2321.425145732948</v>
+      </c>
+      <c r="E9">
+        <v>-1296.011</v>
+      </c>
+      <c r="F9">
+        <v>203.189</v>
+      </c>
+      <c r="G9">
+        <v>348.4</v>
+      </c>
+      <c r="H9">
+        <v>1403.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>393.1</v>
+      </c>
+      <c r="K9">
+        <v>165.8</v>
+      </c>
+      <c r="L9">
+        <v>227.3</v>
+      </c>
+      <c r="M9">
+        <v>9.285737300000001</v>
+      </c>
+      <c r="N9">
+        <v>218.0142627</v>
+      </c>
+      <c r="O9">
+        <v>54.37275711738</v>
+      </c>
+      <c r="P9">
+        <v>163.64150558262</v>
+      </c>
+      <c r="Q9">
+        <v>329.44150558262</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08678403438778792</v>
+      </c>
+      <c r="T9">
+        <v>0.8113304814339053</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.2494</v>
+      </c>
+      <c r="W9">
+        <v>0.03430242000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>24.47840086968646</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08295207293780438</v>
+      </c>
+      <c r="C10">
+        <v>2442.817215165339</v>
+      </c>
+      <c r="D10">
+        <v>2326.633215165339</v>
+      </c>
+      <c r="E10">
+        <v>-1266.984</v>
+      </c>
+      <c r="F10">
+        <v>232.216</v>
+      </c>
+      <c r="G10">
+        <v>348.4</v>
+      </c>
+      <c r="H10">
+        <v>1403.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>393.1</v>
+      </c>
+      <c r="K10">
+        <v>165.8</v>
+      </c>
+      <c r="L10">
+        <v>227.3</v>
+      </c>
+      <c r="M10">
+        <v>10.6122712</v>
+      </c>
+      <c r="N10">
+        <v>216.6877288</v>
+      </c>
+      <c r="O10">
+        <v>54.04191956271999</v>
+      </c>
+      <c r="P10">
+        <v>162.64580923728</v>
+      </c>
+      <c r="Q10">
+        <v>328.4458092372801</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08718247754109171</v>
+      </c>
+      <c r="T10">
+        <v>0.818067494682551</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.2494</v>
+      </c>
+      <c r="W10">
+        <v>0.03430242000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>21.41860076097565</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08279382449496599</v>
+      </c>
+      <c r="C11">
+        <v>2419.021705534818</v>
+      </c>
+      <c r="D11">
+        <v>2331.864705534817</v>
+      </c>
+      <c r="E11">
+        <v>-1237.957</v>
+      </c>
+      <c r="F11">
+        <v>261.243</v>
+      </c>
+      <c r="G11">
+        <v>348.4</v>
+      </c>
+      <c r="H11">
+        <v>1403.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>393.1</v>
+      </c>
+      <c r="K11">
+        <v>165.8</v>
+      </c>
+      <c r="L11">
+        <v>227.3</v>
+      </c>
+      <c r="M11">
+        <v>11.9388051</v>
+      </c>
+      <c r="N11">
+        <v>215.3611949</v>
+      </c>
+      <c r="O11">
+        <v>53.71108200806</v>
+      </c>
+      <c r="P11">
+        <v>161.65011289194</v>
+      </c>
+      <c r="Q11">
+        <v>327.45011289194</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08758967768677581</v>
+      </c>
+      <c r="T11">
+        <v>0.8249525741564419</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.2494</v>
+      </c>
+      <c r="W11">
+        <v>0.03430242000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>19.03875623197836</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.0826355760521276</v>
+      </c>
+      <c r="C12">
+        <v>2395.249775185032</v>
+      </c>
+      <c r="D12">
+        <v>2337.119775185032</v>
+      </c>
+      <c r="E12">
+        <v>-1208.93</v>
+      </c>
+      <c r="F12">
+        <v>290.27</v>
+      </c>
+      <c r="G12">
+        <v>348.4</v>
+      </c>
+      <c r="H12">
+        <v>1403.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>393.1</v>
+      </c>
+      <c r="K12">
+        <v>165.8</v>
+      </c>
+      <c r="L12">
+        <v>227.3</v>
+      </c>
+      <c r="M12">
+        <v>13.265339</v>
+      </c>
+      <c r="N12">
+        <v>214.034661</v>
+      </c>
+      <c r="O12">
+        <v>53.38024445339999</v>
+      </c>
+      <c r="P12">
+        <v>160.6544165466</v>
+      </c>
+      <c r="Q12">
+        <v>326.4544165466</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08800592672458621</v>
+      </c>
+      <c r="T12">
+        <v>0.831990655396419</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.2494</v>
+      </c>
+      <c r="W12">
+        <v>0.03430242000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>17.13488060878052</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08247732760928918</v>
+      </c>
+      <c r="C13">
+        <v>2371.501583890226</v>
+      </c>
+      <c r="D13">
+        <v>2342.398583890226</v>
+      </c>
+      <c r="E13">
+        <v>-1179.903</v>
+      </c>
+      <c r="F13">
+        <v>319.297</v>
+      </c>
+      <c r="G13">
+        <v>348.4</v>
+      </c>
+      <c r="H13">
+        <v>1403.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>393.1</v>
+      </c>
+      <c r="K13">
+        <v>165.8</v>
+      </c>
+      <c r="L13">
+        <v>227.3</v>
+      </c>
+      <c r="M13">
+        <v>14.5918729</v>
+      </c>
+      <c r="N13">
+        <v>212.7081271</v>
+      </c>
+      <c r="O13">
+        <v>53.04940689874</v>
+      </c>
+      <c r="P13">
+        <v>159.65872020126</v>
+      </c>
+      <c r="Q13">
+        <v>325.45872020126</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08843152967335863</v>
+      </c>
+      <c r="T13">
+        <v>0.8391868957653845</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.2494</v>
+      </c>
+      <c r="W13">
+        <v>0.03430242000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>15.57716418980048</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08231907916645077</v>
+      </c>
+      <c r="C14">
+        <v>2347.777292871421</v>
+      </c>
+      <c r="D14">
+        <v>2347.701292871421</v>
+      </c>
+      <c r="E14">
+        <v>-1150.876</v>
+      </c>
+      <c r="F14">
+        <v>348.324</v>
+      </c>
+      <c r="G14">
+        <v>348.4</v>
+      </c>
+      <c r="H14">
+        <v>1403.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>393.1</v>
+      </c>
+      <c r="K14">
+        <v>165.8</v>
+      </c>
+      <c r="L14">
+        <v>227.3</v>
+      </c>
+      <c r="M14">
+        <v>15.9184068</v>
+      </c>
+      <c r="N14">
+        <v>211.3815932</v>
+      </c>
+      <c r="O14">
+        <v>52.71856934407999</v>
+      </c>
+      <c r="P14">
+        <v>158.66302385592</v>
+      </c>
+      <c r="Q14">
+        <v>324.46302385592</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08886680541642134</v>
+      </c>
+      <c r="T14">
+        <v>0.8465466870518265</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.2494</v>
+      </c>
+      <c r="W14">
+        <v>0.03430242000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>14.27906717398377</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.0821608307236124</v>
+      </c>
+      <c r="C15">
+        <v>2324.07706481284</v>
+      </c>
+      <c r="D15">
+        <v>2353.02806481284</v>
+      </c>
+      <c r="E15">
+        <v>-1121.849</v>
+      </c>
+      <c r="F15">
+        <v>377.351</v>
+      </c>
+      <c r="G15">
+        <v>348.4</v>
+      </c>
+      <c r="H15">
+        <v>1403.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>393.1</v>
+      </c>
+      <c r="K15">
+        <v>165.8</v>
+      </c>
+      <c r="L15">
+        <v>227.3</v>
+      </c>
+      <c r="M15">
+        <v>17.2449407</v>
+      </c>
+      <c r="N15">
+        <v>210.0550593</v>
+      </c>
+      <c r="O15">
+        <v>52.38773178941999</v>
+      </c>
+      <c r="P15">
+        <v>157.66732751058</v>
+      </c>
+      <c r="Q15">
+        <v>323.46732751058</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08931208749840505</v>
+      </c>
+      <c r="T15">
+        <v>0.8540756689425546</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.2494</v>
+      </c>
+      <c r="W15">
+        <v>0.03430242000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>13.18067739136963</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.082170716680774</v>
+      </c>
+      <c r="C16">
+        <v>2294.716587650972</v>
+      </c>
+      <c r="D16">
+        <v>2352.694587650972</v>
+      </c>
+      <c r="E16">
+        <v>-1092.822</v>
+      </c>
+      <c r="F16">
+        <v>406.378</v>
+      </c>
+      <c r="G16">
+        <v>348.4</v>
+      </c>
+      <c r="H16">
+        <v>1403.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>393.1</v>
+      </c>
+      <c r="K16">
+        <v>165.8</v>
+      </c>
+      <c r="L16">
+        <v>227.3</v>
+      </c>
+      <c r="M16">
+        <v>19.2216794</v>
+      </c>
+      <c r="N16">
+        <v>208.0783206</v>
+      </c>
+      <c r="O16">
+        <v>51.89473315763999</v>
+      </c>
+      <c r="P16">
+        <v>156.18358744236</v>
+      </c>
+      <c r="Q16">
+        <v>321.98358744236</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08976772497764418</v>
+      </c>
+      <c r="T16">
+        <v>0.8617797434353927</v>
+      </c>
+      <c r="U16">
+        <v>0.0473</v>
+      </c>
+      <c r="V16">
+        <v>0.2494</v>
+      </c>
+      <c r="W16">
+        <v>0.03550338</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>11.82518942647644</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08202447783793559</v>
+      </c>
+      <c r="C17">
+        <v>2270.632239150055</v>
+      </c>
+      <c r="D17">
+        <v>2357.637239150055</v>
+      </c>
+      <c r="E17">
+        <v>-1063.795</v>
+      </c>
+      <c r="F17">
+        <v>435.405</v>
+      </c>
+      <c r="G17">
+        <v>348.4</v>
+      </c>
+      <c r="H17">
+        <v>1403.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>393.1</v>
+      </c>
+      <c r="K17">
+        <v>165.8</v>
+      </c>
+      <c r="L17">
+        <v>227.3</v>
+      </c>
+      <c r="M17">
+        <v>20.5946565</v>
+      </c>
+      <c r="N17">
+        <v>206.7053435</v>
+      </c>
+      <c r="O17">
+        <v>51.55231266889999</v>
+      </c>
+      <c r="P17">
+        <v>155.1530308311</v>
+      </c>
+      <c r="Q17">
+        <v>320.9530308311</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09023408333874777</v>
+      </c>
+      <c r="T17">
+        <v>0.8696650902692384</v>
+      </c>
+      <c r="U17">
+        <v>0.0473</v>
+      </c>
+      <c r="V17">
+        <v>0.2494</v>
+      </c>
+      <c r="W17">
+        <v>0.03550338</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>11.03684346471135</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08187823899509719</v>
+      </c>
+      <c r="C18">
+        <v>2246.568701880058</v>
+      </c>
+      <c r="D18">
+        <v>2362.600701880057</v>
+      </c>
+      <c r="E18">
+        <v>-1034.768</v>
+      </c>
+      <c r="F18">
+        <v>464.432</v>
+      </c>
+      <c r="G18">
+        <v>348.4</v>
+      </c>
+      <c r="H18">
+        <v>1403.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>393.1</v>
+      </c>
+      <c r="K18">
+        <v>165.8</v>
+      </c>
+      <c r="L18">
+        <v>227.3</v>
+      </c>
+      <c r="M18">
+        <v>21.9676336</v>
+      </c>
+      <c r="N18">
+        <v>205.3323664</v>
+      </c>
+      <c r="O18">
+        <v>51.20989218016</v>
+      </c>
+      <c r="P18">
+        <v>154.12247421984</v>
+      </c>
+      <c r="Q18">
+        <v>319.92247421984</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09071154547035382</v>
+      </c>
+      <c r="T18">
+        <v>0.8777381834562712</v>
+      </c>
+      <c r="U18">
+        <v>0.0473</v>
+      </c>
+      <c r="V18">
+        <v>0.2494</v>
+      </c>
+      <c r="W18">
+        <v>0.03550338</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>10.34704074816689</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.0822168877522588</v>
+      </c>
+      <c r="C19">
+        <v>2206.079376907998</v>
+      </c>
+      <c r="D19">
+        <v>2351.138376907998</v>
+      </c>
+      <c r="E19">
+        <v>-1005.741</v>
+      </c>
+      <c r="F19">
+        <v>493.459</v>
+      </c>
+      <c r="G19">
+        <v>348.4</v>
+      </c>
+      <c r="H19">
+        <v>1403.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>393.1</v>
+      </c>
+      <c r="K19">
+        <v>165.8</v>
+      </c>
+      <c r="L19">
+        <v>227.3</v>
+      </c>
+      <c r="M19">
+        <v>25.2157549</v>
+      </c>
+      <c r="N19">
+        <v>202.0842451</v>
+      </c>
+      <c r="O19">
+        <v>50.39981072793999</v>
+      </c>
+      <c r="P19">
+        <v>151.68443437206</v>
+      </c>
+      <c r="Q19">
+        <v>317.48443437206</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09120051271356483</v>
+      </c>
+      <c r="T19">
+        <v>0.8860058090092565</v>
+      </c>
+      <c r="U19">
+        <v>0.0511</v>
+      </c>
+      <c r="V19">
+        <v>0.2494</v>
+      </c>
+      <c r="W19">
+        <v>0.03835566</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>9.014205638554966</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.08209917170942041</v>
+      </c>
+      <c r="C20">
+        <v>2181.024107418008</v>
+      </c>
+      <c r="D20">
+        <v>2355.110107418007</v>
+      </c>
+      <c r="E20">
+        <v>-976.7140000000001</v>
+      </c>
+      <c r="F20">
+        <v>522.486</v>
+      </c>
+      <c r="G20">
+        <v>348.4</v>
+      </c>
+      <c r="H20">
+        <v>1403.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>393.1</v>
+      </c>
+      <c r="K20">
+        <v>165.8</v>
+      </c>
+      <c r="L20">
+        <v>227.3</v>
+      </c>
+      <c r="M20">
+        <v>26.6990346</v>
+      </c>
+      <c r="N20">
+        <v>200.6009654</v>
+      </c>
+      <c r="O20">
+        <v>50.02988077075999</v>
+      </c>
+      <c r="P20">
+        <v>150.57108462924</v>
+      </c>
+      <c r="Q20">
+        <v>316.37108462924</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09170140598709806</v>
+      </c>
+      <c r="T20">
+        <v>0.8944750839659732</v>
+      </c>
+      <c r="U20">
+        <v>0.0511</v>
+      </c>
+      <c r="V20">
+        <v>0.2494</v>
+      </c>
+      <c r="W20">
+        <v>0.03835566</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>8.513416436413024</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.08198145566658202</v>
+      </c>
+      <c r="C21">
+        <v>2155.982279362411</v>
+      </c>
+      <c r="D21">
+        <v>2359.095279362411</v>
+      </c>
+      <c r="E21">
+        <v>-947.6870000000001</v>
+      </c>
+      <c r="F21">
+        <v>551.5129999999999</v>
+      </c>
+      <c r="G21">
+        <v>348.4</v>
+      </c>
+      <c r="H21">
+        <v>1403.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>393.1</v>
+      </c>
+      <c r="K21">
+        <v>165.8</v>
+      </c>
+      <c r="L21">
+        <v>227.3</v>
+      </c>
+      <c r="M21">
+        <v>28.18231429999999</v>
+      </c>
+      <c r="N21">
+        <v>199.1176857</v>
+      </c>
+      <c r="O21">
+        <v>49.65995081358</v>
+      </c>
+      <c r="P21">
+        <v>149.45773488642</v>
+      </c>
+      <c r="Q21">
+        <v>315.2577348864201</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09221466699578026</v>
+      </c>
+      <c r="T21">
+        <v>0.9031534768228556</v>
+      </c>
+      <c r="U21">
+        <v>0.0511</v>
+      </c>
+      <c r="V21">
+        <v>0.2494</v>
+      </c>
+      <c r="W21">
+        <v>0.03835566</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>8.065341887128127</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.08214896762374362</v>
+      </c>
+      <c r="C22">
+        <v>2121.288360571252</v>
+      </c>
+      <c r="D22">
+        <v>2353.428360571252</v>
+      </c>
+      <c r="E22">
+        <v>-918.6600000000001</v>
+      </c>
+      <c r="F22">
+        <v>580.54</v>
+      </c>
+      <c r="G22">
+        <v>348.4</v>
+      </c>
+      <c r="H22">
+        <v>1403.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>393.1</v>
+      </c>
+      <c r="K22">
+        <v>165.8</v>
+      </c>
+      <c r="L22">
+        <v>227.3</v>
+      </c>
+      <c r="M22">
+        <v>30.76862</v>
+      </c>
+      <c r="N22">
+        <v>196.53138</v>
+      </c>
+      <c r="O22">
+        <v>49.014926172</v>
+      </c>
+      <c r="P22">
+        <v>147.516453828</v>
+      </c>
+      <c r="Q22">
+        <v>313.316453828</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09274075952967953</v>
+      </c>
+      <c r="T22">
+        <v>0.9120488295011604</v>
+      </c>
+      <c r="U22">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V22">
+        <v>0.2494</v>
+      </c>
+      <c r="W22">
+        <v>0.03978180000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>7.387396639823301</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08204551298090523</v>
+      </c>
+      <c r="C23">
+        <v>2095.758004781339</v>
+      </c>
+      <c r="D23">
+        <v>2356.925004781338</v>
+      </c>
+      <c r="E23">
+        <v>-889.6330000000002</v>
+      </c>
+      <c r="F23">
+        <v>609.5669999999999</v>
+      </c>
+      <c r="G23">
+        <v>348.4</v>
+      </c>
+      <c r="H23">
+        <v>1403.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>393.1</v>
+      </c>
+      <c r="K23">
+        <v>165.8</v>
+      </c>
+      <c r="L23">
+        <v>227.3</v>
+      </c>
+      <c r="M23">
+        <v>32.30705099999999</v>
+      </c>
+      <c r="N23">
+        <v>194.992949</v>
+      </c>
+      <c r="O23">
+        <v>48.6312414806</v>
+      </c>
+      <c r="P23">
+        <v>146.3617075194</v>
+      </c>
+      <c r="Q23">
+        <v>312.1617075194</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09328017086190535</v>
+      </c>
+      <c r="T23">
+        <v>0.9211693809814473</v>
+      </c>
+      <c r="U23">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V23">
+        <v>0.2494</v>
+      </c>
+      <c r="W23">
+        <v>0.03978180000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>7.035615847450764</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08194205833806684</v>
+      </c>
+      <c r="C24">
+        <v>2070.238054843346</v>
+      </c>
+      <c r="D24">
+        <v>2360.432054843346</v>
+      </c>
+      <c r="E24">
+        <v>-860.6060000000001</v>
+      </c>
+      <c r="F24">
+        <v>638.5939999999999</v>
+      </c>
+      <c r="G24">
+        <v>348.4</v>
+      </c>
+      <c r="H24">
+        <v>1403.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>393.1</v>
+      </c>
+      <c r="K24">
+        <v>165.8</v>
+      </c>
+      <c r="L24">
+        <v>227.3</v>
+      </c>
+      <c r="M24">
+        <v>33.845482</v>
+      </c>
+      <c r="N24">
+        <v>193.454518</v>
+      </c>
+      <c r="O24">
+        <v>48.24755678919999</v>
+      </c>
+      <c r="P24">
+        <v>145.2069612108</v>
+      </c>
+      <c r="Q24">
+        <v>311.0069612108</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09383341325393184</v>
+      </c>
+      <c r="T24">
+        <v>0.9305237927561006</v>
+      </c>
+      <c r="U24">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V24">
+        <v>0.2494</v>
+      </c>
+      <c r="W24">
+        <v>0.03978180000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>6.715815127112092</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08183860369522844</v>
+      </c>
+      <c r="C25">
+        <v>2044.728557277498</v>
+      </c>
+      <c r="D25">
+        <v>2363.949557277498</v>
+      </c>
+      <c r="E25">
+        <v>-831.5790000000001</v>
+      </c>
+      <c r="F25">
+        <v>667.621</v>
+      </c>
+      <c r="G25">
+        <v>348.4</v>
+      </c>
+      <c r="H25">
+        <v>1403.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>393.1</v>
+      </c>
+      <c r="K25">
+        <v>165.8</v>
+      </c>
+      <c r="L25">
+        <v>227.3</v>
+      </c>
+      <c r="M25">
+        <v>35.383913</v>
+      </c>
+      <c r="N25">
+        <v>191.916087</v>
+      </c>
+      <c r="O25">
+        <v>47.86387209779999</v>
+      </c>
+      <c r="P25">
+        <v>144.0522149022</v>
+      </c>
+      <c r="Q25">
+        <v>309.8522149022</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09440102557821875</v>
+      </c>
+      <c r="T25">
+        <v>0.9401211762651606</v>
+      </c>
+      <c r="U25">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V25">
+        <v>0.2494</v>
+      </c>
+      <c r="W25">
+        <v>0.03978180000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>6.42382316506374</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08209543705239004</v>
+      </c>
+      <c r="C26">
+        <v>2006.988334093966</v>
+      </c>
+      <c r="D26">
+        <v>2355.236334093966</v>
+      </c>
+      <c r="E26">
+        <v>-802.5520000000001</v>
+      </c>
+      <c r="F26">
+        <v>696.6479999999999</v>
+      </c>
+      <c r="G26">
+        <v>348.4</v>
+      </c>
+      <c r="H26">
+        <v>1403.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>393.1</v>
+      </c>
+      <c r="K26">
+        <v>165.8</v>
+      </c>
+      <c r="L26">
+        <v>227.3</v>
+      </c>
+      <c r="M26">
+        <v>38.31563999999999</v>
+      </c>
+      <c r="N26">
+        <v>188.98436</v>
+      </c>
+      <c r="O26">
+        <v>47.13269938399999</v>
+      </c>
+      <c r="P26">
+        <v>141.851660616</v>
+      </c>
+      <c r="Q26">
+        <v>307.651660616</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09498357506893426</v>
+      </c>
+      <c r="T26">
+        <v>0.9499711224981431</v>
+      </c>
+      <c r="U26">
+        <v>0.055</v>
+      </c>
+      <c r="V26">
+        <v>0.2494</v>
+      </c>
+      <c r="W26">
+        <v>0.041283</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>5.932303362282348</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08200699440955164</v>
+      </c>
+      <c r="C27">
+        <v>1980.954542745876</v>
+      </c>
+      <c r="D27">
+        <v>2358.229542745876</v>
+      </c>
+      <c r="E27">
+        <v>-773.5250000000001</v>
+      </c>
+      <c r="F27">
+        <v>725.675</v>
+      </c>
+      <c r="G27">
+        <v>348.4</v>
+      </c>
+      <c r="H27">
+        <v>1403.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>393.1</v>
+      </c>
+      <c r="K27">
+        <v>165.8</v>
+      </c>
+      <c r="L27">
+        <v>227.3</v>
+      </c>
+      <c r="M27">
+        <v>39.912125</v>
+      </c>
+      <c r="N27">
+        <v>187.387875</v>
+      </c>
+      <c r="O27">
+        <v>46.734536025</v>
+      </c>
+      <c r="P27">
+        <v>140.653338975</v>
+      </c>
+      <c r="Q27">
+        <v>306.453338975</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09558165921273552</v>
+      </c>
+      <c r="T27">
+        <v>0.960083733964005</v>
+      </c>
+      <c r="U27">
+        <v>0.055</v>
+      </c>
+      <c r="V27">
+        <v>0.2494</v>
+      </c>
+      <c r="W27">
+        <v>0.041283</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>5.695011227791055</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08191855176671325</v>
+      </c>
+      <c r="C28">
+        <v>1954.92836906106</v>
+      </c>
+      <c r="D28">
+        <v>2361.23036906106</v>
+      </c>
+      <c r="E28">
+        <v>-744.498</v>
+      </c>
+      <c r="F28">
+        <v>754.702</v>
+      </c>
+      <c r="G28">
+        <v>348.4</v>
+      </c>
+      <c r="H28">
+        <v>1403.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>393.1</v>
+      </c>
+      <c r="K28">
+        <v>165.8</v>
+      </c>
+      <c r="L28">
+        <v>227.3</v>
+      </c>
+      <c r="M28">
+        <v>41.50861</v>
+      </c>
+      <c r="N28">
+        <v>185.79139</v>
+      </c>
+      <c r="O28">
+        <v>46.336372666</v>
+      </c>
+      <c r="P28">
+        <v>139.455017334</v>
+      </c>
+      <c r="Q28">
+        <v>305.2550173340001</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09619590779285574</v>
+      </c>
+      <c r="T28">
+        <v>0.9704696592532688</v>
+      </c>
+      <c r="U28">
+        <v>0.055</v>
+      </c>
+      <c r="V28">
+        <v>0.2494</v>
+      </c>
+      <c r="W28">
+        <v>0.041283</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>5.475972334414475</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08183010912387484</v>
+      </c>
+      <c r="C29">
+        <v>1928.909842156798</v>
+      </c>
+      <c r="D29">
+        <v>2364.238842156798</v>
+      </c>
+      <c r="E29">
+        <v>-715.471</v>
+      </c>
+      <c r="F29">
+        <v>783.729</v>
+      </c>
+      <c r="G29">
+        <v>348.4</v>
+      </c>
+      <c r="H29">
+        <v>1403.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>393.1</v>
+      </c>
+      <c r="K29">
+        <v>165.8</v>
+      </c>
+      <c r="L29">
+        <v>227.3</v>
+      </c>
+      <c r="M29">
+        <v>43.10509500000001</v>
+      </c>
+      <c r="N29">
+        <v>184.194905</v>
+      </c>
+      <c r="O29">
+        <v>45.93820930699999</v>
+      </c>
+      <c r="P29">
+        <v>138.256695693</v>
+      </c>
+      <c r="Q29">
+        <v>304.0566956930001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09682698510119842</v>
+      </c>
+      <c r="T29">
+        <v>0.9811401304408685</v>
+      </c>
+      <c r="U29">
+        <v>0.055</v>
+      </c>
+      <c r="V29">
+        <v>0.2494</v>
+      </c>
+      <c r="W29">
+        <v>0.041283</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>5.273158544250975</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08174166648103645</v>
+      </c>
+      <c r="C30">
+        <v>1902.898991298952</v>
+      </c>
+      <c r="D30">
+        <v>2367.254991298952</v>
+      </c>
+      <c r="E30">
+        <v>-686.4440000000001</v>
+      </c>
+      <c r="F30">
+        <v>812.756</v>
+      </c>
+      <c r="G30">
+        <v>348.4</v>
+      </c>
+      <c r="H30">
+        <v>1403.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>393.1</v>
+      </c>
+      <c r="K30">
+        <v>165.8</v>
+      </c>
+      <c r="L30">
+        <v>227.3</v>
+      </c>
+      <c r="M30">
+        <v>44.70158</v>
+      </c>
+      <c r="N30">
+        <v>182.59842</v>
+      </c>
+      <c r="O30">
+        <v>45.54004594799999</v>
+      </c>
+      <c r="P30">
+        <v>137.058374052</v>
+      </c>
+      <c r="Q30">
+        <v>302.858374052</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09747559233477286</v>
+      </c>
+      <c r="T30">
+        <v>0.9921070036059016</v>
+      </c>
+      <c r="U30">
+        <v>0.055</v>
+      </c>
+      <c r="V30">
+        <v>0.2494</v>
+      </c>
+      <c r="W30">
+        <v>0.041283</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>5.08483145338487</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08165322383819806</v>
+      </c>
+      <c r="C31">
+        <v>1876.89584590292</v>
+      </c>
+      <c r="D31">
+        <v>2370.27884590292</v>
+      </c>
+      <c r="E31">
+        <v>-657.4170000000001</v>
+      </c>
+      <c r="F31">
+        <v>841.7829999999999</v>
+      </c>
+      <c r="G31">
+        <v>348.4</v>
+      </c>
+      <c r="H31">
+        <v>1403.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>393.1</v>
+      </c>
+      <c r="K31">
+        <v>165.8</v>
+      </c>
+      <c r="L31">
+        <v>227.3</v>
+      </c>
+      <c r="M31">
+        <v>46.29806499999999</v>
+      </c>
+      <c r="N31">
+        <v>181.001935</v>
+      </c>
+      <c r="O31">
+        <v>45.14188258899999</v>
+      </c>
+      <c r="P31">
+        <v>135.860052411</v>
+      </c>
+      <c r="Q31">
+        <v>301.660052411</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09814247019464517</v>
+      </c>
+      <c r="T31">
+        <v>1.003382802775584</v>
+      </c>
+      <c r="U31">
+        <v>0.055</v>
+      </c>
+      <c r="V31">
+        <v>0.2494</v>
+      </c>
+      <c r="W31">
+        <v>0.041283</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>4.909492437750909</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.08156478119535966</v>
+      </c>
+      <c r="C32">
+        <v>1850.900435534589</v>
+      </c>
+      <c r="D32">
+        <v>2373.310435534589</v>
+      </c>
+      <c r="E32">
+        <v>-628.3900000000001</v>
+      </c>
+      <c r="F32">
+        <v>870.8099999999999</v>
+      </c>
+      <c r="G32">
+        <v>348.4</v>
+      </c>
+      <c r="H32">
+        <v>1403.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>393.1</v>
+      </c>
+      <c r="K32">
+        <v>165.8</v>
+      </c>
+      <c r="L32">
+        <v>227.3</v>
+      </c>
+      <c r="M32">
+        <v>47.89455</v>
+      </c>
+      <c r="N32">
+        <v>179.40545</v>
+      </c>
+      <c r="O32">
+        <v>44.74371923</v>
+      </c>
+      <c r="P32">
+        <v>134.66173077</v>
+      </c>
+      <c r="Q32">
+        <v>300.46173077</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.09882840170765667</v>
+      </c>
+      <c r="T32">
+        <v>1.014980767635828</v>
+      </c>
+      <c r="U32">
+        <v>0.055</v>
+      </c>
+      <c r="V32">
+        <v>0.2494</v>
+      </c>
+      <c r="W32">
+        <v>0.041283</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>4.745842689825879</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.08147633855252126</v>
+      </c>
+      <c r="C33">
+        <v>1824.912789911297</v>
+      </c>
+      <c r="D33">
+        <v>2376.349789911297</v>
+      </c>
+      <c r="E33">
+        <v>-599.3630000000001</v>
+      </c>
+      <c r="F33">
+        <v>899.837</v>
+      </c>
+      <c r="G33">
+        <v>348.4</v>
+      </c>
+      <c r="H33">
+        <v>1403.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>393.1</v>
+      </c>
+      <c r="K33">
+        <v>165.8</v>
+      </c>
+      <c r="L33">
+        <v>227.3</v>
+      </c>
+      <c r="M33">
+        <v>49.491035</v>
+      </c>
+      <c r="N33">
+        <v>177.808965</v>
+      </c>
+      <c r="O33">
+        <v>44.34555587099999</v>
+      </c>
+      <c r="P33">
+        <v>133.463409129</v>
+      </c>
+      <c r="Q33">
+        <v>299.263409129</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.09953421529350909</v>
+      </c>
+      <c r="T33">
+        <v>1.026914905390572</v>
+      </c>
+      <c r="U33">
+        <v>0.055</v>
+      </c>
+      <c r="V33">
+        <v>0.2494</v>
+      </c>
+      <c r="W33">
+        <v>0.041283</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>4.592750990154076</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.08230062550968287</v>
+      </c>
+      <c r="C34">
+        <v>1767.857215502891</v>
+      </c>
+      <c r="D34">
+        <v>2348.32121550289</v>
+      </c>
+      <c r="E34">
+        <v>-570.3360000000001</v>
+      </c>
+      <c r="F34">
+        <v>928.8639999999999</v>
+      </c>
+      <c r="G34">
+        <v>348.4</v>
+      </c>
+      <c r="H34">
+        <v>1403.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>393.1</v>
+      </c>
+      <c r="K34">
+        <v>165.8</v>
+      </c>
+      <c r="L34">
+        <v>227.3</v>
+      </c>
+      <c r="M34">
+        <v>54.6172032</v>
+      </c>
+      <c r="N34">
+        <v>172.6827968</v>
+      </c>
+      <c r="O34">
+        <v>43.06708952192</v>
+      </c>
+      <c r="P34">
+        <v>129.61570727808</v>
+      </c>
+      <c r="Q34">
+        <v>295.41570727808</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1002607881024748</v>
+      </c>
+      <c r="T34">
+        <v>1.039200047196926</v>
+      </c>
+      <c r="U34">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V34">
+        <v>0.2494</v>
+      </c>
+      <c r="W34">
+        <v>0.04413528000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>4.161692409764402</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.08224070566684448</v>
+      </c>
+      <c r="C35">
+        <v>1740.845391140987</v>
+      </c>
+      <c r="D35">
+        <v>2350.336391140987</v>
+      </c>
+      <c r="E35">
+        <v>-541.3090000000001</v>
+      </c>
+      <c r="F35">
+        <v>957.891</v>
+      </c>
+      <c r="G35">
+        <v>348.4</v>
+      </c>
+      <c r="H35">
+        <v>1403.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>393.1</v>
+      </c>
+      <c r="K35">
+        <v>165.8</v>
+      </c>
+      <c r="L35">
+        <v>227.3</v>
+      </c>
+      <c r="M35">
+        <v>56.3239908</v>
+      </c>
+      <c r="N35">
+        <v>170.9760092</v>
+      </c>
+      <c r="O35">
+        <v>42.64141669448</v>
+      </c>
+      <c r="P35">
+        <v>128.33459250552</v>
+      </c>
+      <c r="Q35">
+        <v>294.13459250552</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1010090496520067</v>
+      </c>
+      <c r="T35">
+        <v>1.051851909654216</v>
+      </c>
+      <c r="U35">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V35">
+        <v>0.2494</v>
+      </c>
+      <c r="W35">
+        <v>0.04413528000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>4.035580518559421</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08325264262400608</v>
+      </c>
+      <c r="C36">
+        <v>1678.243125959566</v>
+      </c>
+      <c r="D36">
+        <v>2316.761125959566</v>
+      </c>
+      <c r="E36">
+        <v>-512.282</v>
+      </c>
+      <c r="F36">
+        <v>986.918</v>
+      </c>
+      <c r="G36">
+        <v>348.4</v>
+      </c>
+      <c r="H36">
+        <v>1403.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>393.1</v>
+      </c>
+      <c r="K36">
+        <v>165.8</v>
+      </c>
+      <c r="L36">
+        <v>227.3</v>
+      </c>
+      <c r="M36">
+        <v>62.175834</v>
+      </c>
+      <c r="N36">
+        <v>165.124166</v>
+      </c>
+      <c r="O36">
+        <v>41.18196700039999</v>
+      </c>
+      <c r="P36">
+        <v>123.9421989996</v>
+      </c>
+      <c r="Q36">
+        <v>289.7421989996</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1017799857939486</v>
+      </c>
+      <c r="T36">
+        <v>1.064887161882939</v>
+      </c>
+      <c r="U36">
+        <v>0.063</v>
+      </c>
+      <c r="V36">
+        <v>0.2494</v>
+      </c>
+      <c r="W36">
+        <v>0.0472878</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>3.65576117563618</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.08322424798116768</v>
+      </c>
+      <c r="C37">
+        <v>1650.145151716834</v>
+      </c>
+      <c r="D37">
+        <v>2317.690151716834</v>
+      </c>
+      <c r="E37">
+        <v>-483.255</v>
+      </c>
+      <c r="F37">
+        <v>1015.945</v>
+      </c>
+      <c r="G37">
+        <v>348.4</v>
+      </c>
+      <c r="H37">
+        <v>1403.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>393.1</v>
+      </c>
+      <c r="K37">
+        <v>165.8</v>
+      </c>
+      <c r="L37">
+        <v>227.3</v>
+      </c>
+      <c r="M37">
+        <v>64.004535</v>
+      </c>
+      <c r="N37">
+        <v>163.295465</v>
+      </c>
+      <c r="O37">
+        <v>40.725888971</v>
+      </c>
+      <c r="P37">
+        <v>122.569576029</v>
+      </c>
+      <c r="Q37">
+        <v>288.369576029</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1025746430479503</v>
+      </c>
+      <c r="T37">
+        <v>1.078323498795623</v>
+      </c>
+      <c r="U37">
+        <v>0.063</v>
+      </c>
+      <c r="V37">
+        <v>0.2494</v>
+      </c>
+      <c r="W37">
+        <v>0.0472878</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>3.551310856332289</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.0851143869383293</v>
+      </c>
+      <c r="C38">
+        <v>1560.859636303907</v>
+      </c>
+      <c r="D38">
+        <v>2257.431636303907</v>
+      </c>
+      <c r="E38">
+        <v>-454.2280000000001</v>
+      </c>
+      <c r="F38">
+        <v>1044.972</v>
+      </c>
+      <c r="G38">
+        <v>348.4</v>
+      </c>
+      <c r="H38">
+        <v>1403.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>393.1</v>
+      </c>
+      <c r="K38">
+        <v>165.8</v>
+      </c>
+      <c r="L38">
+        <v>227.3</v>
+      </c>
+      <c r="M38">
+        <v>73.25253719999999</v>
+      </c>
+      <c r="N38">
+        <v>154.0474628</v>
+      </c>
+      <c r="O38">
+        <v>38.41943722231999</v>
+      </c>
+      <c r="P38">
+        <v>115.62802557768</v>
+      </c>
+      <c r="Q38">
+        <v>281.42802557768</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1033941333411395</v>
+      </c>
+      <c r="T38">
+        <v>1.092179721236828</v>
+      </c>
+      <c r="U38">
+        <v>0.0701</v>
+      </c>
+      <c r="V38">
+        <v>0.2494</v>
+      </c>
+      <c r="W38">
+        <v>0.05261706</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>3.102964193300325</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.0851392848954909</v>
+      </c>
+      <c r="C39">
+        <v>1531.059779685199</v>
+      </c>
+      <c r="D39">
+        <v>2256.658779685199</v>
+      </c>
+      <c r="E39">
+        <v>-425.201</v>
+      </c>
+      <c r="F39">
+        <v>1073.999</v>
+      </c>
+      <c r="G39">
+        <v>348.4</v>
+      </c>
+      <c r="H39">
+        <v>1403.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>393.1</v>
+      </c>
+      <c r="K39">
+        <v>165.8</v>
+      </c>
+      <c r="L39">
+        <v>227.3</v>
+      </c>
+      <c r="M39">
+        <v>75.2873299</v>
+      </c>
+      <c r="N39">
+        <v>152.0126701</v>
+      </c>
+      <c r="O39">
+        <v>37.91195992293999</v>
+      </c>
+      <c r="P39">
+        <v>114.10071017706</v>
+      </c>
+      <c r="Q39">
+        <v>279.90071017706</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1042396391991919</v>
+      </c>
+      <c r="T39">
+        <v>1.106475823755532</v>
+      </c>
+      <c r="U39">
+        <v>0.0701</v>
+      </c>
+      <c r="V39">
+        <v>0.2494</v>
+      </c>
+      <c r="W39">
+        <v>0.05261706</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>3.019100296184099</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.09123953925265249</v>
+      </c>
+      <c r="C40">
+        <v>1327.38926561767</v>
+      </c>
+      <c r="D40">
+        <v>2082.01526561767</v>
+      </c>
+      <c r="E40">
+        <v>-396.1740000000002</v>
+      </c>
+      <c r="F40">
+        <v>1103.026</v>
+      </c>
+      <c r="G40">
+        <v>348.4</v>
+      </c>
+      <c r="H40">
+        <v>1403.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>393.1</v>
+      </c>
+      <c r="K40">
+        <v>165.8</v>
+      </c>
+      <c r="L40">
+        <v>227.3</v>
+      </c>
+      <c r="M40">
+        <v>100.8165764</v>
+      </c>
+      <c r="N40">
+        <v>126.4834236</v>
+      </c>
+      <c r="O40">
+        <v>31.54496584584</v>
+      </c>
+      <c r="P40">
+        <v>94.93845775416003</v>
+      </c>
+      <c r="Q40">
+        <v>260.73845775416</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1051124194397621</v>
+      </c>
+      <c r="T40">
+        <v>1.121233090871613</v>
+      </c>
+      <c r="U40">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V40">
+        <v>0.2494</v>
+      </c>
+      <c r="W40">
+        <v>0.06860484000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>2.254589553786911</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.0914243150098141</v>
+      </c>
+      <c r="C41">
+        <v>1293.493143512479</v>
+      </c>
+      <c r="D41">
+        <v>2077.146143512479</v>
+      </c>
+      <c r="E41">
+        <v>-367.1470000000002</v>
+      </c>
+      <c r="F41">
+        <v>1132.053</v>
+      </c>
+      <c r="G41">
+        <v>348.4</v>
+      </c>
+      <c r="H41">
+        <v>1403.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>393.1</v>
+      </c>
+      <c r="K41">
+        <v>165.8</v>
+      </c>
+      <c r="L41">
+        <v>227.3</v>
+      </c>
+      <c r="M41">
+        <v>103.4696442</v>
+      </c>
+      <c r="N41">
+        <v>123.8303558</v>
+      </c>
+      <c r="O41">
+        <v>30.88329073652</v>
+      </c>
+      <c r="P41">
+        <v>92.94706506348001</v>
+      </c>
+      <c r="Q41">
+        <v>258.74706506348</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1060138154259248</v>
+      </c>
+      <c r="T41">
+        <v>1.136474202811173</v>
+      </c>
+      <c r="U41">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V41">
+        <v>0.2494</v>
+      </c>
+      <c r="W41">
+        <v>0.06860484000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>2.196779565228272</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.09160909076697571</v>
+      </c>
+      <c r="C42">
+        <v>1259.619742694788</v>
+      </c>
+      <c r="D42">
+        <v>2072.299742694788</v>
+      </c>
+      <c r="E42">
+        <v>-338.1200000000001</v>
+      </c>
+      <c r="F42">
+        <v>1161.08</v>
+      </c>
+      <c r="G42">
+        <v>348.4</v>
+      </c>
+      <c r="H42">
+        <v>1403.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>393.1</v>
+      </c>
+      <c r="K42">
+        <v>165.8</v>
+      </c>
+      <c r="L42">
+        <v>227.3</v>
+      </c>
+      <c r="M42">
+        <v>106.122712</v>
+      </c>
+      <c r="N42">
+        <v>121.177288</v>
+      </c>
+      <c r="O42">
+        <v>30.22161562719999</v>
+      </c>
+      <c r="P42">
+        <v>90.95567237280001</v>
+      </c>
+      <c r="Q42">
+        <v>256.7556723728</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1069452579449595</v>
+      </c>
+      <c r="T42">
+        <v>1.152223351815384</v>
+      </c>
+      <c r="U42">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V42">
+        <v>0.2494</v>
+      </c>
+      <c r="W42">
+        <v>0.06860484000000001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>2.141860076097565</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.09179386652413732</v>
+      </c>
+      <c r="C43">
+        <v>1225.768904494767</v>
+      </c>
+      <c r="D43">
+        <v>2067.475904494767</v>
+      </c>
+      <c r="E43">
+        <v>-309.0930000000001</v>
+      </c>
+      <c r="F43">
+        <v>1190.107</v>
+      </c>
+      <c r="G43">
+        <v>348.4</v>
+      </c>
+      <c r="H43">
+        <v>1403.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>393.1</v>
+      </c>
+      <c r="K43">
+        <v>165.8</v>
+      </c>
+      <c r="L43">
+        <v>227.3</v>
+      </c>
+      <c r="M43">
+        <v>108.7757798</v>
+      </c>
+      <c r="N43">
+        <v>118.5242202</v>
+      </c>
+      <c r="O43">
+        <v>29.55994051787999</v>
+      </c>
+      <c r="P43">
+        <v>88.96427968212001</v>
+      </c>
+      <c r="Q43">
+        <v>254.76427968212</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1079082747866734</v>
+      </c>
+      <c r="T43">
+        <v>1.168506370277365</v>
+      </c>
+      <c r="U43">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V43">
+        <v>0.2494</v>
+      </c>
+      <c r="W43">
+        <v>0.06860484000000001</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>2.089619586436649</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.09197864228129891</v>
+      </c>
+      <c r="C44">
+        <v>1191.940471716547</v>
+      </c>
+      <c r="D44">
+        <v>2062.674471716547</v>
+      </c>
+      <c r="E44">
+        <v>-280.0660000000003</v>
+      </c>
+      <c r="F44">
+        <v>1219.134</v>
+      </c>
+      <c r="G44">
+        <v>348.4</v>
+      </c>
+      <c r="H44">
+        <v>1403.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>393.1</v>
+      </c>
+      <c r="K44">
+        <v>165.8</v>
+      </c>
+      <c r="L44">
+        <v>227.3</v>
+      </c>
+      <c r="M44">
+        <v>111.4288476</v>
+      </c>
+      <c r="N44">
+        <v>115.8711524</v>
+      </c>
+      <c r="O44">
+        <v>28.89826540856</v>
+      </c>
+      <c r="P44">
+        <v>86.97288699144002</v>
+      </c>
+      <c r="Q44">
+        <v>252.77288699144</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1089044991056878</v>
+      </c>
+      <c r="T44">
+        <v>1.185350872134587</v>
+      </c>
+      <c r="U44">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V44">
+        <v>0.2494</v>
+      </c>
+      <c r="W44">
+        <v>0.06860484000000001</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>2.039866739140539</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.09897361183846053</v>
+      </c>
+      <c r="C45">
+        <v>996.2247192521456</v>
+      </c>
+      <c r="D45">
+        <v>1895.985719252146</v>
+      </c>
+      <c r="E45">
+        <v>-251.0390000000002</v>
+      </c>
+      <c r="F45">
+        <v>1248.161</v>
+      </c>
+      <c r="G45">
+        <v>348.4</v>
+      </c>
+      <c r="H45">
+        <v>1403.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>393.1</v>
+      </c>
+      <c r="K45">
+        <v>165.8</v>
+      </c>
+      <c r="L45">
+        <v>227.3</v>
+      </c>
+      <c r="M45">
+        <v>140.4181125</v>
+      </c>
+      <c r="N45">
+        <v>86.88188750000003</v>
+      </c>
+      <c r="O45">
+        <v>21.66834274250001</v>
+      </c>
+      <c r="P45">
+        <v>65.21354475750003</v>
+      </c>
+      <c r="Q45">
+        <v>231.0135447575</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1099356786639658</v>
+      </c>
+      <c r="T45">
+        <v>1.202786409144694</v>
+      </c>
+      <c r="U45">
+        <v>0.1125</v>
+      </c>
+      <c r="V45">
+        <v>0.2494</v>
+      </c>
+      <c r="W45">
+        <v>0.0844425</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>1.618737041490997</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.09931676419562213</v>
+      </c>
+      <c r="C46">
+        <v>959.7109661412549</v>
+      </c>
+      <c r="D46">
+        <v>1888.498966141255</v>
+      </c>
+      <c r="E46">
+        <v>-222.0120000000002</v>
+      </c>
+      <c r="F46">
+        <v>1277.188</v>
+      </c>
+      <c r="G46">
+        <v>348.4</v>
+      </c>
+      <c r="H46">
+        <v>1403.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>393.1</v>
+      </c>
+      <c r="K46">
+        <v>165.8</v>
+      </c>
+      <c r="L46">
+        <v>227.3</v>
+      </c>
+      <c r="M46">
+        <v>143.68365</v>
+      </c>
+      <c r="N46">
+        <v>83.61635000000001</v>
+      </c>
+      <c r="O46">
+        <v>20.85391769</v>
+      </c>
+      <c r="P46">
+        <v>62.76243231000001</v>
+      </c>
+      <c r="Q46">
+        <v>228.56243231</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1110036860636109</v>
+      </c>
+      <c r="T46">
+        <v>1.220844643905162</v>
+      </c>
+      <c r="U46">
+        <v>0.1125</v>
+      </c>
+      <c r="V46">
+        <v>0.2494</v>
+      </c>
+      <c r="W46">
+        <v>0.0844425</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>1.581947563275293</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.09965991655278374</v>
+      </c>
+      <c r="C47">
+        <v>923.256106944468</v>
+      </c>
+      <c r="D47">
+        <v>1881.071106944468</v>
+      </c>
+      <c r="E47">
+        <v>-192.9850000000001</v>
+      </c>
+      <c r="F47">
+        <v>1306.215</v>
+      </c>
+      <c r="G47">
+        <v>348.4</v>
+      </c>
+      <c r="H47">
+        <v>1403.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>393.1</v>
+      </c>
+      <c r="K47">
+        <v>165.8</v>
+      </c>
+      <c r="L47">
+        <v>227.3</v>
+      </c>
+      <c r="M47">
+        <v>146.9491875</v>
+      </c>
+      <c r="N47">
+        <v>80.35081250000002</v>
+      </c>
+      <c r="O47">
+        <v>20.0394926375</v>
+      </c>
+      <c r="P47">
+        <v>60.31131986250001</v>
+      </c>
+      <c r="Q47">
+        <v>226.1113198625</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1121105300959704</v>
+      </c>
+      <c r="T47">
+        <v>1.239559541747829</v>
+      </c>
+      <c r="U47">
+        <v>0.1125</v>
+      </c>
+      <c r="V47">
+        <v>0.2494</v>
+      </c>
+      <c r="W47">
+        <v>0.0844425</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>1.546793172980286</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1000030689099453</v>
+      </c>
+      <c r="C48">
+        <v>886.8594494583274</v>
+      </c>
+      <c r="D48">
+        <v>1873.701449458327</v>
+      </c>
+      <c r="E48">
+        <v>-163.9580000000001</v>
+      </c>
+      <c r="F48">
+        <v>1335.242</v>
+      </c>
+      <c r="G48">
+        <v>348.4</v>
+      </c>
+      <c r="H48">
+        <v>1403.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>393.1</v>
+      </c>
+      <c r="K48">
+        <v>165.8</v>
+      </c>
+      <c r="L48">
+        <v>227.3</v>
+      </c>
+      <c r="M48">
+        <v>150.214725</v>
+      </c>
+      <c r="N48">
+        <v>77.08527500000002</v>
+      </c>
+      <c r="O48">
+        <v>19.225067585</v>
+      </c>
+      <c r="P48">
+        <v>57.86020741500002</v>
+      </c>
+      <c r="Q48">
+        <v>223.660207415</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1132583683517506</v>
+      </c>
+      <c r="T48">
+        <v>1.258967583955039</v>
+      </c>
+      <c r="U48">
+        <v>0.1125</v>
+      </c>
+      <c r="V48">
+        <v>0.2494</v>
+      </c>
+      <c r="W48">
+        <v>0.0844425</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>1.513167234437237</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1343427578890864</v>
+      </c>
+      <c r="C49">
+        <v>330.1238119817174</v>
+      </c>
+      <c r="D49">
+        <v>1345.992811981717</v>
+      </c>
+      <c r="E49">
+        <v>-134.931</v>
+      </c>
+      <c r="F49">
+        <v>1364.269</v>
+      </c>
+      <c r="G49">
+        <v>348.4</v>
+      </c>
+      <c r="H49">
+        <v>1403.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>393.1</v>
+      </c>
+      <c r="K49">
+        <v>165.8</v>
+      </c>
+      <c r="L49">
+        <v>227.3</v>
+      </c>
+      <c r="M49">
+        <v>268.2152854</v>
+      </c>
+      <c r="N49">
+        <v>-40.91528539999996</v>
+      </c>
+      <c r="O49">
+        <v>-10.20427217875999</v>
+      </c>
+      <c r="P49">
+        <v>-30.71101322123997</v>
+      </c>
+      <c r="Q49">
+        <v>135.08898677876</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1159818398905449</v>
+      </c>
+      <c r="T49">
+        <v>1.30501697315154</v>
+      </c>
+      <c r="U49">
+        <v>0.1966</v>
+      </c>
+      <c r="V49">
+        <v>0.2113549192972281</v>
+      </c>
+      <c r="W49">
+        <v>0.155047622866165</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.8474535657467046</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1359207578890863</v>
+      </c>
+      <c r="C50">
+        <v>283.8994206355028</v>
+      </c>
+      <c r="D50">
+        <v>1328.795420635503</v>
+      </c>
+      <c r="E50">
+        <v>-105.9040000000002</v>
+      </c>
+      <c r="F50">
+        <v>1393.296</v>
+      </c>
+      <c r="G50">
+        <v>348.4</v>
+      </c>
+      <c r="H50">
+        <v>1403.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>393.1</v>
+      </c>
+      <c r="K50">
+        <v>165.8</v>
+      </c>
+      <c r="L50">
+        <v>227.3</v>
+      </c>
+      <c r="M50">
+        <v>273.9219936</v>
+      </c>
+      <c r="N50">
+        <v>-46.62199359999994</v>
+      </c>
+      <c r="O50">
+        <v>-11.62752520383998</v>
+      </c>
+      <c r="P50">
+        <v>-34.99446839615996</v>
+      </c>
+      <c r="Q50">
+        <v>130.8055316038401</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1174661060422862</v>
+      </c>
+      <c r="T50">
+        <v>1.330113453404455</v>
+      </c>
+      <c r="U50">
+        <v>0.1966</v>
+      </c>
+      <c r="V50">
+        <v>0.2069516918118692</v>
+      </c>
+      <c r="W50">
+        <v>0.1559132973897865</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.8297982831269817</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1374987578890863</v>
+      </c>
+      <c r="C51">
+        <v>238.108938318846</v>
+      </c>
+      <c r="D51">
+        <v>1312.031938318846</v>
+      </c>
+      <c r="E51">
+        <v>-76.87700000000018</v>
+      </c>
+      <c r="F51">
+        <v>1422.323</v>
+      </c>
+      <c r="G51">
+        <v>348.4</v>
+      </c>
+      <c r="H51">
+        <v>1403.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>393.1</v>
+      </c>
+      <c r="K51">
+        <v>165.8</v>
+      </c>
+      <c r="L51">
+        <v>227.3</v>
+      </c>
+      <c r="M51">
+        <v>279.6287018</v>
+      </c>
+      <c r="N51">
+        <v>-52.32870179999998</v>
+      </c>
+      <c r="O51">
+        <v>-13.05077822891999</v>
+      </c>
+      <c r="P51">
+        <v>-39.27792357107998</v>
+      </c>
+      <c r="Q51">
+        <v>126.52207642892</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.119008578709782</v>
+      </c>
+      <c r="T51">
+        <v>1.356194109353561</v>
+      </c>
+      <c r="U51">
+        <v>0.1966</v>
+      </c>
+      <c r="V51">
+        <v>0.2027281878973412</v>
+      </c>
+      <c r="W51">
+        <v>0.1567436382593827</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.8128636242876554</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1480397185430742</v>
+      </c>
+      <c r="C52">
+        <v>107.1087999323586</v>
+      </c>
+      <c r="D52">
+        <v>1210.058799932358</v>
+      </c>
+      <c r="E52">
+        <v>-47.85000000000014</v>
+      </c>
+      <c r="F52">
+        <v>1451.35</v>
+      </c>
+      <c r="G52">
+        <v>348.4</v>
+      </c>
+      <c r="H52">
+        <v>1403.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>393.1</v>
+      </c>
+      <c r="K52">
+        <v>165.8</v>
+      </c>
+      <c r="L52">
+        <v>227.3</v>
+      </c>
+      <c r="M52">
+        <v>310.2986299999999</v>
+      </c>
+      <c r="N52">
+        <v>-82.99862999999993</v>
+      </c>
+      <c r="O52">
+        <v>-20.69985832199998</v>
+      </c>
+      <c r="P52">
+        <v>-62.29877167799995</v>
+      </c>
+      <c r="Q52">
+        <v>103.5012283220001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1213386715919532</v>
+      </c>
+      <c r="T52">
+        <v>1.395592117545195</v>
+      </c>
+      <c r="U52">
+        <v>0.2138</v>
+      </c>
+      <c r="V52">
+        <v>0.1826905262198547</v>
+      </c>
+      <c r="W52">
+        <v>0.1747407654941951</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.7325201532472123</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1497897185430742</v>
+      </c>
+      <c r="C53">
+        <v>62.66700529773698</v>
+      </c>
+      <c r="D53">
+        <v>1194.644005297737</v>
+      </c>
+      <c r="E53">
+        <v>-18.82300000000009</v>
+      </c>
+      <c r="F53">
+        <v>1480.377</v>
+      </c>
+      <c r="G53">
+        <v>348.4</v>
+      </c>
+      <c r="H53">
+        <v>1403.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>393.1</v>
+      </c>
+      <c r="K53">
+        <v>165.8</v>
+      </c>
+      <c r="L53">
+        <v>227.3</v>
+      </c>
+      <c r="M53">
+        <v>316.5046026</v>
+      </c>
+      <c r="N53">
+        <v>-89.20460259999999</v>
+      </c>
+      <c r="O53">
+        <v>-22.24762788843999</v>
+      </c>
+      <c r="P53">
+        <v>-66.95697471155999</v>
+      </c>
+      <c r="Q53">
+        <v>98.84302528844002</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1230231342775033</v>
+      </c>
+      <c r="T53">
+        <v>1.424073589331832</v>
+      </c>
+      <c r="U53">
+        <v>0.2138</v>
+      </c>
+      <c r="V53">
+        <v>0.1791083590390732</v>
+      </c>
+      <c r="W53">
+        <v>0.1755066328374461</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.718157012987463</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1515397185430742</v>
+      </c>
+      <c r="C54">
+        <v>18.61300505490181</v>
+      </c>
+      <c r="D54">
+        <v>1179.617005054902</v>
+      </c>
+      <c r="E54">
+        <v>10.20399999999995</v>
+      </c>
+      <c r="F54">
+        <v>1509.404</v>
+      </c>
+      <c r="G54">
+        <v>348.4</v>
+      </c>
+      <c r="H54">
+        <v>1403.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>393.1</v>
+      </c>
+      <c r="K54">
+        <v>165.8</v>
+      </c>
+      <c r="L54">
+        <v>227.3</v>
+      </c>
+      <c r="M54">
+        <v>322.7105752</v>
+      </c>
+      <c r="N54">
+        <v>-95.41057519999998</v>
+      </c>
+      <c r="O54">
+        <v>-23.79539745487999</v>
+      </c>
+      <c r="P54">
+        <v>-71.61517774511999</v>
+      </c>
+      <c r="Q54">
+        <v>94.18482225488002</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1247777829082846</v>
+      </c>
+      <c r="T54">
+        <v>1.453741789109579</v>
+      </c>
+      <c r="U54">
+        <v>0.2138</v>
+      </c>
+      <c r="V54">
+        <v>0.1756639675190911</v>
+      </c>
+      <c r="W54">
+        <v>0.1762430437444183</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.7043463011992426</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1532897185430741</v>
+      </c>
+      <c r="C55">
+        <v>-25.06765279109322</v>
+      </c>
+      <c r="D55">
+        <v>1164.963347208907</v>
+      </c>
+      <c r="E55">
+        <v>39.23099999999999</v>
+      </c>
+      <c r="F55">
+        <v>1538.431</v>
+      </c>
+      <c r="G55">
+        <v>348.4</v>
+      </c>
+      <c r="H55">
+        <v>1403.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>393.1</v>
+      </c>
+      <c r="K55">
+        <v>165.8</v>
+      </c>
+      <c r="L55">
+        <v>227.3</v>
+      </c>
+      <c r="M55">
+        <v>328.9165478</v>
+      </c>
+      <c r="N55">
+        <v>-101.6165478</v>
+      </c>
+      <c r="O55">
+        <v>-25.34316702131999</v>
+      </c>
+      <c r="P55">
+        <v>-76.27338077867999</v>
+      </c>
+      <c r="Q55">
+        <v>89.52661922132002</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1266070974382481</v>
+      </c>
+      <c r="T55">
+        <v>1.484672465473612</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0.1723495530375988</v>
+      </c>
+      <c r="W55">
+        <v>0.1769516655605614</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.6910567483464267</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1550397185430741</v>
+      </c>
+      <c r="C56">
+        <v>-68.3887109333732</v>
+      </c>
+      <c r="D56">
+        <v>1150.669289066627</v>
+      </c>
+      <c r="E56">
+        <v>68.25800000000004</v>
+      </c>
+      <c r="F56">
+        <v>1567.458</v>
+      </c>
+      <c r="G56">
+        <v>348.4</v>
+      </c>
+      <c r="H56">
+        <v>1403.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>393.1</v>
+      </c>
+      <c r="K56">
+        <v>165.8</v>
+      </c>
+      <c r="L56">
+        <v>227.3</v>
+      </c>
+      <c r="M56">
+        <v>335.1225204</v>
+      </c>
+      <c r="N56">
+        <v>-107.8225204</v>
+      </c>
+      <c r="O56">
+        <v>-26.89093658775999</v>
+      </c>
+      <c r="P56">
+        <v>-80.93158381223998</v>
+      </c>
+      <c r="Q56">
+        <v>84.86841618776003</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1285159473825579</v>
+      </c>
+      <c r="T56">
+        <v>1.516947953853473</v>
+      </c>
+      <c r="U56">
+        <v>0.2138</v>
+      </c>
+      <c r="V56">
+        <v>0.1691578946480136</v>
+      </c>
+      <c r="W56">
+        <v>0.1776340421242547</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.6782594011548262</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1567897185430742</v>
+      </c>
+      <c r="C57">
+        <v>-111.3632457513181</v>
+      </c>
+      <c r="D57">
+        <v>1136.721754248682</v>
+      </c>
+      <c r="E57">
+        <v>97.28500000000008</v>
+      </c>
+      <c r="F57">
+        <v>1596.485</v>
+      </c>
+      <c r="G57">
+        <v>348.4</v>
+      </c>
+      <c r="H57">
+        <v>1403.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>393.1</v>
+      </c>
+      <c r="K57">
+        <v>165.8</v>
+      </c>
+      <c r="L57">
+        <v>227.3</v>
+      </c>
+      <c r="M57">
+        <v>341.328493</v>
+      </c>
+      <c r="N57">
+        <v>-114.028493</v>
+      </c>
+      <c r="O57">
+        <v>-28.4387061542</v>
+      </c>
+      <c r="P57">
+        <v>-85.58978684580002</v>
+      </c>
+      <c r="Q57">
+        <v>80.21021315419999</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1305096351021703</v>
+      </c>
+      <c r="T57">
+        <v>1.550657908383551</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.1660822965635043</v>
+      </c>
+      <c r="W57">
+        <v>0.1782916049947228</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.6659274120429202</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1585397185430741</v>
+      </c>
+      <c r="C58">
+        <v>-154.0037072096673</v>
+      </c>
+      <c r="D58">
+        <v>1123.108292790333</v>
+      </c>
+      <c r="E58">
+        <v>126.3119999999999</v>
+      </c>
+      <c r="F58">
+        <v>1625.512</v>
+      </c>
+      <c r="G58">
+        <v>348.4</v>
+      </c>
+      <c r="H58">
+        <v>1403.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>393.1</v>
+      </c>
+      <c r="K58">
+        <v>165.8</v>
+      </c>
+      <c r="L58">
+        <v>227.3</v>
+      </c>
+      <c r="M58">
+        <v>347.5344656</v>
+      </c>
+      <c r="N58">
+        <v>-120.2344656</v>
+      </c>
+      <c r="O58">
+        <v>-29.98647572063999</v>
+      </c>
+      <c r="P58">
+        <v>-90.24798987935998</v>
+      </c>
+      <c r="Q58">
+        <v>75.55201012064003</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1325939449908559</v>
+      </c>
+      <c r="T58">
+        <v>1.585900133574085</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.1631165412677274</v>
+      </c>
+      <c r="W58">
+        <v>0.1789256834769599</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.6540358511135824</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1602897185430742</v>
+      </c>
+      <c r="C59">
+        <v>-196.3219559245533</v>
+      </c>
+      <c r="D59">
+        <v>1109.817044075447</v>
+      </c>
+      <c r="E59">
+        <v>155.3389999999999</v>
+      </c>
+      <c r="F59">
+        <v>1654.539</v>
+      </c>
+      <c r="G59">
+        <v>348.4</v>
+      </c>
+      <c r="H59">
+        <v>1403.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>393.1</v>
+      </c>
+      <c r="K59">
+        <v>165.8</v>
+      </c>
+      <c r="L59">
+        <v>227.3</v>
+      </c>
+      <c r="M59">
+        <v>353.7404382</v>
+      </c>
+      <c r="N59">
+        <v>-126.4404382</v>
+      </c>
+      <c r="O59">
+        <v>-31.53424528707998</v>
+      </c>
+      <c r="P59">
+        <v>-94.90619291291998</v>
+      </c>
+      <c r="Q59">
+        <v>70.89380708708003</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.134775199525527</v>
+      </c>
+      <c r="T59">
+        <v>1.622781532029297</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.1602548475612761</v>
+      </c>
+      <c r="W59">
+        <v>0.1795375135913992</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.6425615379361511</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1620397185430741</v>
+      </c>
+      <c r="C60">
+        <v>-238.3292976283942</v>
+      </c>
+      <c r="D60">
+        <v>1096.836702371605</v>
+      </c>
+      <c r="E60">
+        <v>184.3659999999998</v>
+      </c>
+      <c r="F60">
+        <v>1683.566</v>
+      </c>
+      <c r="G60">
+        <v>348.4</v>
+      </c>
+      <c r="H60">
+        <v>1403.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>393.1</v>
+      </c>
+      <c r="K60">
+        <v>165.8</v>
+      </c>
+      <c r="L60">
+        <v>227.3</v>
+      </c>
+      <c r="M60">
+        <v>359.9464108</v>
+      </c>
+      <c r="N60">
+        <v>-132.6464108</v>
+      </c>
+      <c r="O60">
+        <v>-33.08201485351999</v>
+      </c>
+      <c r="P60">
+        <v>-99.56439594647998</v>
+      </c>
+      <c r="Q60">
+        <v>66.23560405352003</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1370603233237538</v>
+      </c>
+      <c r="T60">
+        <v>1.661419187553804</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0.1574918329481506</v>
+      </c>
+      <c r="W60">
+        <v>0.1801282461156854</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.6314828907303555</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1637897185430741</v>
+      </c>
+      <c r="C61">
+        <v>-280.0365152441632</v>
+      </c>
+      <c r="D61">
+        <v>1084.156484755837</v>
+      </c>
+      <c r="E61">
+        <v>213.3929999999998</v>
+      </c>
+      <c r="F61">
+        <v>1712.593</v>
+      </c>
+      <c r="G61">
+        <v>348.4</v>
+      </c>
+      <c r="H61">
+        <v>1403.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>393.1</v>
+      </c>
+      <c r="K61">
+        <v>165.8</v>
+      </c>
+      <c r="L61">
+        <v>227.3</v>
+      </c>
+      <c r="M61">
+        <v>366.1523834</v>
+      </c>
+      <c r="N61">
+        <v>-138.8523834</v>
+      </c>
+      <c r="O61">
+        <v>-34.62978441995998</v>
+      </c>
+      <c r="P61">
+        <v>-104.22259898004</v>
+      </c>
+      <c r="Q61">
+        <v>61.57740101996004</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1394569165755527</v>
+      </c>
+      <c r="T61">
+        <v>1.701941606762433</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0.1548224798473345</v>
+      </c>
+      <c r="W61">
+        <v>0.1806989538086399</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.620779790887468</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1655397185430741</v>
+      </c>
+      <c r="C62">
+        <v>-321.4538987602682</v>
+      </c>
+      <c r="D62">
+        <v>1071.766101239732</v>
+      </c>
+      <c r="E62">
+        <v>242.4199999999998</v>
+      </c>
+      <c r="F62">
+        <v>1741.62</v>
+      </c>
+      <c r="G62">
+        <v>348.4</v>
+      </c>
+      <c r="H62">
+        <v>1403.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>393.1</v>
+      </c>
+      <c r="K62">
+        <v>165.8</v>
+      </c>
+      <c r="L62">
+        <v>227.3</v>
+      </c>
+      <c r="M62">
+        <v>372.358356</v>
+      </c>
+      <c r="N62">
+        <v>-145.0583559999999</v>
+      </c>
+      <c r="O62">
+        <v>-36.17755398639998</v>
+      </c>
+      <c r="P62">
+        <v>-108.8808020136</v>
+      </c>
+      <c r="Q62">
+        <v>56.91919798640004</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1419733394899415</v>
+      </c>
+      <c r="T62">
+        <v>1.744490146931494</v>
+      </c>
+      <c r="U62">
+        <v>0.2138</v>
+      </c>
+      <c r="V62">
+        <v>0.1522421051832123</v>
+      </c>
+      <c r="W62">
+        <v>0.1812506379118292</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.6104334610393436</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1672897185430741</v>
+      </c>
+      <c r="C63">
+        <v>-362.5912730800164</v>
+      </c>
+      <c r="D63">
+        <v>1059.655726919983</v>
+      </c>
+      <c r="E63">
+        <v>271.4469999999999</v>
+      </c>
+      <c r="F63">
+        <v>1770.647</v>
+      </c>
+      <c r="G63">
+        <v>348.4</v>
+      </c>
+      <c r="H63">
+        <v>1403.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>393.1</v>
+      </c>
+      <c r="K63">
+        <v>165.8</v>
+      </c>
+      <c r="L63">
+        <v>227.3</v>
+      </c>
+      <c r="M63">
+        <v>378.5643286</v>
+      </c>
+      <c r="N63">
+        <v>-151.2643285999999</v>
+      </c>
+      <c r="O63">
+        <v>-37.72532355283998</v>
+      </c>
+      <c r="P63">
+        <v>-113.53900504716</v>
+      </c>
+      <c r="Q63">
+        <v>52.26099495284005</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1446188097332734</v>
+      </c>
+      <c r="T63">
+        <v>1.789220663519481</v>
+      </c>
+      <c r="U63">
+        <v>0.2138</v>
+      </c>
+      <c r="V63">
+        <v>0.1497463329670941</v>
+      </c>
+      <c r="W63">
+        <v>0.1817842340116353</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.6004263551206659</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1690397185430741</v>
+      </c>
+      <c r="C64">
+        <v>-403.4580240040709</v>
+      </c>
+      <c r="D64">
+        <v>1047.815975995929</v>
+      </c>
+      <c r="E64">
+        <v>300.4739999999999</v>
+      </c>
+      <c r="F64">
+        <v>1799.674</v>
+      </c>
+      <c r="G64">
+        <v>348.4</v>
+      </c>
+      <c r="H64">
+        <v>1403.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>393.1</v>
+      </c>
+      <c r="K64">
+        <v>165.8</v>
+      </c>
+      <c r="L64">
+        <v>227.3</v>
+      </c>
+      <c r="M64">
+        <v>384.7703012</v>
+      </c>
+      <c r="N64">
+        <v>-157.4703012</v>
+      </c>
+      <c r="O64">
+        <v>-39.27309311927999</v>
+      </c>
+      <c r="P64">
+        <v>-118.19720808072</v>
+      </c>
+      <c r="Q64">
+        <v>47.60279191928001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1474035152525701</v>
+      </c>
+      <c r="T64">
+        <v>1.836305417822625</v>
+      </c>
+      <c r="U64">
+        <v>0.2138</v>
+      </c>
+      <c r="V64">
+        <v>0.1473310695321409</v>
+      </c>
+      <c r="W64">
+        <v>0.1823006173340283</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.5907420590703325</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1707897185430741</v>
+      </c>
+      <c r="C65">
+        <v>-444.0631224903079</v>
+      </c>
+      <c r="D65">
+        <v>1036.237877509692</v>
+      </c>
+      <c r="E65">
+        <v>329.5009999999997</v>
+      </c>
+      <c r="F65">
+        <v>1828.701</v>
+      </c>
+      <c r="G65">
+        <v>348.4</v>
+      </c>
+      <c r="H65">
+        <v>1403.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>393.1</v>
+      </c>
+      <c r="K65">
+        <v>165.8</v>
+      </c>
+      <c r="L65">
+        <v>227.3</v>
+      </c>
+      <c r="M65">
+        <v>390.9762737999999</v>
+      </c>
+      <c r="N65">
+        <v>-163.6762737999999</v>
+      </c>
+      <c r="O65">
+        <v>-40.82086268571997</v>
+      </c>
+      <c r="P65">
+        <v>-122.85541111428</v>
+      </c>
+      <c r="Q65">
+        <v>42.94458888572005</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1503387453945314</v>
+      </c>
+      <c r="T65">
+        <v>1.885935293979993</v>
+      </c>
+      <c r="U65">
+        <v>0.2138</v>
+      </c>
+      <c r="V65">
+        <v>0.1449924811268689</v>
+      </c>
+      <c r="W65">
+        <v>0.1828006075350754</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.5813652009898511</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1725397185430741</v>
+      </c>
+      <c r="C66">
+        <v>-484.4151473228678</v>
+      </c>
+      <c r="D66">
+        <v>1024.912852677132</v>
+      </c>
+      <c r="E66">
+        <v>358.5279999999998</v>
+      </c>
+      <c r="F66">
+        <v>1857.728</v>
+      </c>
+      <c r="G66">
+        <v>348.4</v>
+      </c>
+      <c r="H66">
+        <v>1403.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>393.1</v>
+      </c>
+      <c r="K66">
+        <v>165.8</v>
+      </c>
+      <c r="L66">
+        <v>227.3</v>
+      </c>
+      <c r="M66">
+        <v>397.1822463999999</v>
+      </c>
+      <c r="N66">
+        <v>-169.8822463999999</v>
+      </c>
+      <c r="O66">
+        <v>-42.36863225215998</v>
+      </c>
+      <c r="P66">
+        <v>-127.5136141478399</v>
+      </c>
+      <c r="Q66">
+        <v>38.28638585216007</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1534370438777128</v>
+      </c>
+      <c r="T66">
+        <v>1.938322385479438</v>
+      </c>
+      <c r="U66">
+        <v>0.2138</v>
+      </c>
+      <c r="V66">
+        <v>0.1427269736092615</v>
+      </c>
+      <c r="W66">
+        <v>0.1832849730423399</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.5722813697243847</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1742897185430741</v>
+      </c>
+      <c r="C67">
+        <v>-524.5223063107676</v>
+      </c>
+      <c r="D67">
+        <v>1013.832693689232</v>
+      </c>
+      <c r="E67">
+        <v>387.5549999999998</v>
+      </c>
+      <c r="F67">
+        <v>1886.755</v>
+      </c>
+      <c r="G67">
+        <v>348.4</v>
+      </c>
+      <c r="H67">
+        <v>1403.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>393.1</v>
+      </c>
+      <c r="K67">
+        <v>165.8</v>
+      </c>
+      <c r="L67">
+        <v>227.3</v>
+      </c>
+      <c r="M67">
+        <v>403.3882189999999</v>
+      </c>
+      <c r="N67">
+        <v>-176.0882189999999</v>
+      </c>
+      <c r="O67">
+        <v>-43.91640181859997</v>
+      </c>
+      <c r="P67">
+        <v>-132.1718171813999</v>
+      </c>
+      <c r="Q67">
+        <v>33.62818281860007</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1567123879885046</v>
+      </c>
+      <c r="T67">
+        <v>1.993703025064565</v>
+      </c>
+      <c r="U67">
+        <v>0.2138</v>
+      </c>
+      <c r="V67">
+        <v>0.1405311740152729</v>
+      </c>
+      <c r="W67">
+        <v>0.1837544349955346</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.5634770409593941</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1760397185430742</v>
+      </c>
+      <c r="C68">
+        <v>-564.3924561261836</v>
+      </c>
+      <c r="D68">
+        <v>1002.989543873817</v>
+      </c>
+      <c r="E68">
+        <v>416.5819999999999</v>
+      </c>
+      <c r="F68">
+        <v>1915.782</v>
+      </c>
+      <c r="G68">
+        <v>348.4</v>
+      </c>
+      <c r="H68">
+        <v>1403.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>393.1</v>
+      </c>
+      <c r="K68">
+        <v>165.8</v>
+      </c>
+      <c r="L68">
+        <v>227.3</v>
+      </c>
+      <c r="M68">
+        <v>409.5941916</v>
+      </c>
+      <c r="N68">
+        <v>-182.2941916</v>
+      </c>
+      <c r="O68">
+        <v>-45.46417138503998</v>
+      </c>
+      <c r="P68">
+        <v>-136.83002021496</v>
+      </c>
+      <c r="Q68">
+        <v>28.96997978504001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1601803993999312</v>
+      </c>
+      <c r="T68">
+        <v>2.05234134933117</v>
+      </c>
+      <c r="U68">
+        <v>0.2138</v>
+      </c>
+      <c r="V68">
+        <v>0.1384019138029202</v>
+      </c>
+      <c r="W68">
+        <v>0.1842096708289357</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.5549395100357668</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1777897185430742</v>
+      </c>
+      <c r="C69">
+        <v>-604.033120883149</v>
+      </c>
+      <c r="D69">
+        <v>992.375879116851</v>
+      </c>
+      <c r="E69">
+        <v>445.6089999999999</v>
+      </c>
+      <c r="F69">
+        <v>1944.809</v>
+      </c>
+      <c r="G69">
+        <v>348.4</v>
+      </c>
+      <c r="H69">
+        <v>1403.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>393.1</v>
+      </c>
+      <c r="K69">
+        <v>165.8</v>
+      </c>
+      <c r="L69">
+        <v>227.3</v>
+      </c>
+      <c r="M69">
+        <v>415.8001642</v>
+      </c>
+      <c r="N69">
+        <v>-188.5001642</v>
+      </c>
+      <c r="O69">
+        <v>-47.01194095147999</v>
+      </c>
+      <c r="P69">
+        <v>-141.48822324852</v>
+      </c>
+      <c r="Q69">
+        <v>24.31177675148001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1638585933211413</v>
+      </c>
+      <c r="T69">
+        <v>2.114533511432114</v>
+      </c>
+      <c r="U69">
+        <v>0.2138</v>
+      </c>
+      <c r="V69">
+        <v>0.1363362135969065</v>
+      </c>
+      <c r="W69">
+        <v>0.1846513175329814</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.5466568307815016</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1795397185430742</v>
+      </c>
+      <c r="C70">
+        <v>-643.451509549009</v>
+      </c>
+      <c r="D70">
+        <v>981.9844904509911</v>
+      </c>
+      <c r="E70">
+        <v>474.636</v>
+      </c>
+      <c r="F70">
+        <v>1973.836</v>
+      </c>
+      <c r="G70">
+        <v>348.4</v>
+      </c>
+      <c r="H70">
+        <v>1403.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>393.1</v>
+      </c>
+      <c r="K70">
+        <v>165.8</v>
+      </c>
+      <c r="L70">
+        <v>227.3</v>
+      </c>
+      <c r="M70">
+        <v>422.0061368</v>
+      </c>
+      <c r="N70">
+        <v>-194.7061368</v>
+      </c>
+      <c r="O70">
+        <v>-48.55971051791998</v>
+      </c>
+      <c r="P70">
+        <v>-146.14642628208</v>
+      </c>
+      <c r="Q70">
+        <v>19.65357371792004</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.167766674362427</v>
+      </c>
+      <c r="T70">
+        <v>2.180612683664368</v>
+      </c>
+      <c r="U70">
+        <v>0.2138</v>
+      </c>
+      <c r="V70">
+        <v>0.1343312692793049</v>
+      </c>
+      <c r="W70">
+        <v>0.1850799746280846</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.5386177597405972</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1812897185430742</v>
+      </c>
+      <c r="C71">
+        <v>-682.6545322732907</v>
+      </c>
+      <c r="D71">
+        <v>971.8084677267094</v>
+      </c>
+      <c r="E71">
+        <v>503.663</v>
+      </c>
+      <c r="F71">
+        <v>2002.863</v>
+      </c>
+      <c r="G71">
+        <v>348.4</v>
+      </c>
+      <c r="H71">
+        <v>1403.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>393.1</v>
+      </c>
+      <c r="K71">
+        <v>165.8</v>
+      </c>
+      <c r="L71">
+        <v>227.3</v>
+      </c>
+      <c r="M71">
+        <v>428.2121094</v>
+      </c>
+      <c r="N71">
+        <v>-200.9121094</v>
+      </c>
+      <c r="O71">
+        <v>-50.10748008435998</v>
+      </c>
+      <c r="P71">
+        <v>-150.80462931564</v>
+      </c>
+      <c r="Q71">
+        <v>14.99537068436004</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1719268896644408</v>
+      </c>
+      <c r="T71">
+        <v>2.250955028298703</v>
+      </c>
+      <c r="U71">
+        <v>0.2138</v>
+      </c>
+      <c r="V71">
+        <v>0.1323844392897498</v>
+      </c>
+      <c r="W71">
+        <v>0.1854962068798515</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.530811705251603</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1830397185430742</v>
+      </c>
+      <c r="C72">
+        <v>-721.6488157117208</v>
+      </c>
+      <c r="D72">
+        <v>961.8411842882794</v>
+      </c>
+      <c r="E72">
+        <v>532.6900000000001</v>
+      </c>
+      <c r="F72">
+        <v>2031.89</v>
+      </c>
+      <c r="G72">
+        <v>348.4</v>
+      </c>
+      <c r="H72">
+        <v>1403.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>393.1</v>
+      </c>
+      <c r="K72">
+        <v>165.8</v>
+      </c>
+      <c r="L72">
+        <v>227.3</v>
+      </c>
+      <c r="M72">
+        <v>434.418082</v>
+      </c>
+      <c r="N72">
+        <v>-207.118082</v>
+      </c>
+      <c r="O72">
+        <v>-51.65524965079999</v>
+      </c>
+      <c r="P72">
+        <v>-155.4628323492</v>
+      </c>
+      <c r="Q72">
+        <v>10.33716765079998</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1763644526532554</v>
+      </c>
+      <c r="T72">
+        <v>2.325986862575326</v>
+      </c>
+      <c r="U72">
+        <v>0.2138</v>
+      </c>
+      <c r="V72">
+        <v>0.1304932330141819</v>
+      </c>
+      <c r="W72">
+        <v>0.1859005467815679</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.5232286808908659</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1847897185430741</v>
+      </c>
+      <c r="C73">
+        <v>-760.4407174167984</v>
+      </c>
+      <c r="D73">
+        <v>952.0762825832015</v>
+      </c>
+      <c r="E73">
+        <v>561.7169999999999</v>
+      </c>
+      <c r="F73">
+        <v>2060.917</v>
+      </c>
+      <c r="G73">
+        <v>348.4</v>
+      </c>
+      <c r="H73">
+        <v>1403.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>393.1</v>
+      </c>
+      <c r="K73">
+        <v>165.8</v>
+      </c>
+      <c r="L73">
+        <v>227.3</v>
+      </c>
+      <c r="M73">
+        <v>440.6240546</v>
+      </c>
+      <c r="N73">
+        <v>-213.3240546</v>
+      </c>
+      <c r="O73">
+        <v>-53.20301921723998</v>
+      </c>
+      <c r="P73">
+        <v>-160.12103538276</v>
+      </c>
+      <c r="Q73">
+        <v>5.678964617240041</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1811080544688849</v>
+      </c>
+      <c r="T73">
+        <v>2.406193306112405</v>
+      </c>
+      <c r="U73">
+        <v>0.2138</v>
+      </c>
+      <c r="V73">
+        <v>0.1286553001548273</v>
+      </c>
+      <c r="W73">
+        <v>0.1862934968268979</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.5158592628501495</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1865397185430741</v>
+      </c>
+      <c r="C74">
+        <v>-799.0363393605935</v>
+      </c>
+      <c r="D74">
+        <v>942.5076606394065</v>
+      </c>
+      <c r="E74">
+        <v>590.7439999999999</v>
+      </c>
+      <c r="F74">
+        <v>2089.944</v>
+      </c>
+      <c r="G74">
+        <v>348.4</v>
+      </c>
+      <c r="H74">
+        <v>1403.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>393.1</v>
+      </c>
+      <c r="K74">
+        <v>165.8</v>
+      </c>
+      <c r="L74">
+        <v>227.3</v>
+      </c>
+      <c r="M74">
+        <v>446.8300272</v>
+      </c>
+      <c r="N74">
+        <v>-219.5300271999999</v>
+      </c>
+      <c r="O74">
+        <v>-54.75078878367998</v>
+      </c>
+      <c r="P74">
+        <v>-164.77923841632</v>
+      </c>
+      <c r="Q74">
+        <v>1.020761583680041</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1861904849856308</v>
+      </c>
+      <c r="T74">
+        <v>2.492128781330706</v>
+      </c>
+      <c r="U74">
+        <v>0.2138</v>
+      </c>
+      <c r="V74">
+        <v>0.1268684209860102</v>
+      </c>
+      <c r="W74">
+        <v>0.186675531593191</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.5086945508661196</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1882897185430741</v>
+      </c>
+      <c r="C75">
+        <v>-837.4415406502112</v>
+      </c>
+      <c r="D75">
+        <v>933.1294593497889</v>
+      </c>
+      <c r="E75">
+        <v>619.771</v>
+      </c>
+      <c r="F75">
+        <v>2118.971</v>
+      </c>
+      <c r="G75">
+        <v>348.4</v>
+      </c>
+      <c r="H75">
+        <v>1403.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>393.1</v>
+      </c>
+      <c r="K75">
+        <v>165.8</v>
+      </c>
+      <c r="L75">
+        <v>227.3</v>
+      </c>
+      <c r="M75">
+        <v>453.0359998</v>
+      </c>
+      <c r="N75">
+        <v>-225.7359997999999</v>
+      </c>
+      <c r="O75">
+        <v>-56.29855835011998</v>
+      </c>
+      <c r="P75">
+        <v>-169.43744144988</v>
+      </c>
+      <c r="Q75">
+        <v>-3.637441449879958</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1916493918369504</v>
+      </c>
+      <c r="T75">
+        <v>2.584429847305917</v>
+      </c>
+      <c r="U75">
+        <v>0.2138</v>
+      </c>
+      <c r="V75">
+        <v>0.1251304974108594</v>
+      </c>
+      <c r="W75">
+        <v>0.1870470996535583</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.5017261323611043</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2089740490167483</v>
+      </c>
+      <c r="C76">
+        <v>-964.6637614743604</v>
+      </c>
+      <c r="D76">
+        <v>834.9342385256398</v>
+      </c>
+      <c r="E76">
+        <v>648.798</v>
+      </c>
+      <c r="F76">
+        <v>2147.998</v>
+      </c>
+      <c r="G76">
+        <v>348.4</v>
+      </c>
+      <c r="H76">
+        <v>1403.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>393.1</v>
+      </c>
+      <c r="K76">
+        <v>165.8</v>
+      </c>
+      <c r="L76">
+        <v>227.3</v>
+      </c>
+      <c r="M76">
+        <v>512.9419224000001</v>
+      </c>
+      <c r="N76">
+        <v>-285.6419224000001</v>
+      </c>
+      <c r="O76">
+        <v>-71.23909544656</v>
+      </c>
+      <c r="P76">
+        <v>-214.4028269534401</v>
+      </c>
+      <c r="Q76">
+        <v>-48.60282695344006</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1991987164217335</v>
+      </c>
+      <c r="T76">
+        <v>2.712076412002271</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.1105166443303367</v>
+      </c>
+      <c r="W76">
+        <v>0.2124086253339156</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.443130089536234</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2109740490167482</v>
+      </c>
+      <c r="C77">
+        <v>-1002.10069585154</v>
+      </c>
+      <c r="D77">
+        <v>826.5243041484592</v>
+      </c>
+      <c r="E77">
+        <v>677.8249999999996</v>
+      </c>
+      <c r="F77">
+        <v>2177.025</v>
+      </c>
+      <c r="G77">
+        <v>348.4</v>
+      </c>
+      <c r="H77">
+        <v>1403.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>393.1</v>
+      </c>
+      <c r="K77">
+        <v>165.8</v>
+      </c>
+      <c r="L77">
+        <v>227.3</v>
+      </c>
+      <c r="M77">
+        <v>519.87357</v>
+      </c>
+      <c r="N77">
+        <v>-292.57357</v>
+      </c>
+      <c r="O77">
+        <v>-72.96784835799998</v>
+      </c>
+      <c r="P77">
+        <v>-219.605721642</v>
+      </c>
+      <c r="Q77">
+        <v>-53.80572164199998</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2056146650786028</v>
+      </c>
+      <c r="T77">
+        <v>2.820559468482362</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.1090430890725989</v>
+      </c>
+      <c r="W77">
+        <v>0.2127605103294634</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.4372216883424176</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2129740490167482</v>
+      </c>
+      <c r="C78">
+        <v>-1039.369900377728</v>
+      </c>
+      <c r="D78">
+        <v>818.2820996222717</v>
+      </c>
+      <c r="E78">
+        <v>706.8519999999996</v>
+      </c>
+      <c r="F78">
+        <v>2206.052</v>
+      </c>
+      <c r="G78">
+        <v>348.4</v>
+      </c>
+      <c r="H78">
+        <v>1403.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>393.1</v>
+      </c>
+      <c r="K78">
+        <v>165.8</v>
+      </c>
+      <c r="L78">
+        <v>227.3</v>
+      </c>
+      <c r="M78">
+        <v>526.8052176</v>
+      </c>
+      <c r="N78">
+        <v>-299.5052176</v>
+      </c>
+      <c r="O78">
+        <v>-74.69660126943998</v>
+      </c>
+      <c r="P78">
+        <v>-224.80861633056</v>
+      </c>
+      <c r="Q78">
+        <v>-59.00861633055999</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2125652761235446</v>
+      </c>
+      <c r="T78">
+        <v>2.938082779669128</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.1076083115848016</v>
+      </c>
+      <c r="W78">
+        <v>0.2131031351935494</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.4314687713905436</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2149740490167482</v>
+      </c>
+      <c r="C79">
+        <v>-1076.476343377799</v>
+      </c>
+      <c r="D79">
+        <v>810.2026566222009</v>
+      </c>
+      <c r="E79">
+        <v>735.8789999999997</v>
+      </c>
+      <c r="F79">
+        <v>2235.079</v>
+      </c>
+      <c r="G79">
+        <v>348.4</v>
+      </c>
+      <c r="H79">
+        <v>1403.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>393.1</v>
+      </c>
+      <c r="K79">
+        <v>165.8</v>
+      </c>
+      <c r="L79">
+        <v>227.3</v>
+      </c>
+      <c r="M79">
+        <v>533.7368652</v>
+      </c>
+      <c r="N79">
+        <v>-306.4368652</v>
+      </c>
+      <c r="O79">
+        <v>-76.42535418087999</v>
+      </c>
+      <c r="P79">
+        <v>-230.01151101912</v>
+      </c>
+      <c r="Q79">
+        <v>-64.21151101912</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2201202881289161</v>
+      </c>
+      <c r="T79">
+        <v>3.065825509219959</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.1062108010447392</v>
+      </c>
+      <c r="W79">
+        <v>0.2134368607105163</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.4258652808530041</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2169740490167482</v>
+      </c>
+      <c r="C80">
+        <v>-1113.424798872826</v>
+      </c>
+      <c r="D80">
+        <v>802.2812011271737</v>
+      </c>
+      <c r="E80">
+        <v>764.9059999999997</v>
+      </c>
+      <c r="F80">
+        <v>2264.106</v>
+      </c>
+      <c r="G80">
+        <v>348.4</v>
+      </c>
+      <c r="H80">
+        <v>1403.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>393.1</v>
+      </c>
+      <c r="K80">
+        <v>165.8</v>
+      </c>
+      <c r="L80">
+        <v>227.3</v>
+      </c>
+      <c r="M80">
+        <v>540.6685127999999</v>
+      </c>
+      <c r="N80">
+        <v>-313.3685127999999</v>
+      </c>
+      <c r="O80">
+        <v>-78.15410709231996</v>
+      </c>
+      <c r="P80">
+        <v>-235.2144057076799</v>
+      </c>
+      <c r="Q80">
+        <v>-69.41440570767992</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2283621194075033</v>
+      </c>
+      <c r="T80">
+        <v>3.205181214184503</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.1048491241082682</v>
+      </c>
+      <c r="W80">
+        <v>0.2137620291629456</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.420405469560017</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2189740490167483</v>
+      </c>
+      <c r="C81">
+        <v>-1150.219855986776</v>
+      </c>
+      <c r="D81">
+        <v>794.513144013224</v>
+      </c>
+      <c r="E81">
+        <v>793.9329999999998</v>
+      </c>
+      <c r="F81">
+        <v>2293.133</v>
+      </c>
+      <c r="G81">
+        <v>348.4</v>
+      </c>
+      <c r="H81">
+        <v>1403.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>393.1</v>
+      </c>
+      <c r="K81">
+        <v>165.8</v>
+      </c>
+      <c r="L81">
+        <v>227.3</v>
+      </c>
+      <c r="M81">
+        <v>547.6001603999999</v>
+      </c>
+      <c r="N81">
+        <v>-320.3001603999999</v>
+      </c>
+      <c r="O81">
+        <v>-79.88286000375997</v>
+      </c>
+      <c r="P81">
+        <v>-240.41730039624</v>
+      </c>
+      <c r="Q81">
+        <v>-74.61730039623995</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2373888869983367</v>
+      </c>
+      <c r="T81">
+        <v>3.357808891050431</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.1035219200056319</v>
+      </c>
+      <c r="W81">
+        <v>0.2140789655026551</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.4150838813377382</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2209740490167482</v>
+      </c>
+      <c r="C82">
+        <v>-1186.865927811963</v>
+      </c>
+      <c r="D82">
+        <v>786.8940721880373</v>
+      </c>
+      <c r="E82">
+        <v>822.9599999999998</v>
+      </c>
+      <c r="F82">
+        <v>2322.16</v>
+      </c>
+      <c r="G82">
+        <v>348.4</v>
+      </c>
+      <c r="H82">
+        <v>1403.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>393.1</v>
+      </c>
+      <c r="K82">
+        <v>165.8</v>
+      </c>
+      <c r="L82">
+        <v>227.3</v>
+      </c>
+      <c r="M82">
+        <v>554.531808</v>
+      </c>
+      <c r="N82">
+        <v>-327.2318079999999</v>
+      </c>
+      <c r="O82">
+        <v>-81.61161291519997</v>
+      </c>
+      <c r="P82">
+        <v>-245.6201950848</v>
+      </c>
+      <c r="Q82">
+        <v>-79.82019508479996</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2473183313482535</v>
+      </c>
+      <c r="T82">
+        <v>3.525699335602953</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.1022278960055615</v>
+      </c>
+      <c r="W82">
+        <v>0.2143879784338719</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.4098953328210165</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2229740490167482</v>
+      </c>
+      <c r="C83">
+        <v>-1223.367259769255</v>
+      </c>
+      <c r="D83">
+        <v>779.4197402307453</v>
+      </c>
+      <c r="E83">
+        <v>851.9869999999999</v>
+      </c>
+      <c r="F83">
+        <v>2351.187</v>
+      </c>
+      <c r="G83">
+        <v>348.4</v>
+      </c>
+      <c r="H83">
+        <v>1403.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>393.1</v>
+      </c>
+      <c r="K83">
+        <v>165.8</v>
+      </c>
+      <c r="L83">
+        <v>227.3</v>
+      </c>
+      <c r="M83">
+        <v>561.4634556</v>
+      </c>
+      <c r="N83">
+        <v>-334.1634556</v>
+      </c>
+      <c r="O83">
+        <v>-83.34036582663998</v>
+      </c>
+      <c r="P83">
+        <v>-250.82308977336</v>
+      </c>
+      <c r="Q83">
+        <v>-85.02308977335997</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2582929803665827</v>
+      </c>
+      <c r="T83">
+        <v>3.711262458529425</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.1009658232153694</v>
+      </c>
+      <c r="W83">
+        <v>0.2146893614161698</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.4048348966133496</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2249740490167483</v>
+      </c>
+      <c r="C84">
+        <v>-1259.727937496302</v>
+      </c>
+      <c r="D84">
+        <v>772.0860625036978</v>
+      </c>
+      <c r="E84">
+        <v>881.0139999999999</v>
+      </c>
+      <c r="F84">
+        <v>2380.214</v>
+      </c>
+      <c r="G84">
+        <v>348.4</v>
+      </c>
+      <c r="H84">
+        <v>1403.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>393.1</v>
+      </c>
+      <c r="K84">
+        <v>165.8</v>
+      </c>
+      <c r="L84">
+        <v>227.3</v>
+      </c>
+      <c r="M84">
+        <v>568.3951032</v>
+      </c>
+      <c r="N84">
+        <v>-341.0951032</v>
+      </c>
+      <c r="O84">
+        <v>-85.06911873807998</v>
+      </c>
+      <c r="P84">
+        <v>-256.02598446192</v>
+      </c>
+      <c r="Q84">
+        <v>-90.22598446192001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2704870348313929</v>
+      </c>
+      <c r="T84">
+        <v>3.917443706225504</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.09973453268835268</v>
+      </c>
+      <c r="W84">
+        <v>0.2149833935940214</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3998978856790405</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2269740490167483</v>
+      </c>
+      <c r="C85">
+        <v>-1295.951894294589</v>
+      </c>
+      <c r="D85">
+        <v>764.8891057054107</v>
+      </c>
+      <c r="E85">
+        <v>910.0409999999999</v>
+      </c>
+      <c r="F85">
+        <v>2409.241</v>
+      </c>
+      <c r="G85">
+        <v>348.4</v>
+      </c>
+      <c r="H85">
+        <v>1403.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>393.1</v>
+      </c>
+      <c r="K85">
+        <v>165.8</v>
+      </c>
+      <c r="L85">
+        <v>227.3</v>
+      </c>
+      <c r="M85">
+        <v>575.3267508</v>
+      </c>
+      <c r="N85">
+        <v>-348.0267508</v>
+      </c>
+      <c r="O85">
+        <v>-86.79787164951999</v>
+      </c>
+      <c r="P85">
+        <v>-261.22887915048</v>
+      </c>
+      <c r="Q85">
+        <v>-95.42887915047999</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2841156839391219</v>
+      </c>
+      <c r="T85">
+        <v>4.147881571297593</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.09853291181258939</v>
+      </c>
+      <c r="W85">
+        <v>0.2152703406591537</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3950798388636303</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2289740490167483</v>
+      </c>
+      <c r="C86">
+        <v>-1332.042918163829</v>
+      </c>
+      <c r="D86">
+        <v>757.8250818361709</v>
+      </c>
+      <c r="E86">
+        <v>939.0679999999995</v>
+      </c>
+      <c r="F86">
+        <v>2438.268</v>
+      </c>
+      <c r="G86">
+        <v>348.4</v>
+      </c>
+      <c r="H86">
+        <v>1403.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>393.1</v>
+      </c>
+      <c r="K86">
+        <v>165.8</v>
+      </c>
+      <c r="L86">
+        <v>227.3</v>
+      </c>
+      <c r="M86">
+        <v>582.2583983999999</v>
+      </c>
+      <c r="N86">
+        <v>-354.9583983999999</v>
+      </c>
+      <c r="O86">
+        <v>-88.52662456095996</v>
+      </c>
+      <c r="P86">
+        <v>-266.4317738390399</v>
+      </c>
+      <c r="Q86">
+        <v>-100.6317738390399</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2994479141853169</v>
+      </c>
+      <c r="T86">
+        <v>4.40712416950369</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.09735990095767763</v>
+      </c>
+      <c r="W86">
+        <v>0.2155504556513066</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3903765074485872</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2309740490167483</v>
+      </c>
+      <c r="C87">
+        <v>-1368.004658450132</v>
+      </c>
+      <c r="D87">
+        <v>750.8903415498675</v>
+      </c>
+      <c r="E87">
+        <v>968.0949999999996</v>
+      </c>
+      <c r="F87">
+        <v>2467.295</v>
+      </c>
+      <c r="G87">
+        <v>348.4</v>
+      </c>
+      <c r="H87">
+        <v>1403.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>393.1</v>
+      </c>
+      <c r="K87">
+        <v>165.8</v>
+      </c>
+      <c r="L87">
+        <v>227.3</v>
+      </c>
+      <c r="M87">
+        <v>589.1900459999999</v>
+      </c>
+      <c r="N87">
+        <v>-361.8900459999999</v>
+      </c>
+      <c r="O87">
+        <v>-90.25537747239997</v>
+      </c>
+      <c r="P87">
+        <v>-271.6346685276</v>
+      </c>
+      <c r="Q87">
+        <v>-105.8346685275999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3168244417976714</v>
+      </c>
+      <c r="T87">
+        <v>4.700932447470604</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.09621449035817553</v>
+      </c>
+      <c r="W87">
+        <v>0.2158239797024677</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3857838426550744</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2329740490167482</v>
+      </c>
+      <c r="C88">
+        <v>-1403.840632132471</v>
+      </c>
+      <c r="D88">
+        <v>744.0813678675288</v>
+      </c>
+      <c r="E88">
+        <v>997.1219999999996</v>
+      </c>
+      <c r="F88">
+        <v>2496.322</v>
+      </c>
+      <c r="G88">
+        <v>348.4</v>
+      </c>
+      <c r="H88">
+        <v>1403.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>393.1</v>
+      </c>
+      <c r="K88">
+        <v>165.8</v>
+      </c>
+      <c r="L88">
+        <v>227.3</v>
+      </c>
+      <c r="M88">
+        <v>596.1216936</v>
+      </c>
+      <c r="N88">
+        <v>-368.8216935999999</v>
+      </c>
+      <c r="O88">
+        <v>-91.98413038383997</v>
+      </c>
+      <c r="P88">
+        <v>-276.83756321616</v>
+      </c>
+      <c r="Q88">
+        <v>-111.03756321616</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.336683330497505</v>
+      </c>
+      <c r="T88">
+        <v>5.036713336575646</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.09509571721447581</v>
+      </c>
+      <c r="W88">
+        <v>0.2160911427291832</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3812979840195503</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2349740490167483</v>
+      </c>
+      <c r="C89">
+        <v>-1439.554229770184</v>
+      </c>
+      <c r="D89">
+        <v>737.3947702298157</v>
+      </c>
+      <c r="E89">
+        <v>1026.149</v>
+      </c>
+      <c r="F89">
+        <v>2525.349</v>
+      </c>
+      <c r="G89">
+        <v>348.4</v>
+      </c>
+      <c r="H89">
+        <v>1403.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>393.1</v>
+      </c>
+      <c r="K89">
+        <v>165.8</v>
+      </c>
+      <c r="L89">
+        <v>227.3</v>
+      </c>
+      <c r="M89">
+        <v>603.0533412</v>
+      </c>
+      <c r="N89">
+        <v>-375.7533412</v>
+      </c>
+      <c r="O89">
+        <v>-93.71288329527998</v>
+      </c>
+      <c r="P89">
+        <v>-282.04045790472</v>
+      </c>
+      <c r="Q89">
+        <v>-116.24045790472</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.359597432843467</v>
+      </c>
+      <c r="T89">
+        <v>5.424152824004542</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.09400266299361976</v>
+      </c>
+      <c r="W89">
+        <v>0.2163521640771236</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3769152485710496</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2369740490167483</v>
+      </c>
+      <c r="C90">
+        <v>-1475.148721132662</v>
+      </c>
+      <c r="D90">
+        <v>730.8272788673377</v>
+      </c>
+      <c r="E90">
+        <v>1055.176</v>
+      </c>
+      <c r="F90">
+        <v>2554.376</v>
+      </c>
+      <c r="G90">
+        <v>348.4</v>
+      </c>
+      <c r="H90">
+        <v>1403.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>393.1</v>
+      </c>
+      <c r="K90">
+        <v>165.8</v>
+      </c>
+      <c r="L90">
+        <v>227.3</v>
+      </c>
+      <c r="M90">
+        <v>609.9849888</v>
+      </c>
+      <c r="N90">
+        <v>-382.6849888</v>
+      </c>
+      <c r="O90">
+        <v>-95.44163620671998</v>
+      </c>
+      <c r="P90">
+        <v>-287.24335259328</v>
+      </c>
+      <c r="Q90">
+        <v>-121.44335259328</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3863305522470893</v>
+      </c>
+      <c r="T90">
+        <v>5.876165559338255</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.09293445091414682</v>
+      </c>
+      <c r="W90">
+        <v>0.2166072531217018</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3726321207463786</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2389740490167483</v>
+      </c>
+      <c r="C91">
+        <v>-1510.627260530845</v>
+      </c>
+      <c r="D91">
+        <v>724.3757394691543</v>
+      </c>
+      <c r="E91">
+        <v>1084.203</v>
+      </c>
+      <c r="F91">
+        <v>2583.403</v>
+      </c>
+      <c r="G91">
+        <v>348.4</v>
+      </c>
+      <c r="H91">
+        <v>1403.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>393.1</v>
+      </c>
+      <c r="K91">
+        <v>165.8</v>
+      </c>
+      <c r="L91">
+        <v>227.3</v>
+      </c>
+      <c r="M91">
+        <v>616.9166364</v>
+      </c>
+      <c r="N91">
+        <v>-389.6166364</v>
+      </c>
+      <c r="O91">
+        <v>-97.17038911815999</v>
+      </c>
+      <c r="P91">
+        <v>-292.44624728184</v>
+      </c>
+      <c r="Q91">
+        <v>-126.64624728184</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4179242388150065</v>
+      </c>
+      <c r="T91">
+        <v>6.410362428369006</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.09189024360050471</v>
+      </c>
+      <c r="W91">
+        <v>0.2168566098281995</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3684452429851833</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2409740490167482</v>
+      </c>
+      <c r="C92">
+        <v>-1545.992891868808</v>
+      </c>
+      <c r="D92">
+        <v>718.037108131192</v>
+      </c>
+      <c r="E92">
+        <v>1113.23</v>
+      </c>
+      <c r="F92">
+        <v>2612.43</v>
+      </c>
+      <c r="G92">
+        <v>348.4</v>
+      </c>
+      <c r="H92">
+        <v>1403.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>393.1</v>
+      </c>
+      <c r="K92">
+        <v>165.8</v>
+      </c>
+      <c r="L92">
+        <v>227.3</v>
+      </c>
+      <c r="M92">
+        <v>623.848284</v>
+      </c>
+      <c r="N92">
+        <v>-396.548284</v>
+      </c>
+      <c r="O92">
+        <v>-98.89914202959999</v>
+      </c>
+      <c r="P92">
+        <v>-297.6491419704</v>
+      </c>
+      <c r="Q92">
+        <v>-131.8491419704</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4558366626965071</v>
+      </c>
+      <c r="T92">
+        <v>7.051398671205906</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.09086924089383243</v>
+      </c>
+      <c r="W92">
+        <v>0.2171004252745528</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3643514069520146</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2429740490167483</v>
+      </c>
+      <c r="C93">
+        <v>-1581.248553432413</v>
+      </c>
+      <c r="D93">
+        <v>711.8084465675867</v>
+      </c>
+      <c r="E93">
+        <v>1142.257</v>
+      </c>
+      <c r="F93">
+        <v>2641.457</v>
+      </c>
+      <c r="G93">
+        <v>348.4</v>
+      </c>
+      <c r="H93">
+        <v>1403.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>393.1</v>
+      </c>
+      <c r="K93">
+        <v>165.8</v>
+      </c>
+      <c r="L93">
+        <v>227.3</v>
+      </c>
+      <c r="M93">
+        <v>630.7799316000001</v>
+      </c>
+      <c r="N93">
+        <v>-403.4799316</v>
+      </c>
+      <c r="O93">
+        <v>-100.62789494104</v>
+      </c>
+      <c r="P93">
+        <v>-302.8520366589601</v>
+      </c>
+      <c r="Q93">
+        <v>-137.05203665896</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5021740696627858</v>
+      </c>
+      <c r="T93">
+        <v>7.834887412451008</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.08987067780708702</v>
+      </c>
+      <c r="W93">
+        <v>0.2173388821396676</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3603475453371573</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2449740490167482</v>
+      </c>
+      <c r="C94">
+        <v>-1616.397082430882</v>
+      </c>
+      <c r="D94">
+        <v>705.6869175691181</v>
+      </c>
+      <c r="E94">
+        <v>1171.284</v>
+      </c>
+      <c r="F94">
+        <v>2670.484</v>
+      </c>
+      <c r="G94">
+        <v>348.4</v>
+      </c>
+      <c r="H94">
+        <v>1403.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>393.1</v>
+      </c>
+      <c r="K94">
+        <v>165.8</v>
+      </c>
+      <c r="L94">
+        <v>227.3</v>
+      </c>
+      <c r="M94">
+        <v>637.7115792</v>
+      </c>
+      <c r="N94">
+        <v>-410.4115791999999</v>
+      </c>
+      <c r="O94">
+        <v>-102.35664785248</v>
+      </c>
+      <c r="P94">
+        <v>-308.05493134752</v>
+      </c>
+      <c r="Q94">
+        <v>-142.25493134752</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5600958283706341</v>
+      </c>
+      <c r="T94">
+        <v>8.814248339007387</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.08889382261353174</v>
+      </c>
+      <c r="W94">
+        <v>0.2175721551598886</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3564307241921882</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2469740490167483</v>
+      </c>
+      <c r="C95">
+        <v>-1651.441219306012</v>
+      </c>
+      <c r="D95">
+        <v>699.6697806939884</v>
+      </c>
+      <c r="E95">
+        <v>1200.311</v>
+      </c>
+      <c r="F95">
+        <v>2699.511</v>
+      </c>
+      <c r="G95">
+        <v>348.4</v>
+      </c>
+      <c r="H95">
+        <v>1403.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>393.1</v>
+      </c>
+      <c r="K95">
+        <v>165.8</v>
+      </c>
+      <c r="L95">
+        <v>227.3</v>
+      </c>
+      <c r="M95">
+        <v>644.6432268</v>
+      </c>
+      <c r="N95">
+        <v>-417.3432268</v>
+      </c>
+      <c r="O95">
+        <v>-104.08540076392</v>
+      </c>
+      <c r="P95">
+        <v>-313.25782603608</v>
+      </c>
+      <c r="Q95">
+        <v>-147.45782603608</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6345666609950107</v>
+      </c>
+      <c r="T95">
+        <v>10.0734266731513</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.08793797505854753</v>
+      </c>
+      <c r="W95">
+        <v>0.2178004115560189</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3525981357600142</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2489740490167482</v>
+      </c>
+      <c r="C96">
+        <v>-1686.3836118228</v>
+      </c>
+      <c r="D96">
+        <v>693.7543881772001</v>
+      </c>
+      <c r="E96">
+        <v>1229.338</v>
+      </c>
+      <c r="F96">
+        <v>2728.538</v>
+      </c>
+      <c r="G96">
+        <v>348.4</v>
+      </c>
+      <c r="H96">
+        <v>1403.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>393.1</v>
+      </c>
+      <c r="K96">
+        <v>165.8</v>
+      </c>
+      <c r="L96">
+        <v>227.3</v>
+      </c>
+      <c r="M96">
+        <v>651.5748744</v>
+      </c>
+      <c r="N96">
+        <v>-424.2748744</v>
+      </c>
+      <c r="O96">
+        <v>-105.81415367536</v>
+      </c>
+      <c r="P96">
+        <v>-318.46072072464</v>
+      </c>
+      <c r="Q96">
+        <v>-152.66072072464</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.733861104494179</v>
+      </c>
+      <c r="T96">
+        <v>11.75233111867652</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.08700246468558426</v>
+      </c>
+      <c r="W96">
+        <v>0.2180238114330825</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3488470917625672</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2509740490167482</v>
+      </c>
+      <c r="C97">
+        <v>-1721.226818954305</v>
+      </c>
+      <c r="D97">
+        <v>687.938181045695</v>
+      </c>
+      <c r="E97">
+        <v>1258.365</v>
+      </c>
+      <c r="F97">
+        <v>2757.565</v>
+      </c>
+      <c r="G97">
+        <v>348.4</v>
+      </c>
+      <c r="H97">
+        <v>1403.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>393.1</v>
+      </c>
+      <c r="K97">
+        <v>165.8</v>
+      </c>
+      <c r="L97">
+        <v>227.3</v>
+      </c>
+      <c r="M97">
+        <v>658.506522</v>
+      </c>
+      <c r="N97">
+        <v>-431.206522</v>
+      </c>
+      <c r="O97">
+        <v>-107.5429065868</v>
+      </c>
+      <c r="P97">
+        <v>-323.6636154132</v>
+      </c>
+      <c r="Q97">
+        <v>-157.8636154132</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.8728733253930154</v>
+      </c>
+      <c r="T97">
+        <v>14.10279734241183</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.08608664926784125</v>
+      </c>
+      <c r="W97">
+        <v>0.2182425081548395</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3451750171124349</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2529740490167482</v>
+      </c>
+      <c r="C98">
+        <v>-1755.973314572709</v>
+      </c>
+      <c r="D98">
+        <v>682.2186854272908</v>
+      </c>
+      <c r="E98">
+        <v>1287.392</v>
+      </c>
+      <c r="F98">
+        <v>2786.592</v>
+      </c>
+      <c r="G98">
+        <v>348.4</v>
+      </c>
+      <c r="H98">
+        <v>1403.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>393.1</v>
+      </c>
+      <c r="K98">
+        <v>165.8</v>
+      </c>
+      <c r="L98">
+        <v>227.3</v>
+      </c>
+      <c r="M98">
+        <v>665.4381695999999</v>
+      </c>
+      <c r="N98">
+        <v>-438.1381695999999</v>
+      </c>
+      <c r="O98">
+        <v>-109.27165949824</v>
+      </c>
+      <c r="P98">
+        <v>-328.86651010176</v>
+      </c>
+      <c r="Q98">
+        <v>-163.0665101017599</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.081391656741267</v>
+      </c>
+      <c r="T98">
+        <v>17.62849667801475</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.08518991333796792</v>
+      </c>
+      <c r="W98">
+        <v>0.2184566486948933</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.3415794440175137</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2549740490167482</v>
+      </c>
+      <c r="C99">
+        <v>-1790.625490957781</v>
+      </c>
+      <c r="D99">
+        <v>676.593509042219</v>
+      </c>
+      <c r="E99">
+        <v>1316.419</v>
+      </c>
+      <c r="F99">
+        <v>2815.619</v>
+      </c>
+      <c r="G99">
+        <v>348.4</v>
+      </c>
+      <c r="H99">
+        <v>1403.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>393.1</v>
+      </c>
+      <c r="K99">
+        <v>165.8</v>
+      </c>
+      <c r="L99">
+        <v>227.3</v>
+      </c>
+      <c r="M99">
+        <v>672.3698171999999</v>
+      </c>
+      <c r="N99">
+        <v>-445.0698171999999</v>
+      </c>
+      <c r="O99">
+        <v>-111.00041240968</v>
+      </c>
+      <c r="P99">
+        <v>-334.0694047903199</v>
+      </c>
+      <c r="Q99">
+        <v>-168.2694047903199</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.428922208988356</v>
+      </c>
+      <c r="T99">
+        <v>23.504662237353</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.08431166680871052</v>
+      </c>
+      <c r="W99">
+        <v>0.2186663739660799</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3380580064503229</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2569740490167483</v>
+      </c>
+      <c r="C100">
+        <v>-1825.185662133183</v>
+      </c>
+      <c r="D100">
+        <v>671.060337866817</v>
+      </c>
+      <c r="E100">
+        <v>1345.446</v>
+      </c>
+      <c r="F100">
+        <v>2844.646</v>
+      </c>
+      <c r="G100">
+        <v>348.4</v>
+      </c>
+      <c r="H100">
+        <v>1403.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>393.1</v>
+      </c>
+      <c r="K100">
+        <v>165.8</v>
+      </c>
+      <c r="L100">
+        <v>227.3</v>
+      </c>
+      <c r="M100">
+        <v>679.3014648</v>
+      </c>
+      <c r="N100">
+        <v>-452.0014648</v>
+      </c>
+      <c r="O100">
+        <v>-112.72916532112</v>
+      </c>
+      <c r="P100">
+        <v>-339.27229947888</v>
+      </c>
+      <c r="Q100">
+        <v>-173.47229947888</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.123983313482534</v>
+      </c>
+      <c r="T100">
+        <v>35.2569933560295</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.08345134367800938</v>
+      </c>
+      <c r="W100">
+        <v>0.2188718191296914</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3346084349559318</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2589740490167483</v>
+      </c>
+      <c r="C101">
+        <v>-1859.6560670404</v>
+      </c>
+      <c r="D101">
+        <v>665.6169329596001</v>
+      </c>
+      <c r="E101">
+        <v>1374.473</v>
+      </c>
+      <c r="F101">
+        <v>2873.673</v>
+      </c>
+      <c r="G101">
+        <v>348.4</v>
+      </c>
+      <c r="H101">
+        <v>1403.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>393.1</v>
+      </c>
+      <c r="K101">
+        <v>165.8</v>
+      </c>
+      <c r="L101">
+        <v>227.3</v>
+      </c>
+      <c r="M101">
+        <v>686.2331124</v>
+      </c>
+      <c r="N101">
+        <v>-458.9331124</v>
+      </c>
+      <c r="O101">
+        <v>-114.45791823256</v>
+      </c>
+      <c r="P101">
+        <v>-344.47519416744</v>
+      </c>
+      <c r="Q101">
+        <v>-178.67519416744</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.209166626965067</v>
+      </c>
+      <c r="T101">
+        <v>70.51398671205899</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.08260840081257495</v>
+      </c>
+      <c r="W101">
+        <v>0.2190731138859571</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3312285517745588</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/luxembourg/luxembourg_air_transport.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_air_transport.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08062267324884481</v>
+        <v>0.08045537730176218</v>
       </c>
       <c r="C2">
-        <v>4073.449135832363</v>
+        <v>4038.193042268085</v>
       </c>
       <c r="D2">
-        <v>3562.549135832363</v>
+        <v>3569.729042268085</v>
       </c>
       <c r="E2">
-        <v>-1239.9</v>
+        <v>-1197.464</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>42.43600000000001</v>
       </c>
       <c r="G2">
         <v>510.9</v>
@@ -1445,28 +1445,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.1345308</v>
       </c>
       <c r="N2">
-        <v>471.6666666666667</v>
+        <v>469.5321358666667</v>
       </c>
       <c r="O2">
-        <v>117.6336666666667</v>
+        <v>117.1013146851467</v>
       </c>
       <c r="P2">
-        <v>354.033</v>
+        <v>352.43082118152</v>
       </c>
       <c r="Q2">
-        <v>516.0329999999999</v>
+        <v>514.4308211815199</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08062267324884481</v>
+        <v>0.08088669242602241</v>
       </c>
       <c r="T2">
-        <v>0.8042187817285175</v>
+        <v>0.8103162223099863</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>220.9697169357625</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08045537730176218</v>
+        <v>0.08028808135467956</v>
       </c>
       <c r="C3">
-        <v>4038.193042268085</v>
+        <v>4002.965947692715</v>
       </c>
       <c r="D3">
-        <v>3569.729042268085</v>
+        <v>3576.937947692715</v>
       </c>
       <c r="E3">
-        <v>-1197.464</v>
+        <v>-1155.028</v>
       </c>
       <c r="F3">
-        <v>42.43600000000001</v>
+        <v>84.87200000000001</v>
       </c>
       <c r="G3">
         <v>510.9</v>
@@ -1527,28 +1527,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M3">
-        <v>2.1345308</v>
+        <v>4.269061600000001</v>
       </c>
       <c r="N3">
-        <v>469.5321358666667</v>
+        <v>467.3976050666667</v>
       </c>
       <c r="O3">
-        <v>117.1013146851467</v>
+        <v>116.5689627036267</v>
       </c>
       <c r="P3">
-        <v>352.43082118152</v>
+        <v>350.82864236304</v>
       </c>
       <c r="Q3">
-        <v>514.4308211815199</v>
+        <v>512.82864236304</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08088669242602241</v>
+        <v>0.08115609974967303</v>
       </c>
       <c r="T3">
-        <v>0.8103162223099863</v>
+        <v>0.8165381004543425</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>220.9697169357625</v>
+        <v>110.4848584678812</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08028808135467956</v>
+        <v>0.08012078540759694</v>
       </c>
       <c r="C4">
-        <v>4002.965947692715</v>
+        <v>3967.76802814818</v>
       </c>
       <c r="D4">
-        <v>3576.937947692715</v>
+        <v>3584.17602814818</v>
       </c>
       <c r="E4">
-        <v>-1155.028</v>
+        <v>-1112.592</v>
       </c>
       <c r="F4">
-        <v>84.87200000000001</v>
+        <v>127.308</v>
       </c>
       <c r="G4">
         <v>510.9</v>
@@ -1609,28 +1609,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M4">
-        <v>4.269061600000001</v>
+        <v>6.4035924</v>
       </c>
       <c r="N4">
-        <v>467.3976050666667</v>
+        <v>465.2630742666667</v>
       </c>
       <c r="O4">
-        <v>116.5689627036267</v>
+        <v>116.0366107221067</v>
       </c>
       <c r="P4">
-        <v>350.82864236304</v>
+        <v>349.22646354456</v>
       </c>
       <c r="Q4">
-        <v>512.82864236304</v>
+        <v>511.22646354456</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08115609974967303</v>
+        <v>0.08143106186350201</v>
       </c>
       <c r="T4">
-        <v>0.8165381004543425</v>
+        <v>0.8228882647460047</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>110.4848584678812</v>
+        <v>73.65657231192084</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08012078540759694</v>
+        <v>0.07995348946051434</v>
       </c>
       <c r="C5">
-        <v>3967.76802814818</v>
+        <v>3932.599461104207</v>
       </c>
       <c r="D5">
-        <v>3584.17602814818</v>
+        <v>3591.443461104207</v>
       </c>
       <c r="E5">
-        <v>-1112.592</v>
+        <v>-1070.156</v>
       </c>
       <c r="F5">
-        <v>127.308</v>
+        <v>169.744</v>
       </c>
       <c r="G5">
         <v>510.9</v>
@@ -1691,28 +1691,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M5">
-        <v>6.4035924</v>
+        <v>8.538123200000001</v>
       </c>
       <c r="N5">
-        <v>465.2630742666667</v>
+        <v>463.1285434666667</v>
       </c>
       <c r="O5">
-        <v>116.0366107221067</v>
+        <v>115.5042587405867</v>
       </c>
       <c r="P5">
-        <v>349.22646354456</v>
+        <v>347.62428472608</v>
       </c>
       <c r="Q5">
-        <v>511.22646354456</v>
+        <v>509.6242847260799</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08143106186350201</v>
+        <v>0.08171175235470243</v>
       </c>
       <c r="T5">
-        <v>0.8228882647460047</v>
+        <v>0.8293707241270768</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>73.65657231192084</v>
+        <v>55.24242923394061</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07995348946051434</v>
+        <v>0.07978619351343171</v>
       </c>
       <c r="C6">
-        <v>3932.599461104207</v>
+        <v>3897.46042547283</v>
       </c>
       <c r="D6">
-        <v>3591.443461104207</v>
+        <v>3598.740425472829</v>
       </c>
       <c r="E6">
-        <v>-1070.156</v>
+        <v>-1027.72</v>
       </c>
       <c r="F6">
-        <v>169.744</v>
+        <v>212.18</v>
       </c>
       <c r="G6">
         <v>510.9</v>
@@ -1773,28 +1773,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M6">
-        <v>8.538123200000001</v>
+        <v>10.672654</v>
       </c>
       <c r="N6">
-        <v>463.1285434666667</v>
+        <v>460.9940126666667</v>
       </c>
       <c r="O6">
-        <v>115.5042587405867</v>
+        <v>114.9719067590667</v>
       </c>
       <c r="P6">
-        <v>347.62428472608</v>
+        <v>346.0221059076</v>
       </c>
       <c r="Q6">
-        <v>509.6242847260799</v>
+        <v>508.0221059076</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08171175235470243</v>
+        <v>0.08199835211940179</v>
       </c>
       <c r="T6">
-        <v>0.8293707241270768</v>
+        <v>0.835989656337224</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>55.24242923394061</v>
+        <v>44.19394338715249</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07978619351343171</v>
+        <v>0.07961889756634909</v>
       </c>
       <c r="C7">
-        <v>3897.46042547283</v>
+        <v>3862.351101623069</v>
       </c>
       <c r="D7">
-        <v>3598.740425472829</v>
+        <v>3606.067101623069</v>
       </c>
       <c r="E7">
-        <v>-1027.72</v>
+        <v>-985.2840000000001</v>
       </c>
       <c r="F7">
-        <v>212.18</v>
+        <v>254.616</v>
       </c>
       <c r="G7">
         <v>510.9</v>
@@ -1855,28 +1855,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M7">
-        <v>10.672654</v>
+        <v>12.8071848</v>
       </c>
       <c r="N7">
-        <v>460.9940126666667</v>
+        <v>458.8594818666667</v>
       </c>
       <c r="O7">
-        <v>114.9719067590667</v>
+        <v>114.4395547775467</v>
       </c>
       <c r="P7">
-        <v>346.0221059076</v>
+        <v>344.41992708912</v>
       </c>
       <c r="Q7">
-        <v>508.0221059076</v>
+        <v>506.4199270891199</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08199835211940179</v>
+        <v>0.0822910497514352</v>
       </c>
       <c r="T7">
-        <v>0.835989656337224</v>
+        <v>0.8427494168922679</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.19394338715249</v>
+        <v>36.82828615596041</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07961889756634909</v>
+        <v>0.07945160161926648</v>
       </c>
       <c r="C8">
-        <v>3862.351101623069</v>
+        <v>3827.271671395795</v>
       </c>
       <c r="D8">
-        <v>3606.067101623069</v>
+        <v>3613.423671395795</v>
       </c>
       <c r="E8">
-        <v>-985.2840000000001</v>
+        <v>-942.8480000000001</v>
       </c>
       <c r="F8">
-        <v>254.616</v>
+        <v>297.052</v>
       </c>
       <c r="G8">
         <v>510.9</v>
@@ -1937,28 +1937,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M8">
-        <v>12.8071848</v>
+        <v>14.9417156</v>
       </c>
       <c r="N8">
-        <v>458.8594818666667</v>
+        <v>456.7249510666667</v>
       </c>
       <c r="O8">
-        <v>114.4395547775467</v>
+        <v>113.9072027960267</v>
       </c>
       <c r="P8">
-        <v>344.41992708912</v>
+        <v>342.81774827064</v>
       </c>
       <c r="Q8">
-        <v>506.4199270891199</v>
+        <v>504.8177482706399</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0822910497514352</v>
+        <v>0.08259004195620051</v>
       </c>
       <c r="T8">
-        <v>0.8427494168922679</v>
+        <v>0.8496545486420441</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.82828615596041</v>
+        <v>31.56710241939464</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07945160161926647</v>
+        <v>0.07928430567218386</v>
       </c>
       <c r="C9">
-        <v>3827.271671395796</v>
+        <v>3792.222318118776</v>
       </c>
       <c r="D9">
-        <v>3613.423671395796</v>
+        <v>3620.810318118776</v>
       </c>
       <c r="E9">
-        <v>-942.848</v>
+        <v>-900.412</v>
       </c>
       <c r="F9">
-        <v>297.0520000000001</v>
+        <v>339.4880000000001</v>
       </c>
       <c r="G9">
         <v>510.9</v>
@@ -2019,28 +2019,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M9">
-        <v>14.9417156</v>
+        <v>17.0762464</v>
       </c>
       <c r="N9">
-        <v>456.7249510666667</v>
+        <v>454.5904202666667</v>
       </c>
       <c r="O9">
-        <v>113.9072027960267</v>
+        <v>113.3748508145067</v>
       </c>
       <c r="P9">
-        <v>342.81774827064</v>
+        <v>341.21556945216</v>
       </c>
       <c r="Q9">
-        <v>504.8177482706399</v>
+        <v>503.21556945216</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08259004195620051</v>
+        <v>0.08289553399150419</v>
       </c>
       <c r="T9">
-        <v>0.8496545486420441</v>
+        <v>0.8567097919515979</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.56710241939464</v>
+        <v>27.62121461697031</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07928430567218386</v>
+        <v>0.07911700972510126</v>
       </c>
       <c r="C10">
-        <v>3792.222318118776</v>
+        <v>3757.203226621897</v>
       </c>
       <c r="D10">
-        <v>3620.810318118776</v>
+        <v>3628.227226621897</v>
       </c>
       <c r="E10">
-        <v>-900.412</v>
+        <v>-857.9760000000001</v>
       </c>
       <c r="F10">
-        <v>339.4880000000001</v>
+        <v>381.924</v>
       </c>
       <c r="G10">
         <v>510.9</v>
@@ -2101,28 +2101,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M10">
-        <v>17.0762464</v>
+        <v>19.2107772</v>
       </c>
       <c r="N10">
-        <v>454.5904202666667</v>
+        <v>452.4558894666667</v>
       </c>
       <c r="O10">
-        <v>113.3748508145067</v>
+        <v>112.8424988329867</v>
       </c>
       <c r="P10">
-        <v>341.21556945216</v>
+        <v>339.61339063368</v>
       </c>
       <c r="Q10">
-        <v>503.21556945216</v>
+        <v>501.61339063368</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08289553399150419</v>
+        <v>0.0832077401374739</v>
       </c>
       <c r="T10">
-        <v>0.8567097919515979</v>
+        <v>0.8639200955536694</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.62121461697031</v>
+        <v>24.55219077064028</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07911700972510126</v>
+        <v>0.07894971377801863</v>
       </c>
       <c r="C11">
-        <v>3757.203226621897</v>
+        <v>3722.214583252586</v>
       </c>
       <c r="D11">
-        <v>3628.227226621897</v>
+        <v>3635.674583252586</v>
       </c>
       <c r="E11">
-        <v>-857.9760000000001</v>
+        <v>-815.5400000000001</v>
       </c>
       <c r="F11">
-        <v>381.924</v>
+        <v>424.36</v>
       </c>
       <c r="G11">
         <v>510.9</v>
@@ -2183,28 +2183,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M11">
-        <v>19.2107772</v>
+        <v>21.345308</v>
       </c>
       <c r="N11">
-        <v>452.4558894666667</v>
+        <v>450.3213586666667</v>
       </c>
       <c r="O11">
-        <v>112.8424988329867</v>
+        <v>112.3101468514667</v>
       </c>
       <c r="P11">
-        <v>339.61339063368</v>
+        <v>338.0112118152</v>
       </c>
       <c r="Q11">
-        <v>501.61339063368</v>
+        <v>500.0112118151999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0832077401374739</v>
+        <v>0.08352688419779847</v>
       </c>
       <c r="T11">
-        <v>0.8639200955536694</v>
+        <v>0.8712906281246757</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.55219077064028</v>
+        <v>22.09697169357625</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07894971377801863</v>
+        <v>0.07878241783093601</v>
       </c>
       <c r="C12">
-        <v>3722.214583252586</v>
+        <v>3687.256575891414</v>
       </c>
       <c r="D12">
-        <v>3635.674583252586</v>
+        <v>3643.152575891414</v>
       </c>
       <c r="E12">
-        <v>-815.54</v>
+        <v>-773.104</v>
       </c>
       <c r="F12">
-        <v>424.3600000000001</v>
+        <v>466.796</v>
       </c>
       <c r="G12">
         <v>510.9</v>
@@ -2265,28 +2265,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M12">
-        <v>21.345308</v>
+        <v>23.4798388</v>
       </c>
       <c r="N12">
-        <v>450.3213586666667</v>
+        <v>448.1868278666667</v>
       </c>
       <c r="O12">
-        <v>112.3101468514667</v>
+        <v>111.7777948699467</v>
       </c>
       <c r="P12">
-        <v>338.0112118152</v>
+        <v>336.40903299672</v>
       </c>
       <c r="Q12">
-        <v>500.0112118151999</v>
+        <v>498.40903299672</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08352688419779847</v>
+        <v>0.08385320003475955</v>
       </c>
       <c r="T12">
-        <v>0.8712906281246757</v>
+        <v>0.878826790641098</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.09697169357625</v>
+        <v>20.08815608506932</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07878241783093601</v>
+        <v>0.07861512188385336</v>
       </c>
       <c r="C13">
-        <v>3687.256575891414</v>
+        <v>3652.329393967902</v>
       </c>
       <c r="D13">
-        <v>3643.152575891414</v>
+        <v>3650.661393967902</v>
       </c>
       <c r="E13">
-        <v>-773.104</v>
+        <v>-730.6680000000001</v>
       </c>
       <c r="F13">
-        <v>466.796</v>
+        <v>509.232</v>
       </c>
       <c r="G13">
         <v>510.9</v>
@@ -2347,28 +2347,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M13">
-        <v>23.4798388</v>
+        <v>25.6143696</v>
       </c>
       <c r="N13">
-        <v>448.1868278666667</v>
+        <v>446.0522970666667</v>
       </c>
       <c r="O13">
-        <v>111.7777948699467</v>
+        <v>111.2454428884267</v>
       </c>
       <c r="P13">
-        <v>336.40903299672</v>
+        <v>334.80685417824</v>
       </c>
       <c r="Q13">
-        <v>498.40903299672</v>
+        <v>496.80685417824</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08385320003475955</v>
+        <v>0.08418693214074247</v>
       </c>
       <c r="T13">
-        <v>0.878826790641098</v>
+        <v>0.8865342295783482</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.08815608506932</v>
+        <v>18.41414307798021</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07861512188385336</v>
+        <v>0.07844782593677074</v>
       </c>
       <c r="C14">
-        <v>3652.329393967902</v>
+        <v>3617.433228476503</v>
       </c>
       <c r="D14">
-        <v>3650.661393967902</v>
+        <v>3658.201228476503</v>
       </c>
       <c r="E14">
-        <v>-730.6680000000001</v>
+        <v>-688.232</v>
       </c>
       <c r="F14">
-        <v>509.232</v>
+        <v>551.6680000000001</v>
       </c>
       <c r="G14">
         <v>510.9</v>
@@ -2429,28 +2429,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M14">
-        <v>25.6143696</v>
+        <v>27.7489004</v>
       </c>
       <c r="N14">
-        <v>446.0522970666667</v>
+        <v>443.9177662666667</v>
       </c>
       <c r="O14">
-        <v>111.2454428884267</v>
+        <v>110.7130909069067</v>
       </c>
       <c r="P14">
-        <v>334.80685417824</v>
+        <v>333.20467535976</v>
       </c>
       <c r="Q14">
-        <v>496.80685417824</v>
+        <v>495.20467535976</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08418693214074247</v>
+        <v>0.08452833624916178</v>
       </c>
       <c r="T14">
-        <v>0.8865342295783482</v>
+        <v>0.8944188510199028</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.41414307798021</v>
+        <v>16.99767053352019</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07844782593677074</v>
+        <v>0.07828052998968812</v>
       </c>
       <c r="C15">
-        <v>3617.433228476503</v>
+        <v>3582.568271992814</v>
       </c>
       <c r="D15">
-        <v>3658.201228476503</v>
+        <v>3665.772271992814</v>
       </c>
       <c r="E15">
-        <v>-688.232</v>
+        <v>-645.7959999999999</v>
       </c>
       <c r="F15">
-        <v>551.6680000000001</v>
+        <v>594.1040000000002</v>
       </c>
       <c r="G15">
         <v>510.9</v>
@@ -2511,28 +2511,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M15">
-        <v>27.7489004</v>
+        <v>29.88343120000001</v>
       </c>
       <c r="N15">
-        <v>443.9177662666667</v>
+        <v>441.7832354666667</v>
       </c>
       <c r="O15">
-        <v>110.7130909069067</v>
+        <v>110.1807389253867</v>
       </c>
       <c r="P15">
-        <v>333.20467535976</v>
+        <v>331.60249654128</v>
       </c>
       <c r="Q15">
-        <v>495.20467535976</v>
+        <v>493.6024965412799</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08452833624916178</v>
+        <v>0.08487767998800946</v>
       </c>
       <c r="T15">
-        <v>0.8944188510199028</v>
+        <v>0.902486835750796</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.99767053352019</v>
+        <v>15.78355120969732</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07828052998968812</v>
+        <v>0.07811323404260552</v>
       </c>
       <c r="C16">
-        <v>3582.568271992814</v>
+        <v>3547.734718689957</v>
       </c>
       <c r="D16">
-        <v>3665.772271992814</v>
+        <v>3673.374718689957</v>
       </c>
       <c r="E16">
-        <v>-645.7959999999999</v>
+        <v>-603.3599999999999</v>
       </c>
       <c r="F16">
-        <v>594.1040000000002</v>
+        <v>636.5400000000002</v>
       </c>
       <c r="G16">
         <v>510.9</v>
@@ -2593,28 +2593,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M16">
-        <v>29.88343120000001</v>
+        <v>32.01796200000001</v>
       </c>
       <c r="N16">
-        <v>441.7832354666667</v>
+        <v>439.6487046666667</v>
       </c>
       <c r="O16">
-        <v>110.1807389253867</v>
+        <v>109.6483869438667</v>
       </c>
       <c r="P16">
-        <v>331.60249654128</v>
+        <v>330.0003177228</v>
       </c>
       <c r="Q16">
-        <v>493.6024965412799</v>
+        <v>492.0003177227999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08487767998800946</v>
+        <v>0.08523524357953591</v>
       </c>
       <c r="T16">
-        <v>0.902486835750796</v>
+        <v>0.9107446554165337</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.78355120969732</v>
+        <v>14.73131446238416</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07811323404260552</v>
+        <v>0.07794593809552289</v>
       </c>
       <c r="C17">
-        <v>3547.734718689957</v>
+        <v>3512.932764355188</v>
       </c>
       <c r="D17">
-        <v>3673.374718689957</v>
+        <v>3681.008764355189</v>
       </c>
       <c r="E17">
-        <v>-603.36</v>
+        <v>-560.924</v>
       </c>
       <c r="F17">
-        <v>636.5400000000001</v>
+        <v>678.9760000000001</v>
       </c>
       <c r="G17">
         <v>510.9</v>
@@ -2675,28 +2675,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M17">
-        <v>32.017962</v>
+        <v>34.1524928</v>
       </c>
       <c r="N17">
-        <v>439.6487046666667</v>
+        <v>437.5141738666667</v>
       </c>
       <c r="O17">
-        <v>109.6483869438667</v>
+        <v>109.1160349623467</v>
       </c>
       <c r="P17">
-        <v>330.0003177228</v>
+        <v>328.39813890432</v>
       </c>
       <c r="Q17">
-        <v>492.0003177227999</v>
+        <v>490.39813890432</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08523524357953591</v>
+        <v>0.08560132058990821</v>
       </c>
       <c r="T17">
-        <v>0.9107446554165337</v>
+        <v>0.9191990898362175</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.73131446238416</v>
+        <v>13.81060730848515</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07794593809552289</v>
+        <v>0.07777864214844027</v>
       </c>
       <c r="C18">
-        <v>3512.932764355188</v>
+        <v>3478.162606406697</v>
       </c>
       <c r="D18">
-        <v>3681.008764355189</v>
+        <v>3688.674606406697</v>
       </c>
       <c r="E18">
-        <v>-560.924</v>
+        <v>-518.4879999999999</v>
       </c>
       <c r="F18">
-        <v>678.9760000000001</v>
+        <v>721.4120000000001</v>
       </c>
       <c r="G18">
         <v>510.9</v>
@@ -2757,28 +2757,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M18">
-        <v>34.1524928</v>
+        <v>36.2870236</v>
       </c>
       <c r="N18">
-        <v>437.5141738666667</v>
+        <v>435.3796430666667</v>
       </c>
       <c r="O18">
-        <v>109.1160349623467</v>
+        <v>108.5836829808267</v>
       </c>
       <c r="P18">
-        <v>328.39813890432</v>
+        <v>326.79596008584</v>
       </c>
       <c r="Q18">
-        <v>490.39813890432</v>
+        <v>488.79596008584</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08560132058990821</v>
+        <v>0.08597621873306058</v>
       </c>
       <c r="T18">
-        <v>0.9191990898362175</v>
+        <v>0.927857245567219</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.81060730848515</v>
+        <v>12.99821864328015</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07777864214844027</v>
+        <v>0.07781400820135766</v>
       </c>
       <c r="C19">
-        <v>3478.162606406697</v>
+        <v>3434.103401376162</v>
       </c>
       <c r="D19">
-        <v>3688.674606406697</v>
+        <v>3687.051401376162</v>
       </c>
       <c r="E19">
-        <v>-518.4879999999999</v>
+        <v>-476.0519999999999</v>
       </c>
       <c r="F19">
-        <v>721.4120000000001</v>
+        <v>763.8480000000002</v>
       </c>
       <c r="G19">
         <v>510.9</v>
@@ -2839,45 +2839,45 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M19">
-        <v>36.2870236</v>
+        <v>39.56732640000001</v>
       </c>
       <c r="N19">
-        <v>435.3796430666667</v>
+        <v>432.0993402666667</v>
       </c>
       <c r="O19">
-        <v>108.5836829808267</v>
+        <v>107.7655754625067</v>
       </c>
       <c r="P19">
-        <v>326.79596008584</v>
+        <v>324.33376480416</v>
       </c>
       <c r="Q19">
-        <v>488.79596008584</v>
+        <v>486.33376480416</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08597621873306058</v>
+        <v>0.086360260733363</v>
       </c>
       <c r="T19">
-        <v>0.927857245567219</v>
+        <v>0.9367265758282449</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.2494</v>
       </c>
       <c r="W19">
-        <v>0.03775517999999999</v>
+        <v>0.03888108</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>12.99821864328015</v>
+        <v>11.92060999771434</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07781400820135767</v>
+        <v>0.07765797125427505</v>
       </c>
       <c r="C20">
-        <v>3434.103401376161</v>
+        <v>3398.839844173736</v>
       </c>
       <c r="D20">
-        <v>3687.051401376161</v>
+        <v>3694.223844173736</v>
       </c>
       <c r="E20">
-        <v>-476.052</v>
+        <v>-433.616</v>
       </c>
       <c r="F20">
-        <v>763.8480000000001</v>
+        <v>806.2840000000001</v>
       </c>
       <c r="G20">
         <v>510.9</v>
@@ -2921,28 +2921,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M20">
-        <v>39.56732640000001</v>
+        <v>41.76551120000001</v>
       </c>
       <c r="N20">
-        <v>432.0993402666667</v>
+        <v>429.9011554666667</v>
       </c>
       <c r="O20">
-        <v>107.7655754625067</v>
+        <v>107.2173481733867</v>
       </c>
       <c r="P20">
-        <v>324.33376480416</v>
+        <v>322.68380729328</v>
       </c>
       <c r="Q20">
-        <v>486.33376480416</v>
+        <v>484.6838072932799</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.086360260733363</v>
+        <v>0.08675378525219141</v>
       </c>
       <c r="T20">
-        <v>0.9367265758282449</v>
+        <v>0.9458149018981851</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.92060999771434</v>
+        <v>11.29320947151885</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07765797125427505</v>
+        <v>0.07750193430719243</v>
       </c>
       <c r="C21">
-        <v>3398.839844173736</v>
+        <v>3363.604246551647</v>
       </c>
       <c r="D21">
-        <v>3694.223844173736</v>
+        <v>3701.424246551647</v>
       </c>
       <c r="E21">
-        <v>-433.616</v>
+        <v>-391.1799999999999</v>
       </c>
       <c r="F21">
-        <v>806.2840000000001</v>
+        <v>848.7200000000001</v>
       </c>
       <c r="G21">
         <v>510.9</v>
@@ -3003,28 +3003,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M21">
-        <v>41.76551120000001</v>
+        <v>43.96369600000001</v>
       </c>
       <c r="N21">
-        <v>429.9011554666667</v>
+        <v>427.7029706666667</v>
       </c>
       <c r="O21">
-        <v>107.2173481733867</v>
+        <v>106.6691208842667</v>
       </c>
       <c r="P21">
-        <v>322.68380729328</v>
+        <v>321.0338497824</v>
       </c>
       <c r="Q21">
-        <v>484.6838072932799</v>
+        <v>483.0338497824</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08675378525219141</v>
+        <v>0.08715714788399054</v>
       </c>
       <c r="T21">
-        <v>0.9458149018981851</v>
+        <v>0.9551304361198738</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.29320947151885</v>
+        <v>10.72854899794291</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07750193430719243</v>
+        <v>0.07734589736010981</v>
       </c>
       <c r="C22">
-        <v>3363.604246551647</v>
+        <v>3328.396772317013</v>
       </c>
       <c r="D22">
-        <v>3701.424246551647</v>
+        <v>3708.652772317013</v>
       </c>
       <c r="E22">
-        <v>-391.1799999999999</v>
+        <v>-348.7439999999999</v>
       </c>
       <c r="F22">
-        <v>848.7200000000001</v>
+        <v>891.1560000000002</v>
       </c>
       <c r="G22">
         <v>510.9</v>
@@ -3085,28 +3085,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M22">
-        <v>43.96369600000001</v>
+        <v>46.16188080000001</v>
       </c>
       <c r="N22">
-        <v>427.7029706666667</v>
+        <v>425.5047858666667</v>
       </c>
       <c r="O22">
-        <v>106.6691208842667</v>
+        <v>106.1208935951467</v>
       </c>
       <c r="P22">
-        <v>321.0338497824</v>
+        <v>319.38389227152</v>
       </c>
       <c r="Q22">
-        <v>483.0338497824</v>
+        <v>481.38389227152</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08715714788399054</v>
+        <v>0.08757072222798711</v>
       </c>
       <c r="T22">
-        <v>0.9551304361198738</v>
+        <v>0.9646818066509724</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.72854899794291</v>
+        <v>10.21766571232658</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07734589736010981</v>
+        <v>0.07747058481302721</v>
       </c>
       <c r="C23">
-        <v>3328.396772317013</v>
+        <v>3280.182271981889</v>
       </c>
       <c r="D23">
-        <v>3708.652772317013</v>
+        <v>3702.874271981889</v>
       </c>
       <c r="E23">
-        <v>-348.744</v>
+        <v>-306.308</v>
       </c>
       <c r="F23">
-        <v>891.1560000000001</v>
+        <v>933.5920000000001</v>
       </c>
       <c r="G23">
         <v>510.9</v>
@@ -3167,45 +3167,45 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M23">
-        <v>46.1618808</v>
+        <v>49.947172</v>
       </c>
       <c r="N23">
-        <v>425.5047858666667</v>
+        <v>421.7194946666667</v>
       </c>
       <c r="O23">
-        <v>106.1208935951467</v>
+        <v>105.1768419698667</v>
       </c>
       <c r="P23">
-        <v>319.38389227152</v>
+        <v>316.5426526968</v>
       </c>
       <c r="Q23">
-        <v>481.38389227152</v>
+        <v>478.5426526968</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08757072222798711</v>
+        <v>0.08799490104234256</v>
       </c>
       <c r="T23">
-        <v>0.9646818066509724</v>
+        <v>0.9744780841187657</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.2494</v>
       </c>
       <c r="W23">
-        <v>0.03888108</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>10.21766571232658</v>
+        <v>9.443310757747538</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07747058481302721</v>
+        <v>0.07732730806594457</v>
       </c>
       <c r="C24">
-        <v>3280.182271981889</v>
+        <v>3244.387817534825</v>
       </c>
       <c r="D24">
-        <v>3702.874271981889</v>
+        <v>3709.515817534826</v>
       </c>
       <c r="E24">
-        <v>-306.308</v>
+        <v>-263.872</v>
       </c>
       <c r="F24">
-        <v>933.5920000000001</v>
+        <v>976.0280000000001</v>
       </c>
       <c r="G24">
         <v>510.9</v>
@@ -3249,28 +3249,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M24">
-        <v>49.947172</v>
+        <v>52.21749800000001</v>
       </c>
       <c r="N24">
-        <v>421.7194946666667</v>
+        <v>419.4491686666667</v>
       </c>
       <c r="O24">
-        <v>105.1768419698667</v>
+        <v>104.6106226654667</v>
       </c>
       <c r="P24">
-        <v>316.5426526968</v>
+        <v>314.8385460012</v>
       </c>
       <c r="Q24">
-        <v>478.5426526968</v>
+        <v>476.8385460011999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08799490104234256</v>
+        <v>0.0884300974882397</v>
       </c>
       <c r="T24">
-        <v>0.9744780841187657</v>
+        <v>0.9845288103519562</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.443310757747538</v>
+        <v>9.032732029149818</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07732730806594457</v>
+        <v>0.07718403131886194</v>
       </c>
       <c r="C25">
-        <v>3244.387817534825</v>
+        <v>3208.617230701408</v>
       </c>
       <c r="D25">
-        <v>3709.515817534826</v>
+        <v>3716.181230701408</v>
       </c>
       <c r="E25">
-        <v>-263.872</v>
+        <v>-221.4359999999999</v>
       </c>
       <c r="F25">
-        <v>976.0280000000001</v>
+        <v>1018.464</v>
       </c>
       <c r="G25">
         <v>510.9</v>
@@ -3331,28 +3331,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M25">
-        <v>52.21749800000001</v>
+        <v>54.48782400000001</v>
       </c>
       <c r="N25">
-        <v>419.4491686666667</v>
+        <v>417.1788426666667</v>
       </c>
       <c r="O25">
-        <v>104.6106226654667</v>
+        <v>104.0444033610667</v>
       </c>
       <c r="P25">
-        <v>314.8385460012</v>
+        <v>313.1344393056</v>
       </c>
       <c r="Q25">
-        <v>476.8385460011999</v>
+        <v>475.1344393056</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0884300974882397</v>
+        <v>0.08887674647218677</v>
       </c>
       <c r="T25">
-        <v>0.9845288103519562</v>
+        <v>0.994844029380757</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.032732029149818</v>
+        <v>8.65636819460191</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07718403131886194</v>
+        <v>0.07704075457177934</v>
       </c>
       <c r="C26">
-        <v>3208.617230701408</v>
+        <v>3172.87064037221</v>
       </c>
       <c r="D26">
-        <v>3716.181230701408</v>
+        <v>3722.870640372211</v>
       </c>
       <c r="E26">
-        <v>-221.436</v>
+        <v>-179</v>
       </c>
       <c r="F26">
-        <v>1018.464</v>
+        <v>1060.9</v>
       </c>
       <c r="G26">
         <v>510.9</v>
@@ -3413,28 +3413,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M26">
-        <v>54.487824</v>
+        <v>56.75815</v>
       </c>
       <c r="N26">
-        <v>417.1788426666667</v>
+        <v>414.9085166666667</v>
       </c>
       <c r="O26">
-        <v>104.0444033610667</v>
+        <v>103.4781840566667</v>
       </c>
       <c r="P26">
-        <v>313.1344393056</v>
+        <v>311.43033261</v>
       </c>
       <c r="Q26">
-        <v>475.1344393056</v>
+        <v>473.4303326099999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08887674647218677</v>
+        <v>0.08933530609570578</v>
       </c>
       <c r="T26">
-        <v>0.994844029380757</v>
+        <v>1.005434320916992</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.65636819460191</v>
+        <v>8.310113466817835</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07704075457177934</v>
+        <v>0.07689747782469672</v>
       </c>
       <c r="C27">
-        <v>3172.87064037221</v>
+        <v>3137.148176367537</v>
       </c>
       <c r="D27">
-        <v>3722.870640372211</v>
+        <v>3729.584176367538</v>
       </c>
       <c r="E27">
-        <v>-179</v>
+        <v>-136.5639999999999</v>
       </c>
       <c r="F27">
-        <v>1060.9</v>
+        <v>1103.336</v>
       </c>
       <c r="G27">
         <v>510.9</v>
@@ -3495,28 +3495,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M27">
-        <v>56.75815</v>
+        <v>59.02847600000001</v>
       </c>
       <c r="N27">
-        <v>414.9085166666667</v>
+        <v>412.6381906666667</v>
       </c>
       <c r="O27">
-        <v>103.4781840566667</v>
+        <v>102.9119647522667</v>
       </c>
       <c r="P27">
-        <v>311.43033261</v>
+        <v>309.7262259144</v>
       </c>
       <c r="Q27">
-        <v>473.4303326099999</v>
+        <v>471.7262259143999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08933530609570578</v>
+        <v>0.08980625922256313</v>
       </c>
       <c r="T27">
-        <v>1.005434320916992</v>
+        <v>1.016310836548802</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.310113466817835</v>
+        <v>7.99049371809407</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07689747782469672</v>
+        <v>0.07675420107761409</v>
       </c>
       <c r="C28">
-        <v>3137.148176367537</v>
+        <v>3101.44996944581</v>
       </c>
       <c r="D28">
-        <v>3729.584176367538</v>
+        <v>3736.32196944581</v>
       </c>
       <c r="E28">
-        <v>-136.5639999999999</v>
+        <v>-94.12799999999993</v>
       </c>
       <c r="F28">
-        <v>1103.336</v>
+        <v>1145.772</v>
       </c>
       <c r="G28">
         <v>510.9</v>
@@ -3577,28 +3577,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M28">
-        <v>59.02847600000001</v>
+        <v>61.29880200000001</v>
       </c>
       <c r="N28">
-        <v>412.6381906666667</v>
+        <v>410.3678646666667</v>
       </c>
       <c r="O28">
-        <v>102.9119647522667</v>
+        <v>102.3457454478667</v>
       </c>
       <c r="P28">
-        <v>309.7262259144</v>
+        <v>308.0221192188</v>
       </c>
       <c r="Q28">
-        <v>471.7262259143999</v>
+        <v>470.0221192187999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08980625922256313</v>
+        <v>0.09029011517481383</v>
       </c>
       <c r="T28">
-        <v>1.016310836548802</v>
+        <v>1.02748533891025</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.99049371809407</v>
+        <v>7.694549506312809</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07675420107761409</v>
+        <v>0.07677905873053148</v>
       </c>
       <c r="C29">
-        <v>3101.44996944581</v>
+        <v>3057.843258021671</v>
       </c>
       <c r="D29">
-        <v>3736.32196944581</v>
+        <v>3735.151258021672</v>
       </c>
       <c r="E29">
-        <v>-94.12799999999993</v>
+        <v>-51.69199999999978</v>
       </c>
       <c r="F29">
-        <v>1145.772</v>
+        <v>1188.208</v>
       </c>
       <c r="G29">
         <v>510.9</v>
@@ -3659,45 +3659,45 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M29">
-        <v>61.29880200000001</v>
+        <v>64.51969440000002</v>
       </c>
       <c r="N29">
-        <v>410.3678646666667</v>
+        <v>407.1469722666667</v>
       </c>
       <c r="O29">
-        <v>102.3457454478667</v>
+        <v>101.5424548833067</v>
       </c>
       <c r="P29">
-        <v>308.0221192188</v>
+        <v>305.60451738336</v>
       </c>
       <c r="Q29">
-        <v>470.0221192187999</v>
+        <v>467.60451738336</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09029011517481383</v>
+        <v>0.09078741157018261</v>
       </c>
       <c r="T29">
-        <v>1.02748533891025</v>
+        <v>1.038970244115072</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.2494</v>
       </c>
       <c r="W29">
-        <v>0.04015709999999999</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.694549506312809</v>
+        <v>7.310429335614872</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07677905873053148</v>
+        <v>0.07664178678344885</v>
       </c>
       <c r="C30">
-        <v>3057.843258021671</v>
+        <v>3021.881479484743</v>
       </c>
       <c r="D30">
-        <v>3735.151258021672</v>
+        <v>3741.625479484743</v>
       </c>
       <c r="E30">
-        <v>-51.69199999999978</v>
+        <v>-9.255999999999858</v>
       </c>
       <c r="F30">
-        <v>1188.208</v>
+        <v>1230.644</v>
       </c>
       <c r="G30">
         <v>510.9</v>
@@ -3741,28 +3741,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M30">
-        <v>64.51969440000002</v>
+        <v>66.82396920000001</v>
       </c>
       <c r="N30">
-        <v>407.1469722666667</v>
+        <v>404.8426974666667</v>
       </c>
       <c r="O30">
-        <v>101.5424548833067</v>
+        <v>100.9677687481867</v>
       </c>
       <c r="P30">
-        <v>305.60451738336</v>
+        <v>303.87492871848</v>
       </c>
       <c r="Q30">
-        <v>467.60451738336</v>
+        <v>465.8749287184799</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09078741157018261</v>
+        <v>0.0912987163147167</v>
       </c>
       <c r="T30">
-        <v>1.038970244115072</v>
+        <v>1.050778667776367</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.310429335614872</v>
+        <v>7.058345565421257</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07664178678344885</v>
+        <v>0.07650451483636624</v>
       </c>
       <c r="C31">
-        <v>3021.881479484743</v>
+        <v>2985.942183744336</v>
       </c>
       <c r="D31">
-        <v>3741.625479484743</v>
+        <v>3748.122183744336</v>
       </c>
       <c r="E31">
-        <v>-9.256000000000085</v>
+        <v>33.18000000000006</v>
       </c>
       <c r="F31">
-        <v>1230.644</v>
+        <v>1273.08</v>
       </c>
       <c r="G31">
         <v>510.9</v>
@@ -3823,28 +3823,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M31">
-        <v>66.82396920000001</v>
+        <v>69.12824400000001</v>
       </c>
       <c r="N31">
-        <v>404.8426974666667</v>
+        <v>402.5384226666667</v>
       </c>
       <c r="O31">
-        <v>100.9677687481867</v>
+        <v>100.3930826130667</v>
       </c>
       <c r="P31">
-        <v>303.87492871848</v>
+        <v>302.1453400536</v>
       </c>
       <c r="Q31">
-        <v>465.8749287184799</v>
+        <v>464.1453400536</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0912987163147167</v>
+        <v>0.09182462976623748</v>
       </c>
       <c r="T31">
-        <v>1.050778667776367</v>
+        <v>1.062924474970843</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.058345565421257</v>
+        <v>6.823067379907215</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07650451483636624</v>
+        <v>0.07636724288928361</v>
       </c>
       <c r="C32">
-        <v>2985.942183744336</v>
+        <v>2950.025488116951</v>
       </c>
       <c r="D32">
-        <v>3748.122183744336</v>
+        <v>3754.641488116951</v>
       </c>
       <c r="E32">
-        <v>33.18000000000006</v>
+        <v>75.61599999999999</v>
       </c>
       <c r="F32">
-        <v>1273.08</v>
+        <v>1315.516</v>
       </c>
       <c r="G32">
         <v>510.9</v>
@@ -3905,28 +3905,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M32">
-        <v>69.12824400000001</v>
+        <v>71.43251880000001</v>
       </c>
       <c r="N32">
-        <v>402.5384226666667</v>
+        <v>400.2341478666667</v>
       </c>
       <c r="O32">
-        <v>100.3930826130667</v>
+        <v>99.81839647794666</v>
       </c>
       <c r="P32">
-        <v>302.1453400536</v>
+        <v>300.41575138872</v>
       </c>
       <c r="Q32">
-        <v>464.1453400536</v>
+        <v>462.4157513887199</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09182462976623748</v>
+        <v>0.09236578708591828</v>
       </c>
       <c r="T32">
-        <v>1.062924474970843</v>
+        <v>1.075422334547766</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.823067379907215</v>
+        <v>6.602968432168272</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07636724288928361</v>
+        <v>0.07622997094220101</v>
       </c>
       <c r="C33">
-        <v>2950.025488116951</v>
+        <v>2914.131510736729</v>
       </c>
       <c r="D33">
-        <v>3754.641488116951</v>
+        <v>3761.18351073673</v>
       </c>
       <c r="E33">
-        <v>75.61599999999999</v>
+        <v>118.0520000000001</v>
       </c>
       <c r="F33">
-        <v>1315.516</v>
+        <v>1357.952</v>
       </c>
       <c r="G33">
         <v>510.9</v>
@@ -3987,28 +3987,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M33">
-        <v>71.43251880000001</v>
+        <v>73.73679360000001</v>
       </c>
       <c r="N33">
-        <v>400.2341478666667</v>
+        <v>397.9298730666667</v>
       </c>
       <c r="O33">
-        <v>99.81839647794666</v>
+        <v>99.24371034282667</v>
       </c>
       <c r="P33">
-        <v>300.41575138872</v>
+        <v>298.68616272384</v>
       </c>
       <c r="Q33">
-        <v>462.4157513887199</v>
+        <v>460.68616272384</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09236578708591828</v>
+        <v>0.09292286079735441</v>
       </c>
       <c r="T33">
-        <v>1.075422334547766</v>
+        <v>1.088287778229894</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.602968432168272</v>
+        <v>6.396625668663013</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07622997094220101</v>
+        <v>0.07609269899511838</v>
       </c>
       <c r="C34">
-        <v>2914.131510736729</v>
+        <v>2878.260370562592</v>
       </c>
       <c r="D34">
-        <v>3761.18351073673</v>
+        <v>3767.748370562593</v>
       </c>
       <c r="E34">
-        <v>118.0520000000001</v>
+        <v>160.4880000000001</v>
       </c>
       <c r="F34">
-        <v>1357.952</v>
+        <v>1400.388</v>
       </c>
       <c r="G34">
         <v>510.9</v>
@@ -4069,28 +4069,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M34">
-        <v>73.73679360000001</v>
+        <v>76.04106840000001</v>
       </c>
       <c r="N34">
-        <v>397.9298730666667</v>
+        <v>395.6255982666667</v>
       </c>
       <c r="O34">
-        <v>99.24371034282667</v>
+        <v>98.66902420770667</v>
       </c>
       <c r="P34">
-        <v>298.68616272384</v>
+        <v>296.95657405896</v>
       </c>
       <c r="Q34">
-        <v>460.68616272384</v>
+        <v>458.9565740589599</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09292286079735441</v>
+        <v>0.09349656357480356</v>
       </c>
       <c r="T34">
-        <v>1.088287778229894</v>
+        <v>1.101537265007011</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.396625668663013</v>
+        <v>6.202788527188376</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07609269899511838</v>
+        <v>0.07621063104803574</v>
       </c>
       <c r="C35">
-        <v>2878.260370562592</v>
+        <v>2830.183032242381</v>
       </c>
       <c r="D35">
-        <v>3767.748370562593</v>
+        <v>3762.107032242382</v>
       </c>
       <c r="E35">
-        <v>160.4880000000001</v>
+        <v>202.9240000000002</v>
       </c>
       <c r="F35">
-        <v>1400.388</v>
+        <v>1442.824</v>
       </c>
       <c r="G35">
         <v>510.9</v>
@@ -4151,45 +4151,45 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M35">
-        <v>76.04106840000001</v>
+        <v>79.78816720000002</v>
       </c>
       <c r="N35">
-        <v>395.6255982666667</v>
+        <v>391.8784994666667</v>
       </c>
       <c r="O35">
-        <v>98.66902420770667</v>
+        <v>97.73449776698666</v>
       </c>
       <c r="P35">
-        <v>296.95657405896</v>
+        <v>294.14400169968</v>
       </c>
       <c r="Q35">
-        <v>458.9565740589599</v>
+        <v>456.1440016996799</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09349656357480356</v>
+        <v>0.09408765128490267</v>
       </c>
       <c r="T35">
-        <v>1.101537265007011</v>
+        <v>1.115188251383433</v>
       </c>
       <c r="U35">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.2494</v>
       </c>
       <c r="W35">
-        <v>0.04075757999999999</v>
+        <v>0.04150818</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.202788527188376</v>
+        <v>5.911486417332651</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07621063104803574</v>
+        <v>0.07608086510095313</v>
       </c>
       <c r="C36">
-        <v>2830.183032242381</v>
+        <v>2793.955384931246</v>
       </c>
       <c r="D36">
-        <v>3762.107032242382</v>
+        <v>3768.315384931247</v>
       </c>
       <c r="E36">
-        <v>202.9240000000002</v>
+        <v>245.3600000000001</v>
       </c>
       <c r="F36">
-        <v>1442.824</v>
+        <v>1485.26</v>
       </c>
       <c r="G36">
         <v>510.9</v>
@@ -4233,28 +4233,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M36">
-        <v>79.78816720000002</v>
+        <v>82.13487800000001</v>
       </c>
       <c r="N36">
-        <v>391.8784994666667</v>
+        <v>389.5317886666667</v>
       </c>
       <c r="O36">
-        <v>97.73449776698666</v>
+        <v>97.14922809346668</v>
       </c>
       <c r="P36">
-        <v>294.14400169968</v>
+        <v>292.3825605732</v>
       </c>
       <c r="Q36">
-        <v>456.1440016996799</v>
+        <v>454.3825605732</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09408765128490267</v>
+        <v>0.09469692630915869</v>
       </c>
       <c r="T36">
-        <v>1.115188251383433</v>
+        <v>1.1292592681099</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.911486417332651</v>
+        <v>5.742586805408862</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07608086510095313</v>
+        <v>0.07595109915387052</v>
       </c>
       <c r="C37">
-        <v>2793.955384931246</v>
+        <v>2757.748261945391</v>
       </c>
       <c r="D37">
-        <v>3768.315384931247</v>
+        <v>3774.544261945391</v>
       </c>
       <c r="E37">
-        <v>245.3600000000001</v>
+        <v>287.7960000000003</v>
       </c>
       <c r="F37">
-        <v>1485.26</v>
+        <v>1527.696</v>
       </c>
       <c r="G37">
         <v>510.9</v>
@@ -4315,28 +4315,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M37">
-        <v>82.13487800000001</v>
+        <v>84.48158880000003</v>
       </c>
       <c r="N37">
-        <v>389.5317886666667</v>
+        <v>387.1850778666667</v>
       </c>
       <c r="O37">
-        <v>97.14922809346668</v>
+        <v>96.56395841994667</v>
       </c>
       <c r="P37">
-        <v>292.3825605732</v>
+        <v>290.62111944672</v>
       </c>
       <c r="Q37">
-        <v>454.3825605732</v>
+        <v>452.6211194467199</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09469692630915869</v>
+        <v>0.0953252411779227</v>
       </c>
       <c r="T37">
-        <v>1.1292592681099</v>
+        <v>1.143770004109069</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.742586805408862</v>
+        <v>5.583070505258616</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07595109915387052</v>
+        <v>0.07582133320678791</v>
       </c>
       <c r="C38">
-        <v>2757.748261945391</v>
+        <v>2721.561765231034</v>
       </c>
       <c r="D38">
-        <v>3774.544261945391</v>
+        <v>3780.793765231035</v>
       </c>
       <c r="E38">
-        <v>287.796</v>
+        <v>330.232</v>
       </c>
       <c r="F38">
-        <v>1527.696</v>
+        <v>1570.132</v>
       </c>
       <c r="G38">
         <v>510.9</v>
@@ -4397,28 +4397,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M38">
-        <v>84.48158880000001</v>
+        <v>86.82829960000001</v>
       </c>
       <c r="N38">
-        <v>387.1850778666667</v>
+        <v>384.8383670666667</v>
       </c>
       <c r="O38">
-        <v>96.56395841994667</v>
+        <v>95.97868874642668</v>
       </c>
       <c r="P38">
-        <v>290.62111944672</v>
+        <v>288.8596783202401</v>
       </c>
       <c r="Q38">
-        <v>452.6211194467199</v>
+        <v>450.85967832024</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0953252411779227</v>
+        <v>0.09597350255045699</v>
       </c>
       <c r="T38">
-        <v>1.143770004109069</v>
+        <v>1.158741398393926</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.583070505258616</v>
+        <v>5.432176707819194</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07582133320678791</v>
+        <v>0.07569156725970527</v>
       </c>
       <c r="C39">
-        <v>2721.561765231034</v>
+        <v>2685.395997410686</v>
       </c>
       <c r="D39">
-        <v>3780.793765231035</v>
+        <v>3787.063997410686</v>
       </c>
       <c r="E39">
-        <v>330.232</v>
+        <v>372.6680000000001</v>
       </c>
       <c r="F39">
-        <v>1570.132</v>
+        <v>1612.568</v>
       </c>
       <c r="G39">
         <v>510.9</v>
@@ -4479,28 +4479,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M39">
-        <v>86.82829960000001</v>
+        <v>89.17501040000002</v>
       </c>
       <c r="N39">
-        <v>384.8383670666667</v>
+        <v>382.4916562666667</v>
       </c>
       <c r="O39">
-        <v>95.97868874642668</v>
+        <v>95.39341907290667</v>
       </c>
       <c r="P39">
-        <v>288.8596783202401</v>
+        <v>287.09823719376</v>
       </c>
       <c r="Q39">
-        <v>450.85967832024</v>
+        <v>449.0982371937599</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09597350255045699</v>
+        <v>0.09664267558016981</v>
       </c>
       <c r="T39">
-        <v>1.158741398393926</v>
+        <v>1.17419574088152</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.432176707819194</v>
+        <v>5.289224689192372</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07569156725970527</v>
+        <v>0.07556180131262266</v>
       </c>
       <c r="C40">
-        <v>2685.395997410686</v>
+        <v>2649.251061788753</v>
       </c>
       <c r="D40">
-        <v>3787.063997410686</v>
+        <v>3793.355061788753</v>
       </c>
       <c r="E40">
-        <v>372.6680000000001</v>
+        <v>415.104</v>
       </c>
       <c r="F40">
-        <v>1612.568</v>
+        <v>1655.004</v>
       </c>
       <c r="G40">
         <v>510.9</v>
@@ -4561,28 +4561,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M40">
-        <v>89.17501040000002</v>
+        <v>91.52172120000002</v>
       </c>
       <c r="N40">
-        <v>382.4916562666667</v>
+        <v>380.1449454666667</v>
       </c>
       <c r="O40">
-        <v>95.39341907290667</v>
+        <v>94.80814939938668</v>
       </c>
       <c r="P40">
-        <v>287.09823719376</v>
+        <v>285.33679606728</v>
       </c>
       <c r="Q40">
-        <v>449.0982371937599</v>
+        <v>447.33679606728</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09664267558016981</v>
+        <v>0.09733378870921749</v>
       </c>
       <c r="T40">
-        <v>1.17419574088152</v>
+        <v>1.190156783122806</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.289224689192372</v>
+        <v>5.153603543315645</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07556180131262266</v>
+        <v>0.07543203536554005</v>
       </c>
       <c r="C41">
-        <v>2649.251061788753</v>
+        <v>2613.127062357228</v>
       </c>
       <c r="D41">
-        <v>3793.355061788753</v>
+        <v>3799.667062357229</v>
       </c>
       <c r="E41">
-        <v>415.104</v>
+        <v>457.5400000000002</v>
       </c>
       <c r="F41">
-        <v>1655.004</v>
+        <v>1697.44</v>
       </c>
       <c r="G41">
         <v>510.9</v>
@@ -4643,28 +4643,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M41">
-        <v>91.52172120000002</v>
+        <v>93.86843200000001</v>
       </c>
       <c r="N41">
-        <v>380.1449454666667</v>
+        <v>377.7982346666666</v>
       </c>
       <c r="O41">
-        <v>94.80814939938668</v>
+        <v>94.22287972586666</v>
       </c>
       <c r="P41">
-        <v>285.33679606728</v>
+        <v>283.5753549408</v>
       </c>
       <c r="Q41">
-        <v>447.33679606728</v>
+        <v>445.5753549407999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09733378870921749</v>
+        <v>0.09804793894256675</v>
       </c>
       <c r="T41">
-        <v>1.190156783122806</v>
+        <v>1.206649860105468</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.153603543315645</v>
+        <v>5.024763454732754</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07543203536554005</v>
+        <v>0.07530226941845743</v>
       </c>
       <c r="C42">
-        <v>2613.127062357228</v>
+        <v>2577.024103801414</v>
       </c>
       <c r="D42">
-        <v>3799.667062357229</v>
+        <v>3806.000103801414</v>
       </c>
       <c r="E42">
-        <v>457.5400000000002</v>
+        <v>499.9760000000001</v>
       </c>
       <c r="F42">
-        <v>1697.44</v>
+        <v>1739.876</v>
       </c>
       <c r="G42">
         <v>510.9</v>
@@ -4725,28 +4725,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M42">
-        <v>93.86843200000001</v>
+        <v>96.21514280000001</v>
       </c>
       <c r="N42">
-        <v>377.7982346666666</v>
+        <v>375.4515238666667</v>
       </c>
       <c r="O42">
-        <v>94.22287972586666</v>
+        <v>93.63761005234667</v>
       </c>
       <c r="P42">
-        <v>283.5753549408</v>
+        <v>281.81391381432</v>
       </c>
       <c r="Q42">
-        <v>445.5753549407999</v>
+        <v>443.81391381432</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09804793894256675</v>
+        <v>0.09878629765840242</v>
       </c>
       <c r="T42">
-        <v>1.206649860105468</v>
+        <v>1.223702024443474</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.024763454732754</v>
+        <v>4.90220824851976</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07530226941845743</v>
+        <v>0.0751725034713748</v>
       </c>
       <c r="C43">
-        <v>2577.024103801414</v>
+        <v>2540.942291505702</v>
       </c>
       <c r="D43">
-        <v>3806.000103801414</v>
+        <v>3812.354291505702</v>
       </c>
       <c r="E43">
-        <v>499.9760000000001</v>
+        <v>542.4120000000003</v>
       </c>
       <c r="F43">
-        <v>1739.876</v>
+        <v>1782.312</v>
       </c>
       <c r="G43">
         <v>510.9</v>
@@ -4807,28 +4807,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M43">
-        <v>96.21514280000001</v>
+        <v>98.56185360000002</v>
       </c>
       <c r="N43">
-        <v>375.4515238666667</v>
+        <v>373.1048130666667</v>
       </c>
       <c r="O43">
-        <v>93.63761005234667</v>
+        <v>93.05234037882667</v>
       </c>
       <c r="P43">
-        <v>281.81391381432</v>
+        <v>280.05247268784</v>
       </c>
       <c r="Q43">
-        <v>443.81391381432</v>
+        <v>442.05247268784</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09878629765840242</v>
+        <v>0.09955011701961174</v>
       </c>
       <c r="T43">
-        <v>1.223702024443474</v>
+        <v>1.241342194448308</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.90220824851976</v>
+        <v>4.785489004507385</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0751725034713748</v>
+        <v>0.07504273752429219</v>
       </c>
       <c r="C44">
-        <v>2540.942291505702</v>
+        <v>2504.881731559432</v>
       </c>
       <c r="D44">
-        <v>3812.354291505702</v>
+        <v>3818.729731559432</v>
       </c>
       <c r="E44">
-        <v>542.412</v>
+        <v>584.848</v>
       </c>
       <c r="F44">
-        <v>1782.312</v>
+        <v>1824.748</v>
       </c>
       <c r="G44">
         <v>510.9</v>
@@ -4889,28 +4889,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M44">
-        <v>98.56185360000001</v>
+        <v>100.9085644</v>
       </c>
       <c r="N44">
-        <v>373.1048130666667</v>
+        <v>370.7581022666667</v>
       </c>
       <c r="O44">
-        <v>93.05234037882667</v>
+        <v>92.46707070530668</v>
       </c>
       <c r="P44">
-        <v>280.05247268784</v>
+        <v>278.29103156136</v>
       </c>
       <c r="Q44">
-        <v>442.05247268784</v>
+        <v>440.2910315613599</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09955011701961174</v>
+        <v>0.1003407370601617</v>
       </c>
       <c r="T44">
-        <v>1.241342194448308</v>
+        <v>1.259601317786645</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.785489004507385</v>
+        <v>4.674198562542097</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07504273752429219</v>
+        <v>0.07491297157720958</v>
       </c>
       <c r="C45">
-        <v>2504.881731559432</v>
+        <v>2468.842530762787</v>
       </c>
       <c r="D45">
-        <v>3818.729731559432</v>
+        <v>3825.126530762787</v>
       </c>
       <c r="E45">
-        <v>584.848</v>
+        <v>627.2840000000001</v>
       </c>
       <c r="F45">
-        <v>1824.748</v>
+        <v>1867.184</v>
       </c>
       <c r="G45">
         <v>510.9</v>
@@ -4971,28 +4971,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M45">
-        <v>100.9085644</v>
+        <v>103.2552752</v>
       </c>
       <c r="N45">
-        <v>370.7581022666667</v>
+        <v>368.4113914666667</v>
       </c>
       <c r="O45">
-        <v>92.46707070530668</v>
+        <v>91.88180103178667</v>
       </c>
       <c r="P45">
-        <v>278.29103156136</v>
+        <v>276.52959043488</v>
       </c>
       <c r="Q45">
-        <v>440.2910315613599</v>
+        <v>438.5295904348799</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1003407370601617</v>
+        <v>0.1011595935307314</v>
       </c>
       <c r="T45">
-        <v>1.259601317786645</v>
+        <v>1.27851255267278</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.674198562542097</v>
+        <v>4.567966777029776</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07491297157720958</v>
+        <v>0.07562763063012695</v>
       </c>
       <c r="C46">
-        <v>2468.842530762787</v>
+        <v>2391.441040841069</v>
       </c>
       <c r="D46">
-        <v>3825.126530762787</v>
+        <v>3790.161040841068</v>
       </c>
       <c r="E46">
-        <v>627.2840000000001</v>
+        <v>669.72</v>
       </c>
       <c r="F46">
-        <v>1867.184</v>
+        <v>1909.62</v>
       </c>
       <c r="G46">
         <v>510.9</v>
@@ -5053,45 +5053,45 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M46">
-        <v>103.2552752</v>
+        <v>110.376036</v>
       </c>
       <c r="N46">
-        <v>368.4113914666667</v>
+        <v>361.2906306666667</v>
       </c>
       <c r="O46">
-        <v>91.88180103178667</v>
+        <v>90.10588328826668</v>
       </c>
       <c r="P46">
-        <v>276.52959043488</v>
+        <v>271.1847473784</v>
       </c>
       <c r="Q46">
-        <v>438.5295904348799</v>
+        <v>433.1847473783999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1011595935307314</v>
+        <v>0.1020082266002308</v>
       </c>
       <c r="T46">
-        <v>1.27851255267278</v>
+        <v>1.298111468827502</v>
       </c>
       <c r="U46">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.2494</v>
       </c>
       <c r="W46">
-        <v>0.04150818</v>
+        <v>0.04338468</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.567966777029776</v>
+        <v>4.273270573575107</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07562763063012695</v>
+        <v>0.07551662968304435</v>
       </c>
       <c r="C47">
-        <v>2391.441040841069</v>
+        <v>2354.39389340362</v>
       </c>
       <c r="D47">
-        <v>3790.161040841068</v>
+        <v>3795.54989340362</v>
       </c>
       <c r="E47">
-        <v>669.72</v>
+        <v>712.1560000000002</v>
       </c>
       <c r="F47">
-        <v>1909.62</v>
+        <v>1952.056</v>
       </c>
       <c r="G47">
         <v>510.9</v>
@@ -5135,28 +5135,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M47">
-        <v>110.376036</v>
+        <v>112.8288368</v>
       </c>
       <c r="N47">
-        <v>361.2906306666667</v>
+        <v>358.8378298666667</v>
       </c>
       <c r="O47">
-        <v>90.10588328826668</v>
+        <v>89.49415476874667</v>
       </c>
       <c r="P47">
-        <v>271.1847473784</v>
+        <v>269.34367509792</v>
       </c>
       <c r="Q47">
-        <v>433.1847473783999</v>
+        <v>431.3436750979199</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1020082266002308</v>
+        <v>0.1028882905241562</v>
       </c>
       <c r="T47">
-        <v>1.298111468827502</v>
+        <v>1.318436270765732</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.273270573575107</v>
+        <v>4.180373387193039</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07551662968304435</v>
+        <v>0.07540562873596171</v>
       </c>
       <c r="C48">
-        <v>2354.39389340362</v>
+        <v>2317.362091530184</v>
       </c>
       <c r="D48">
-        <v>3795.54989340362</v>
+        <v>3800.954091530184</v>
       </c>
       <c r="E48">
-        <v>712.1560000000002</v>
+        <v>754.5920000000001</v>
       </c>
       <c r="F48">
-        <v>1952.056</v>
+        <v>1994.492</v>
       </c>
       <c r="G48">
         <v>510.9</v>
@@ -5217,28 +5217,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M48">
-        <v>112.8288368</v>
+        <v>115.2816376</v>
       </c>
       <c r="N48">
-        <v>358.8378298666667</v>
+        <v>356.3850290666667</v>
       </c>
       <c r="O48">
-        <v>89.49415476874667</v>
+        <v>88.88242624922667</v>
       </c>
       <c r="P48">
-        <v>269.34367509792</v>
+        <v>267.50260281744</v>
       </c>
       <c r="Q48">
-        <v>431.3436750979199</v>
+        <v>429.5026028174399</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1028882905241562</v>
+        <v>0.1038015644074749</v>
       </c>
       <c r="T48">
-        <v>1.318436270765732</v>
+        <v>1.339528046362008</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.180373387193039</v>
+        <v>4.091429272571911</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07540562873596171</v>
+        <v>0.0752946277888791</v>
       </c>
       <c r="C49">
-        <v>2317.362091530184</v>
+        <v>2280.345700862404</v>
       </c>
       <c r="D49">
-        <v>3800.954091530184</v>
+        <v>3806.373700862404</v>
       </c>
       <c r="E49">
-        <v>754.5920000000001</v>
+        <v>797.0280000000002</v>
       </c>
       <c r="F49">
-        <v>1994.492</v>
+        <v>2036.928</v>
       </c>
       <c r="G49">
         <v>510.9</v>
@@ -5299,28 +5299,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M49">
-        <v>115.2816376</v>
+        <v>117.7344384</v>
       </c>
       <c r="N49">
-        <v>356.3850290666667</v>
+        <v>353.9322282666666</v>
       </c>
       <c r="O49">
-        <v>88.88242624922667</v>
+        <v>88.27069772970667</v>
       </c>
       <c r="P49">
-        <v>267.50260281744</v>
+        <v>265.66153053696</v>
       </c>
       <c r="Q49">
-        <v>429.5026028174399</v>
+        <v>427.6615305369599</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1038015644074749</v>
+        <v>0.1047499642093829</v>
       </c>
       <c r="T49">
-        <v>1.339528046362008</v>
+        <v>1.361431044096602</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.091429272571911</v>
+        <v>4.006191162726662</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0752946277888791</v>
+        <v>0.07647090584179647</v>
       </c>
       <c r="C50">
-        <v>2280.345700862405</v>
+        <v>2181.252244661778</v>
       </c>
       <c r="D50">
-        <v>3806.373700862404</v>
+        <v>3749.716244661778</v>
       </c>
       <c r="E50">
-        <v>797.028</v>
+        <v>839.4639999999999</v>
       </c>
       <c r="F50">
-        <v>2036.928</v>
+        <v>2079.364</v>
       </c>
       <c r="G50">
         <v>510.9</v>
@@ -5381,45 +5381,45 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M50">
-        <v>117.7344384</v>
+        <v>127.4650132</v>
       </c>
       <c r="N50">
-        <v>353.9322282666667</v>
+        <v>344.2016534666667</v>
       </c>
       <c r="O50">
-        <v>88.27069772970668</v>
+        <v>85.84389237458667</v>
       </c>
       <c r="P50">
-        <v>265.66153053696</v>
+        <v>258.35776109208</v>
       </c>
       <c r="Q50">
-        <v>427.66153053696</v>
+        <v>420.35776109208</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1047499642093829</v>
+        <v>0.1057355561603852</v>
       </c>
       <c r="T50">
-        <v>1.361431044096602</v>
+        <v>1.384192982918828</v>
       </c>
       <c r="U50">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V50">
         <v>0.2494</v>
       </c>
       <c r="W50">
-        <v>0.04338468</v>
+        <v>0.04601178</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.006191162726663</v>
+        <v>3.700361807726755</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07647090584179647</v>
+        <v>0.07638617589471386</v>
       </c>
       <c r="C51">
-        <v>2181.252244661778</v>
+        <v>2142.840975950547</v>
       </c>
       <c r="D51">
-        <v>3749.716244661778</v>
+        <v>3753.740975950547</v>
       </c>
       <c r="E51">
-        <v>839.4639999999999</v>
+        <v>881.9000000000001</v>
       </c>
       <c r="F51">
-        <v>2079.364</v>
+        <v>2121.8</v>
       </c>
       <c r="G51">
         <v>510.9</v>
@@ -5463,28 +5463,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M51">
-        <v>127.4650132</v>
+        <v>130.06634</v>
       </c>
       <c r="N51">
-        <v>344.2016534666667</v>
+        <v>341.6003266666667</v>
       </c>
       <c r="O51">
-        <v>85.84389237458667</v>
+        <v>85.19512147066666</v>
       </c>
       <c r="P51">
-        <v>258.35776109208</v>
+        <v>256.405205196</v>
       </c>
       <c r="Q51">
-        <v>420.35776109208</v>
+        <v>418.4052051959999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1057355561603852</v>
+        <v>0.1067605717894277</v>
       </c>
       <c r="T51">
-        <v>1.384192982918828</v>
+        <v>1.407865399293943</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.700361807726755</v>
+        <v>3.626354571572219</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07638617589471386</v>
+        <v>0.07630144594763125</v>
       </c>
       <c r="C52">
-        <v>2142.840975950547</v>
+        <v>2104.438356356246</v>
       </c>
       <c r="D52">
-        <v>3753.740975950547</v>
+        <v>3757.774356356247</v>
       </c>
       <c r="E52">
-        <v>881.9000000000001</v>
+        <v>924.3360000000002</v>
       </c>
       <c r="F52">
-        <v>2121.8</v>
+        <v>2164.236</v>
       </c>
       <c r="G52">
         <v>510.9</v>
@@ -5545,28 +5545,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M52">
-        <v>130.06634</v>
+        <v>132.6676668</v>
       </c>
       <c r="N52">
-        <v>341.6003266666667</v>
+        <v>338.9989998666666</v>
       </c>
       <c r="O52">
-        <v>85.19512147066666</v>
+        <v>84.54635056674665</v>
       </c>
       <c r="P52">
-        <v>256.405205196</v>
+        <v>254.45264929992</v>
       </c>
       <c r="Q52">
-        <v>418.4052051959999</v>
+        <v>416.4526492999199</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1067605717894277</v>
+        <v>0.1078274247910842</v>
       </c>
       <c r="T52">
-        <v>1.407865399293943</v>
+        <v>1.432504036745593</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.626354571572219</v>
+        <v>3.555249579972763</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07630144594763125</v>
+        <v>0.07730958960054862</v>
       </c>
       <c r="C53">
-        <v>2104.438356356246</v>
+        <v>2014.566806761502</v>
       </c>
       <c r="D53">
-        <v>3757.774356356247</v>
+        <v>3710.338806761502</v>
       </c>
       <c r="E53">
-        <v>924.3360000000002</v>
+        <v>966.7720000000004</v>
       </c>
       <c r="F53">
-        <v>2164.236</v>
+        <v>2206.672</v>
       </c>
       <c r="G53">
         <v>510.9</v>
@@ -5627,45 +5627,45 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M53">
-        <v>132.6676668</v>
+        <v>141.4476752</v>
       </c>
       <c r="N53">
-        <v>338.9989998666666</v>
+        <v>330.2189914666666</v>
       </c>
       <c r="O53">
-        <v>84.54635056674665</v>
+        <v>82.35661647178667</v>
       </c>
       <c r="P53">
-        <v>254.45264929992</v>
+        <v>247.86237499488</v>
       </c>
       <c r="Q53">
-        <v>416.4526492999199</v>
+        <v>409.8623749948799</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1078274247910842</v>
+        <v>0.108938730001143</v>
       </c>
       <c r="T53">
-        <v>1.432504036745593</v>
+        <v>1.458169284091061</v>
       </c>
       <c r="U53">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V53">
         <v>0.2494</v>
       </c>
       <c r="W53">
-        <v>0.04601178</v>
+        <v>0.04811346</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.555249579972763</v>
+        <v>3.334566411217104</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07730958960054862</v>
+        <v>0.07724587645346601</v>
       </c>
       <c r="C54">
-        <v>2014.566806761502</v>
+        <v>1975.093181879855</v>
       </c>
       <c r="D54">
-        <v>3710.338806761502</v>
+        <v>3713.301181879855</v>
       </c>
       <c r="E54">
-        <v>966.7720000000004</v>
+        <v>1009.208</v>
       </c>
       <c r="F54">
-        <v>2206.672</v>
+        <v>2249.108</v>
       </c>
       <c r="G54">
         <v>510.9</v>
@@ -5709,28 +5709,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M54">
-        <v>141.4476752</v>
+        <v>144.1678228</v>
       </c>
       <c r="N54">
-        <v>330.2189914666666</v>
+        <v>327.4988438666667</v>
       </c>
       <c r="O54">
-        <v>82.35661647178667</v>
+        <v>81.67821166034668</v>
       </c>
       <c r="P54">
-        <v>247.86237499488</v>
+        <v>245.82063220632</v>
       </c>
       <c r="Q54">
-        <v>409.8623749948799</v>
+        <v>407.8206322063199</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.108938730001143</v>
+        <v>0.1100973247946085</v>
       </c>
       <c r="T54">
-        <v>1.458169284091061</v>
+        <v>1.484926669621444</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.334566411217104</v>
+        <v>3.27165006383565</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07724587645346601</v>
+        <v>0.07718216330638338</v>
       </c>
       <c r="C55">
-        <v>1975.093181879855</v>
+        <v>1935.624291163462</v>
       </c>
       <c r="D55">
-        <v>3713.301181879855</v>
+        <v>3716.268291163462</v>
       </c>
       <c r="E55">
-        <v>1009.208</v>
+        <v>1051.644</v>
       </c>
       <c r="F55">
-        <v>2249.108</v>
+        <v>2291.544</v>
       </c>
       <c r="G55">
         <v>510.9</v>
@@ -5791,28 +5791,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M55">
-        <v>144.1678228</v>
+        <v>146.8879704</v>
       </c>
       <c r="N55">
-        <v>327.4988438666667</v>
+        <v>324.7786962666667</v>
       </c>
       <c r="O55">
-        <v>81.67821166034668</v>
+        <v>80.99980684890667</v>
       </c>
       <c r="P55">
-        <v>245.82063220632</v>
+        <v>243.77888941776</v>
       </c>
       <c r="Q55">
-        <v>407.8206322063199</v>
+        <v>405.77888941776</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1100973247946085</v>
+        <v>0.1113062932747465</v>
       </c>
       <c r="T55">
-        <v>1.484926669621444</v>
+        <v>1.512847419740104</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.27165006383565</v>
+        <v>3.211063951542397</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07718216330638338</v>
+        <v>0.07711845015930076</v>
       </c>
       <c r="C56">
-        <v>1935.624291163462</v>
+        <v>1896.160145969885</v>
       </c>
       <c r="D56">
-        <v>3716.268291163462</v>
+        <v>3719.240145969886</v>
       </c>
       <c r="E56">
-        <v>1051.644</v>
+        <v>1094.08</v>
       </c>
       <c r="F56">
-        <v>2291.544</v>
+        <v>2333.98</v>
       </c>
       <c r="G56">
         <v>510.9</v>
@@ -5873,28 +5873,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M56">
-        <v>146.8879704</v>
+        <v>149.608118</v>
       </c>
       <c r="N56">
-        <v>324.7786962666667</v>
+        <v>322.0585486666666</v>
       </c>
       <c r="O56">
-        <v>80.99980684890667</v>
+        <v>80.32140203746667</v>
       </c>
       <c r="P56">
-        <v>243.77888941776</v>
+        <v>241.7371466292</v>
       </c>
       <c r="Q56">
-        <v>405.77888941776</v>
+        <v>403.7371466291999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1113062932747465</v>
+        <v>0.112568993687335</v>
       </c>
       <c r="T56">
-        <v>1.512847419740104</v>
+        <v>1.542009092086259</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.211063951542397</v>
+        <v>3.152680970605262</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07711845015930076</v>
+        <v>0.07705473701221814</v>
       </c>
       <c r="C57">
-        <v>1896.160145969885</v>
+        <v>1856.70075769305</v>
       </c>
       <c r="D57">
-        <v>3719.240145969886</v>
+        <v>3722.21675769305</v>
       </c>
       <c r="E57">
-        <v>1094.08</v>
+        <v>1136.516000000001</v>
       </c>
       <c r="F57">
-        <v>2333.98</v>
+        <v>2376.416000000001</v>
       </c>
       <c r="G57">
         <v>510.9</v>
@@ -5955,28 +5955,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M57">
-        <v>149.608118</v>
+        <v>152.3282656</v>
       </c>
       <c r="N57">
-        <v>322.0585486666666</v>
+        <v>319.3384010666666</v>
       </c>
       <c r="O57">
-        <v>80.32140203746667</v>
+        <v>79.64299722602667</v>
       </c>
       <c r="P57">
-        <v>241.7371466292</v>
+        <v>239.69540384064</v>
       </c>
       <c r="Q57">
-        <v>403.7371466291999</v>
+        <v>401.6954038406399</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.112568993687335</v>
+        <v>0.1138890895732231</v>
       </c>
       <c r="T57">
-        <v>1.542009092086259</v>
+        <v>1.572496294993604</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.152680970605262</v>
+        <v>3.096383096130168</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07705473701221814</v>
+        <v>0.07699102386513552</v>
       </c>
       <c r="C58">
-        <v>1856.70075769305</v>
+        <v>1817.246137763382</v>
       </c>
       <c r="D58">
-        <v>3722.21675769305</v>
+        <v>3725.198137763383</v>
       </c>
       <c r="E58">
-        <v>1136.516000000001</v>
+        <v>1178.952</v>
       </c>
       <c r="F58">
-        <v>2376.416000000001</v>
+        <v>2418.852</v>
       </c>
       <c r="G58">
         <v>510.9</v>
@@ -6037,28 +6037,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M58">
-        <v>152.3282656</v>
+        <v>155.0484132</v>
       </c>
       <c r="N58">
-        <v>319.3384010666666</v>
+        <v>316.6182534666667</v>
       </c>
       <c r="O58">
-        <v>79.64299722602667</v>
+        <v>78.96459241458666</v>
       </c>
       <c r="P58">
-        <v>239.69540384064</v>
+        <v>237.65366105208</v>
       </c>
       <c r="Q58">
-        <v>401.6954038406399</v>
+        <v>399.6536610520799</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1138890895732231</v>
+        <v>0.115270585267757</v>
       </c>
       <c r="T58">
-        <v>1.572496294993604</v>
+        <v>1.6044015073385</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.096383096130168</v>
+        <v>3.042060585671744</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07699102386513552</v>
+        <v>0.08032302511805291</v>
       </c>
       <c r="C59">
-        <v>1817.246137763382</v>
+        <v>1625.04179058319</v>
       </c>
       <c r="D59">
-        <v>3725.198137763383</v>
+        <v>3575.42979058319</v>
       </c>
       <c r="E59">
-        <v>1178.952</v>
+        <v>1221.388</v>
       </c>
       <c r="F59">
-        <v>2418.852</v>
+        <v>2461.288</v>
       </c>
       <c r="G59">
         <v>510.9</v>
@@ -6119,45 +6119,45 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M59">
-        <v>155.0484132</v>
+        <v>176.9666072000001</v>
       </c>
       <c r="N59">
-        <v>316.6182534666667</v>
+        <v>294.7000594666666</v>
       </c>
       <c r="O59">
-        <v>78.96459241458666</v>
+        <v>73.49819483098666</v>
       </c>
       <c r="P59">
-        <v>237.65366105208</v>
+        <v>221.20186463568</v>
       </c>
       <c r="Q59">
-        <v>399.6536610520799</v>
+        <v>383.2018646356799</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.115270585267757</v>
+        <v>0.1167178664715545</v>
       </c>
       <c r="T59">
-        <v>1.6044015073385</v>
+        <v>1.637826015509343</v>
       </c>
       <c r="U59">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V59">
         <v>0.2494</v>
       </c>
       <c r="W59">
-        <v>0.04811346</v>
+        <v>0.05396814</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.042060585671744</v>
+        <v>2.665286260099959</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08032302511805291</v>
+        <v>0.08031785877097029</v>
       </c>
       <c r="C60">
-        <v>1625.04179058319</v>
+        <v>1582.828687679617</v>
       </c>
       <c r="D60">
-        <v>3575.42979058319</v>
+        <v>3575.652687679617</v>
       </c>
       <c r="E60">
-        <v>1221.388</v>
+        <v>1263.824</v>
       </c>
       <c r="F60">
-        <v>2461.288</v>
+        <v>2503.724</v>
       </c>
       <c r="G60">
         <v>510.9</v>
@@ -6201,28 +6201,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M60">
-        <v>176.9666072</v>
+        <v>180.0177556</v>
       </c>
       <c r="N60">
-        <v>294.7000594666666</v>
+        <v>291.6489110666666</v>
       </c>
       <c r="O60">
-        <v>73.49819483098666</v>
+        <v>72.73723842002666</v>
       </c>
       <c r="P60">
-        <v>221.20186463568</v>
+        <v>218.91167264664</v>
       </c>
       <c r="Q60">
-        <v>383.2018646356799</v>
+        <v>380.9116726466399</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1167178664715545</v>
+        <v>0.1182357467584641</v>
       </c>
       <c r="T60">
-        <v>1.637826015509343</v>
+        <v>1.672880987493398</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.665286260099959</v>
+        <v>2.620111916708435</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08031785877097029</v>
+        <v>0.08031269242388767</v>
       </c>
       <c r="C61">
-        <v>1582.828687679617</v>
+        <v>1540.615612569186</v>
       </c>
       <c r="D61">
-        <v>3575.652687679617</v>
+        <v>3575.875612569186</v>
       </c>
       <c r="E61">
-        <v>1263.824</v>
+        <v>1306.26</v>
       </c>
       <c r="F61">
-        <v>2503.724</v>
+        <v>2546.16</v>
       </c>
       <c r="G61">
         <v>510.9</v>
@@ -6283,28 +6283,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M61">
-        <v>180.0177556</v>
+        <v>183.068904</v>
       </c>
       <c r="N61">
-        <v>291.6489110666666</v>
+        <v>288.5977626666667</v>
       </c>
       <c r="O61">
-        <v>72.73723842002666</v>
+        <v>71.97628200906667</v>
       </c>
       <c r="P61">
-        <v>218.91167264664</v>
+        <v>216.6214806576</v>
       </c>
       <c r="Q61">
-        <v>380.9116726466399</v>
+        <v>378.6214806575999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1182357467584641</v>
+        <v>0.1198295210597192</v>
       </c>
       <c r="T61">
-        <v>1.672880987493398</v>
+        <v>1.709688708076655</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.620111916708435</v>
+        <v>2.576443384763294</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08031269242388767</v>
+        <v>0.08030752607680505</v>
       </c>
       <c r="C62">
-        <v>1540.615612569186</v>
+        <v>1498.402565257095</v>
       </c>
       <c r="D62">
-        <v>3575.875612569186</v>
+        <v>3576.098565257095</v>
       </c>
       <c r="E62">
-        <v>1306.26</v>
+        <v>1348.696</v>
       </c>
       <c r="F62">
-        <v>2546.16</v>
+        <v>2588.596</v>
       </c>
       <c r="G62">
         <v>510.9</v>
@@ -6365,28 +6365,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M62">
-        <v>183.068904</v>
+        <v>186.1200524</v>
       </c>
       <c r="N62">
-        <v>288.5977626666667</v>
+        <v>285.5466142666667</v>
       </c>
       <c r="O62">
-        <v>71.97628200906667</v>
+        <v>71.21532559810667</v>
       </c>
       <c r="P62">
-        <v>216.6214806576</v>
+        <v>214.33128866856</v>
       </c>
       <c r="Q62">
-        <v>378.6214806575999</v>
+        <v>376.3312886685599</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1198295210597192</v>
+        <v>0.1215050273764232</v>
       </c>
       <c r="T62">
-        <v>1.709688708076655</v>
+        <v>1.748384004074439</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.576443384763294</v>
+        <v>2.534206607963896</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08030752607680505</v>
+        <v>0.08211731052972243</v>
       </c>
       <c r="C63">
-        <v>1498.402565257095</v>
+        <v>1379.530254682539</v>
       </c>
       <c r="D63">
-        <v>3576.098565257095</v>
+        <v>3499.662254682539</v>
       </c>
       <c r="E63">
-        <v>1348.696</v>
+        <v>1391.132</v>
       </c>
       <c r="F63">
-        <v>2588.596</v>
+        <v>2631.032</v>
       </c>
       <c r="G63">
         <v>510.9</v>
@@ -6447,45 +6447,45 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M63">
-        <v>186.1200524</v>
+        <v>199.4322256</v>
       </c>
       <c r="N63">
-        <v>285.5466142666667</v>
+        <v>272.2344410666666</v>
       </c>
       <c r="O63">
-        <v>71.21532559810667</v>
+        <v>67.89526960202666</v>
       </c>
       <c r="P63">
-        <v>214.33128866856</v>
+        <v>204.33917146464</v>
       </c>
       <c r="Q63">
-        <v>376.3312886685599</v>
+        <v>366.3391714646399</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1215050273764232</v>
+        <v>0.1232687182361117</v>
       </c>
       <c r="T63">
-        <v>1.748384004074439</v>
+        <v>1.789115894598422</v>
       </c>
       <c r="U63">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V63">
         <v>0.2494</v>
       </c>
       <c r="W63">
-        <v>0.05396814</v>
+        <v>0.05689548</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.534206607963896</v>
+        <v>2.365047400176366</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08211731052972243</v>
+        <v>0.08214141758263982</v>
       </c>
       <c r="C64">
-        <v>1379.530254682539</v>
+        <v>1336.098138476344</v>
       </c>
       <c r="D64">
-        <v>3499.662254682539</v>
+        <v>3498.666138476344</v>
       </c>
       <c r="E64">
-        <v>1391.132</v>
+        <v>1433.568</v>
       </c>
       <c r="F64">
-        <v>2631.032</v>
+        <v>2673.468</v>
       </c>
       <c r="G64">
         <v>510.9</v>
@@ -6529,28 +6529,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M64">
-        <v>199.4322256</v>
+        <v>202.6488744</v>
       </c>
       <c r="N64">
-        <v>272.2344410666666</v>
+        <v>269.0177922666667</v>
       </c>
       <c r="O64">
-        <v>67.89526960202666</v>
+        <v>67.09303739130667</v>
       </c>
       <c r="P64">
-        <v>204.33917146464</v>
+        <v>201.92475487536</v>
       </c>
       <c r="Q64">
-        <v>366.3391714646399</v>
+        <v>363.92475487536</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1232687182361117</v>
+        <v>0.1251277437368644</v>
       </c>
       <c r="T64">
-        <v>1.789115894598422</v>
+        <v>1.832049508934512</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.365047400176366</v>
+        <v>2.327506965252932</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08214141758263982</v>
+        <v>0.08216552463555719</v>
       </c>
       <c r="C65">
-        <v>1336.098138476344</v>
+        <v>1292.666589162082</v>
       </c>
       <c r="D65">
-        <v>3498.666138476344</v>
+        <v>3497.670589162083</v>
       </c>
       <c r="E65">
-        <v>1433.568</v>
+        <v>1476.004</v>
       </c>
       <c r="F65">
-        <v>2673.468</v>
+        <v>2715.904</v>
       </c>
       <c r="G65">
         <v>510.9</v>
@@ -6611,28 +6611,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M65">
-        <v>202.6488744</v>
+        <v>205.8655232</v>
       </c>
       <c r="N65">
-        <v>269.0177922666667</v>
+        <v>265.8011434666666</v>
       </c>
       <c r="O65">
-        <v>67.09303739130667</v>
+        <v>66.29080518058666</v>
       </c>
       <c r="P65">
-        <v>201.92475487536</v>
+        <v>199.51033828608</v>
       </c>
       <c r="Q65">
-        <v>363.92475487536</v>
+        <v>361.5103382860799</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1251277437368644</v>
+        <v>0.1270900484321033</v>
       </c>
       <c r="T65">
-        <v>1.832049508934512</v>
+        <v>1.877368324067051</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.327506965252932</v>
+        <v>2.291139668920855</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08216552463555719</v>
+        <v>0.08218963168847457</v>
       </c>
       <c r="C66">
-        <v>1292.666589162082</v>
+        <v>1249.235606255963</v>
       </c>
       <c r="D66">
-        <v>3497.670589162083</v>
+        <v>3496.675606255963</v>
       </c>
       <c r="E66">
-        <v>1476.004</v>
+        <v>1518.44</v>
       </c>
       <c r="F66">
-        <v>2715.904</v>
+        <v>2758.34</v>
       </c>
       <c r="G66">
         <v>510.9</v>
@@ -6693,28 +6693,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M66">
-        <v>205.8655232</v>
+        <v>209.082172</v>
       </c>
       <c r="N66">
-        <v>265.8011434666666</v>
+        <v>262.5844946666667</v>
       </c>
       <c r="O66">
-        <v>66.29080518058666</v>
+        <v>65.48857296986667</v>
       </c>
       <c r="P66">
-        <v>199.51033828608</v>
+        <v>197.0959216968</v>
       </c>
       <c r="Q66">
-        <v>361.5103382860799</v>
+        <v>359.0959216968</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1270900484321033</v>
+        <v>0.1291644848242131</v>
       </c>
       <c r="T66">
-        <v>1.877368324067051</v>
+        <v>1.925276785778593</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.291139668920855</v>
+        <v>2.255891366322073</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08218963168847457</v>
+        <v>0.08221373874139196</v>
       </c>
       <c r="C67">
-        <v>1249.235606255963</v>
+        <v>1205.805189274744</v>
       </c>
       <c r="D67">
-        <v>3496.675606255963</v>
+        <v>3495.681189274744</v>
       </c>
       <c r="E67">
-        <v>1518.44</v>
+        <v>1560.876</v>
       </c>
       <c r="F67">
-        <v>2758.34</v>
+        <v>2800.776</v>
       </c>
       <c r="G67">
         <v>510.9</v>
@@ -6775,28 +6775,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M67">
-        <v>209.082172</v>
+        <v>212.2988208</v>
       </c>
       <c r="N67">
-        <v>262.5844946666667</v>
+        <v>259.3678458666666</v>
       </c>
       <c r="O67">
-        <v>65.48857296986667</v>
+        <v>64.68634075914666</v>
       </c>
       <c r="P67">
-        <v>197.0959216968</v>
+        <v>194.68150510752</v>
       </c>
       <c r="Q67">
-        <v>359.0959216968</v>
+        <v>356.6815051075199</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1291644848242131</v>
+        <v>0.1313609468864469</v>
       </c>
       <c r="T67">
-        <v>1.925276785778593</v>
+        <v>1.976003392296696</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.255891366322073</v>
+        <v>2.221711194105072</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08221373874139196</v>
+        <v>0.08223784579430934</v>
       </c>
       <c r="C68">
-        <v>1205.805189274744</v>
+        <v>1162.375337735734</v>
       </c>
       <c r="D68">
-        <v>3495.681189274744</v>
+        <v>3494.687337735734</v>
       </c>
       <c r="E68">
-        <v>1560.876</v>
+        <v>1603.312</v>
       </c>
       <c r="F68">
-        <v>2800.776</v>
+        <v>2843.212</v>
       </c>
       <c r="G68">
         <v>510.9</v>
@@ -6857,28 +6857,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M68">
-        <v>212.2988208</v>
+        <v>215.5154696</v>
       </c>
       <c r="N68">
-        <v>259.3678458666666</v>
+        <v>256.1511970666667</v>
       </c>
       <c r="O68">
-        <v>64.68634075914666</v>
+        <v>63.88410854842667</v>
       </c>
       <c r="P68">
-        <v>194.68150510752</v>
+        <v>192.26708851824</v>
       </c>
       <c r="Q68">
-        <v>356.6815051075199</v>
+        <v>354.2670885182399</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1313609468864469</v>
+        <v>0.1336905278615435</v>
       </c>
       <c r="T68">
-        <v>1.976003392296696</v>
+        <v>2.029804338603775</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.221711194105072</v>
+        <v>2.188551325536339</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08223784579430934</v>
+        <v>0.08226195284722672</v>
       </c>
       <c r="C69">
-        <v>1162.375337735734</v>
+        <v>1118.946051156791</v>
       </c>
       <c r="D69">
-        <v>3494.687337735734</v>
+        <v>3493.694051156792</v>
       </c>
       <c r="E69">
-        <v>1603.312</v>
+        <v>1645.748000000001</v>
       </c>
       <c r="F69">
-        <v>2843.212</v>
+        <v>2885.648000000001</v>
       </c>
       <c r="G69">
         <v>510.9</v>
@@ -6939,28 +6939,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M69">
-        <v>215.5154696</v>
+        <v>218.7321184000001</v>
       </c>
       <c r="N69">
-        <v>256.1511970666667</v>
+        <v>252.9345482666666</v>
       </c>
       <c r="O69">
-        <v>63.88410854842667</v>
+        <v>63.08187633770665</v>
       </c>
       <c r="P69">
-        <v>192.26708851824</v>
+        <v>189.8526719289599</v>
       </c>
       <c r="Q69">
-        <v>354.2670885182399</v>
+        <v>351.8526719289599</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1336905278615435</v>
+        <v>0.1361657076475835</v>
       </c>
       <c r="T69">
-        <v>2.029804338603775</v>
+        <v>2.086967844055046</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.188551325536339</v>
+        <v>2.156366747219628</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08226195284722672</v>
+        <v>0.08228605990014409</v>
       </c>
       <c r="C70">
-        <v>1118.946051156791</v>
+        <v>1075.51732905632</v>
       </c>
       <c r="D70">
-        <v>3493.694051156792</v>
+        <v>3492.70132905632</v>
       </c>
       <c r="E70">
-        <v>1645.748000000001</v>
+        <v>1688.184</v>
       </c>
       <c r="F70">
-        <v>2885.648000000001</v>
+        <v>2928.084</v>
       </c>
       <c r="G70">
         <v>510.9</v>
@@ -7021,28 +7021,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M70">
-        <v>218.7321184000001</v>
+        <v>221.9487672</v>
       </c>
       <c r="N70">
-        <v>252.9345482666666</v>
+        <v>249.7178994666666</v>
       </c>
       <c r="O70">
-        <v>63.08187633770665</v>
+        <v>62.27964412698666</v>
       </c>
       <c r="P70">
-        <v>189.8526719289599</v>
+        <v>187.43825533968</v>
       </c>
       <c r="Q70">
-        <v>351.8526719289599</v>
+        <v>349.4382553396799</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1361657076475835</v>
+        <v>0.1388005764520777</v>
       </c>
       <c r="T70">
-        <v>2.086967844055046</v>
+        <v>2.147819317599948</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.156366747219628</v>
+        <v>2.125115055230938</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08228605990014409</v>
+        <v>0.08231016695306148</v>
       </c>
       <c r="C71">
-        <v>1075.51732905632</v>
+        <v>1032.089170953272</v>
       </c>
       <c r="D71">
-        <v>3492.70132905632</v>
+        <v>3491.709170953272</v>
       </c>
       <c r="E71">
-        <v>1688.184</v>
+        <v>1730.62</v>
       </c>
       <c r="F71">
-        <v>2928.084</v>
+        <v>2970.52</v>
       </c>
       <c r="G71">
         <v>510.9</v>
@@ -7103,28 +7103,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M71">
-        <v>221.9487672</v>
+        <v>225.1654160000001</v>
       </c>
       <c r="N71">
-        <v>249.7178994666666</v>
+        <v>246.5012506666666</v>
       </c>
       <c r="O71">
-        <v>62.27964412698666</v>
+        <v>61.47741191626666</v>
       </c>
       <c r="P71">
-        <v>187.43825533968</v>
+        <v>185.0238387504</v>
       </c>
       <c r="Q71">
-        <v>349.4382553396799</v>
+        <v>347.0238387503999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1388005764520777</v>
+        <v>0.1416111031768716</v>
       </c>
       <c r="T71">
-        <v>2.147819317599948</v>
+        <v>2.212727556047843</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.125115055230938</v>
+        <v>2.094756268727639</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08231016695306148</v>
+        <v>0.08233427400597887</v>
       </c>
       <c r="C72">
-        <v>1032.089170953272</v>
+        <v>988.6615763671466</v>
       </c>
       <c r="D72">
-        <v>3491.709170953272</v>
+        <v>3490.717576367147</v>
       </c>
       <c r="E72">
-        <v>1730.62</v>
+        <v>1773.056</v>
       </c>
       <c r="F72">
-        <v>2970.52</v>
+        <v>3012.956000000001</v>
       </c>
       <c r="G72">
         <v>510.9</v>
@@ -7185,28 +7185,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M72">
-        <v>225.1654160000001</v>
+        <v>228.3820648000001</v>
       </c>
       <c r="N72">
-        <v>246.5012506666666</v>
+        <v>243.2846018666666</v>
       </c>
       <c r="O72">
-        <v>61.47741191626666</v>
+        <v>60.67517970554666</v>
       </c>
       <c r="P72">
-        <v>185.0238387504</v>
+        <v>182.60942216112</v>
       </c>
       <c r="Q72">
-        <v>347.0238387503999</v>
+        <v>344.6094221611199</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1416111031768716</v>
+        <v>0.1446154593309616</v>
       </c>
       <c r="T72">
-        <v>2.212727556047843</v>
+        <v>2.282112224733525</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.094756268727639</v>
+        <v>2.06525265930894</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08233427400597887</v>
+        <v>0.08235838105889624</v>
       </c>
       <c r="C73">
-        <v>988.6615763671471</v>
+        <v>945.2345448179894</v>
       </c>
       <c r="D73">
-        <v>3490.717576367147</v>
+        <v>3489.72654481799</v>
       </c>
       <c r="E73">
-        <v>1773.056</v>
+        <v>1815.492</v>
       </c>
       <c r="F73">
-        <v>3012.956</v>
+        <v>3055.392</v>
       </c>
       <c r="G73">
         <v>510.9</v>
@@ -7267,28 +7267,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M73">
-        <v>228.3820648</v>
+        <v>231.5987136000001</v>
       </c>
       <c r="N73">
-        <v>243.2846018666667</v>
+        <v>240.0679530666666</v>
       </c>
       <c r="O73">
-        <v>60.67517970554667</v>
+        <v>59.87294749482666</v>
       </c>
       <c r="P73">
-        <v>182.60942216112</v>
+        <v>180.19500557184</v>
       </c>
       <c r="Q73">
-        <v>344.6094221611199</v>
+        <v>342.1950055718399</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1446154593309616</v>
+        <v>0.1478344123532009</v>
       </c>
       <c r="T73">
-        <v>2.282112224733524</v>
+        <v>2.356452941182468</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.06525265930894</v>
+        <v>2.036568594596315</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08235838105889624</v>
+        <v>0.08238248811181362</v>
       </c>
       <c r="C74">
-        <v>945.2345448179894</v>
+        <v>901.8080758263886</v>
       </c>
       <c r="D74">
-        <v>3489.72654481799</v>
+        <v>3488.736075826389</v>
       </c>
       <c r="E74">
-        <v>1815.492</v>
+        <v>1857.928</v>
       </c>
       <c r="F74">
-        <v>3055.392</v>
+        <v>3097.828</v>
       </c>
       <c r="G74">
         <v>510.9</v>
@@ -7349,28 +7349,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M74">
-        <v>231.5987136000001</v>
+        <v>234.8153624</v>
       </c>
       <c r="N74">
-        <v>240.0679530666666</v>
+        <v>236.8513042666667</v>
       </c>
       <c r="O74">
-        <v>59.87294749482666</v>
+        <v>59.07071528410667</v>
       </c>
       <c r="P74">
-        <v>180.19500557184</v>
+        <v>177.78058898256</v>
       </c>
       <c r="Q74">
-        <v>342.1950055718399</v>
+        <v>339.7805889825599</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1478344123532009</v>
+        <v>0.1512918063400504</v>
       </c>
       <c r="T74">
-        <v>2.356452941182468</v>
+        <v>2.43630037736837</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.036568594596315</v>
+        <v>2.008670394670339</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08238248811181362</v>
+        <v>0.090293899964731</v>
       </c>
       <c r="C75">
-        <v>901.8080758263886</v>
+        <v>562.1030097707835</v>
       </c>
       <c r="D75">
-        <v>3488.736075826389</v>
+        <v>3191.467009770784</v>
       </c>
       <c r="E75">
-        <v>1857.928</v>
+        <v>1900.364</v>
       </c>
       <c r="F75">
-        <v>3097.828</v>
+        <v>3140.264</v>
       </c>
       <c r="G75">
         <v>510.9</v>
@@ -7431,45 +7431,45 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M75">
-        <v>234.8153624</v>
+        <v>282.62376</v>
       </c>
       <c r="N75">
-        <v>236.8513042666667</v>
+        <v>189.0429066666667</v>
       </c>
       <c r="O75">
-        <v>59.07071528410667</v>
+        <v>47.14730092266667</v>
       </c>
       <c r="P75">
-        <v>177.78058898256</v>
+        <v>141.895605744</v>
       </c>
       <c r="Q75">
-        <v>339.7805889825599</v>
+        <v>303.895605744</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1512918063400504</v>
+        <v>0.1550151537105038</v>
       </c>
       <c r="T75">
-        <v>2.43630037736837</v>
+        <v>2.522289924030112</v>
       </c>
       <c r="U75">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V75">
         <v>0.2494</v>
       </c>
       <c r="W75">
-        <v>0.05689548</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y75">
-        <v>2.008670394670339</v>
+        <v>1.668885399680008</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.090293899964731</v>
+        <v>0.09042459221764837</v>
       </c>
       <c r="C76">
-        <v>562.1030097707835</v>
+        <v>515.1810339090816</v>
       </c>
       <c r="D76">
-        <v>3191.467009770784</v>
+        <v>3186.981033909082</v>
       </c>
       <c r="E76">
-        <v>1900.364</v>
+        <v>1942.8</v>
       </c>
       <c r="F76">
-        <v>3140.264</v>
+        <v>3182.7</v>
       </c>
       <c r="G76">
         <v>510.9</v>
@@ -7513,28 +7513,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M76">
-        <v>282.62376</v>
+        <v>286.443</v>
       </c>
       <c r="N76">
-        <v>189.0429066666667</v>
+        <v>185.2236666666666</v>
       </c>
       <c r="O76">
-        <v>47.14730092266667</v>
+        <v>46.19478246666667</v>
       </c>
       <c r="P76">
-        <v>141.895605744</v>
+        <v>139.0288842</v>
       </c>
       <c r="Q76">
-        <v>303.895605744</v>
+        <v>301.0288841999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1550151537105038</v>
+        <v>0.1590363688705935</v>
       </c>
       <c r="T76">
-        <v>2.522289924030112</v>
+        <v>2.615158634424793</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.668885399680008</v>
+        <v>1.646633594350941</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09042459221764837</v>
+        <v>0.09055528447056575</v>
       </c>
       <c r="C77">
-        <v>515.1810339090816</v>
+        <v>468.2716514613139</v>
       </c>
       <c r="D77">
-        <v>3186.981033909082</v>
+        <v>3182.507651461314</v>
       </c>
       <c r="E77">
-        <v>1942.8</v>
+        <v>1985.236</v>
       </c>
       <c r="F77">
-        <v>3182.7</v>
+        <v>3225.136</v>
       </c>
       <c r="G77">
         <v>510.9</v>
@@ -7595,28 +7595,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M77">
-        <v>286.443</v>
+        <v>290.26224</v>
       </c>
       <c r="N77">
-        <v>185.2236666666666</v>
+        <v>181.4044266666667</v>
       </c>
       <c r="O77">
-        <v>46.19478246666667</v>
+        <v>45.24226401066667</v>
       </c>
       <c r="P77">
-        <v>139.0288842</v>
+        <v>136.162162656</v>
       </c>
       <c r="Q77">
-        <v>301.0288841999999</v>
+        <v>298.162162656</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1590363688705935</v>
+        <v>0.163392685294024</v>
       </c>
       <c r="T77">
-        <v>2.615158634424793</v>
+        <v>2.715766404019031</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.646633594350941</v>
+        <v>1.624967362846323</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09055528447056575</v>
+        <v>0.09068597672348314</v>
       </c>
       <c r="C78">
-        <v>468.2716514613139</v>
+        <v>421.3748094718535</v>
       </c>
       <c r="D78">
-        <v>3182.507651461314</v>
+        <v>3178.046809471854</v>
       </c>
       <c r="E78">
-        <v>1985.236</v>
+        <v>2027.672</v>
       </c>
       <c r="F78">
-        <v>3225.136</v>
+        <v>3267.572000000001</v>
       </c>
       <c r="G78">
         <v>510.9</v>
@@ -7677,28 +7677,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M78">
-        <v>290.26224</v>
+        <v>294.0814800000001</v>
       </c>
       <c r="N78">
-        <v>181.4044266666667</v>
+        <v>177.5851866666666</v>
       </c>
       <c r="O78">
-        <v>45.24226401066667</v>
+        <v>44.28974555466666</v>
       </c>
       <c r="P78">
-        <v>136.162162656</v>
+        <v>133.295441112</v>
       </c>
       <c r="Q78">
-        <v>298.162162656</v>
+        <v>295.2954411119999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.163392685294024</v>
+        <v>0.1681278118412311</v>
       </c>
       <c r="T78">
-        <v>2.715766404019031</v>
+        <v>2.825122675317115</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.624967362846323</v>
+        <v>1.603863890601566</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09068597672348314</v>
+        <v>0.09081666897640052</v>
       </c>
       <c r="C79">
-        <v>421.3748094718535</v>
+        <v>374.4904552815642</v>
       </c>
       <c r="D79">
-        <v>3178.046809471854</v>
+        <v>3173.598455281564</v>
       </c>
       <c r="E79">
-        <v>2027.672</v>
+        <v>2070.108</v>
       </c>
       <c r="F79">
-        <v>3267.572000000001</v>
+        <v>3310.008</v>
       </c>
       <c r="G79">
         <v>510.9</v>
@@ -7759,28 +7759,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M79">
-        <v>294.0814800000001</v>
+        <v>297.90072</v>
       </c>
       <c r="N79">
-        <v>177.5851866666666</v>
+        <v>173.7659466666667</v>
       </c>
       <c r="O79">
-        <v>44.28974555466666</v>
+        <v>43.33722709866667</v>
       </c>
       <c r="P79">
-        <v>133.295441112</v>
+        <v>130.428719568</v>
       </c>
       <c r="Q79">
-        <v>295.2954411119999</v>
+        <v>292.4287195679999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1681278118412311</v>
+        <v>0.1732934044381842</v>
       </c>
       <c r="T79">
-        <v>2.825122675317115</v>
+        <v>2.944420425824116</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.603863890601566</v>
+        <v>1.583301533029751</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09081666897640052</v>
+        <v>0.0909473612293179</v>
       </c>
       <c r="C80">
-        <v>374.4904552815642</v>
+        <v>327.6185365257274</v>
       </c>
       <c r="D80">
-        <v>3173.598455281564</v>
+        <v>3169.162536525728</v>
       </c>
       <c r="E80">
-        <v>2070.108</v>
+        <v>2112.544</v>
       </c>
       <c r="F80">
-        <v>3310.008</v>
+        <v>3352.444</v>
       </c>
       <c r="G80">
         <v>510.9</v>
@@ -7841,28 +7841,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M80">
-        <v>297.90072</v>
+        <v>301.71996</v>
       </c>
       <c r="N80">
-        <v>173.7659466666667</v>
+        <v>169.9467066666667</v>
       </c>
       <c r="O80">
-        <v>43.33722709866667</v>
+        <v>42.38470864266667</v>
       </c>
       <c r="P80">
-        <v>130.428719568</v>
+        <v>127.561998024</v>
       </c>
       <c r="Q80">
-        <v>292.4287195679999</v>
+        <v>289.5619980239999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1732934044381842</v>
+        <v>0.1789509582348472</v>
       </c>
       <c r="T80">
-        <v>2.944420425824116</v>
+        <v>3.075079866855594</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.583301533029751</v>
+        <v>1.563259741472413</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.0909473612293179</v>
+        <v>0.09107805348223527</v>
       </c>
       <c r="C81">
-        <v>327.6185365257274</v>
+        <v>280.7590011319903</v>
       </c>
       <c r="D81">
-        <v>3169.162536525728</v>
+        <v>3164.739001131991</v>
       </c>
       <c r="E81">
-        <v>2112.544</v>
+        <v>2154.98</v>
       </c>
       <c r="F81">
-        <v>3352.444</v>
+        <v>3394.880000000001</v>
       </c>
       <c r="G81">
         <v>510.9</v>
@@ -7923,28 +7923,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M81">
-        <v>301.71996</v>
+        <v>305.5392000000001</v>
       </c>
       <c r="N81">
-        <v>169.9467066666667</v>
+        <v>166.1274666666666</v>
       </c>
       <c r="O81">
-        <v>42.38470864266667</v>
+        <v>41.43219018666666</v>
       </c>
       <c r="P81">
-        <v>127.561998024</v>
+        <v>124.69527648</v>
       </c>
       <c r="Q81">
-        <v>289.5619980239999</v>
+        <v>286.6952764799999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1789509582348472</v>
+        <v>0.1851742674111765</v>
       </c>
       <c r="T81">
-        <v>3.075079866855594</v>
+        <v>3.218805251990219</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.563259741472413</v>
+        <v>1.543718994704007</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09107805348223527</v>
+        <v>0.09120874573515267</v>
       </c>
       <c r="C82">
-        <v>280.7590011319903</v>
+        <v>233.9117973183234</v>
       </c>
       <c r="D82">
-        <v>3164.739001131991</v>
+        <v>3160.327797318324</v>
       </c>
       <c r="E82">
-        <v>2154.98</v>
+        <v>2197.416000000001</v>
       </c>
       <c r="F82">
-        <v>3394.880000000001</v>
+        <v>3437.316000000001</v>
       </c>
       <c r="G82">
         <v>510.9</v>
@@ -8005,28 +8005,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M82">
-        <v>305.5392000000001</v>
+        <v>309.35844</v>
       </c>
       <c r="N82">
-        <v>166.1274666666666</v>
+        <v>162.3082266666667</v>
       </c>
       <c r="O82">
-        <v>41.43219018666666</v>
+        <v>40.47967173066667</v>
       </c>
       <c r="P82">
-        <v>124.69527648</v>
+        <v>121.828554936</v>
       </c>
       <c r="Q82">
-        <v>286.6952764799999</v>
+        <v>283.8285549359999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1851742674111765</v>
+        <v>0.1920526617639615</v>
       </c>
       <c r="T82">
-        <v>3.218805251990219</v>
+        <v>3.377659625033752</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.543718994704007</v>
+        <v>1.524660735510131</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09120874573515267</v>
+        <v>0.09133943798807004</v>
       </c>
       <c r="C83">
-        <v>233.9117973183234</v>
+        <v>187.0768735910074</v>
       </c>
       <c r="D83">
-        <v>3160.327797318324</v>
+        <v>3155.928873591008</v>
       </c>
       <c r="E83">
-        <v>2197.416000000001</v>
+        <v>2239.852</v>
       </c>
       <c r="F83">
-        <v>3437.316000000001</v>
+        <v>3479.752</v>
       </c>
       <c r="G83">
         <v>510.9</v>
@@ -8087,28 +8087,28 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M83">
-        <v>309.35844</v>
+        <v>313.17768</v>
       </c>
       <c r="N83">
-        <v>162.3082266666667</v>
+        <v>158.4889866666667</v>
       </c>
       <c r="O83">
-        <v>40.47967173066667</v>
+        <v>39.52715327466667</v>
       </c>
       <c r="P83">
-        <v>121.828554936</v>
+        <v>118.961833392</v>
       </c>
       <c r="Q83">
-        <v>283.8285549359999</v>
+        <v>280.961833392</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1920526617639615</v>
+        <v>0.1996953221559448</v>
       </c>
       <c r="T83">
-        <v>3.377659625033752</v>
+        <v>3.554164483971011</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.524660735510131</v>
+        <v>1.506067311906349</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09133943798807004</v>
+        <v>0.1301568524223559</v>
       </c>
       <c r="C84">
-        <v>187.0768735910074</v>
+        <v>-778.4557415456306</v>
       </c>
       <c r="D84">
-        <v>3155.928873591008</v>
+        <v>2232.83225845437</v>
       </c>
       <c r="E84">
-        <v>2239.852</v>
+        <v>2282.288</v>
       </c>
       <c r="F84">
-        <v>3479.752</v>
+        <v>3522.188000000001</v>
       </c>
       <c r="G84">
         <v>510.9</v>
@@ -8169,45 +8169,45 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M84">
-        <v>313.17768</v>
+        <v>517.0571984000002</v>
       </c>
       <c r="N84">
-        <v>158.4889866666667</v>
+        <v>-45.39053173333349</v>
       </c>
       <c r="O84">
-        <v>39.52715327466667</v>
+        <v>-11.32039861429337</v>
       </c>
       <c r="P84">
-        <v>118.961833392</v>
+        <v>-34.07013311904011</v>
       </c>
       <c r="Q84">
-        <v>280.961833392</v>
+        <v>127.9298668809598</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1996953221559448</v>
+        <v>0.2119594450968049</v>
       </c>
       <c r="T84">
-        <v>3.554164483971011</v>
+        <v>3.837400579602884</v>
       </c>
       <c r="U84">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2494</v>
+        <v>0.2275060999647165</v>
       </c>
       <c r="W84">
-        <v>0.06755399999999999</v>
+        <v>0.1134021045251796</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y84">
-        <v>1.506067311906349</v>
+        <v>0.9122137127695127</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1301568524223559</v>
+        <v>0.1311668524223559</v>
       </c>
       <c r="C85">
-        <v>-778.4557415456306</v>
+        <v>-837.7564222415867</v>
       </c>
       <c r="D85">
-        <v>2232.83225845437</v>
+        <v>2215.967577758414</v>
       </c>
       <c r="E85">
-        <v>2282.288</v>
+        <v>2324.724000000001</v>
       </c>
       <c r="F85">
-        <v>3522.188000000001</v>
+        <v>3564.624000000001</v>
       </c>
       <c r="G85">
         <v>510.9</v>
@@ -8251,37 +8251,37 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M85">
-        <v>517.0571984000002</v>
+        <v>523.2868032000001</v>
       </c>
       <c r="N85">
-        <v>-45.39053173333349</v>
+        <v>-51.62013653333344</v>
       </c>
       <c r="O85">
-        <v>-11.32039861429337</v>
+        <v>-12.87406205141336</v>
       </c>
       <c r="P85">
-        <v>-34.07013311904011</v>
+        <v>-38.74607448192008</v>
       </c>
       <c r="Q85">
-        <v>127.9298668809598</v>
+        <v>123.2539255180799</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2119594450968049</v>
+        <v>0.2223444104153552</v>
       </c>
       <c r="T85">
-        <v>3.837400579602884</v>
+        <v>4.077238115828065</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2275060999647165</v>
+        <v>0.2247976940127556</v>
       </c>
       <c r="W85">
-        <v>0.1134021045251796</v>
+        <v>0.1137996985189275</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9122137127695127</v>
+        <v>0.9013540257127328</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1311668524223559</v>
+        <v>0.1321768524223559</v>
       </c>
       <c r="C86">
-        <v>-837.7564222415858</v>
+        <v>-896.8042533647599</v>
       </c>
       <c r="D86">
-        <v>2215.967577758414</v>
+        <v>2199.35574663524</v>
       </c>
       <c r="E86">
-        <v>2324.724</v>
+        <v>2367.16</v>
       </c>
       <c r="F86">
-        <v>3564.624</v>
+        <v>3607.06</v>
       </c>
       <c r="G86">
         <v>510.9</v>
@@ -8333,37 +8333,37 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M86">
-        <v>523.2868032000001</v>
+        <v>529.5164080000001</v>
       </c>
       <c r="N86">
-        <v>-51.62013653333344</v>
+        <v>-57.84974133333338</v>
       </c>
       <c r="O86">
-        <v>-12.87406205141336</v>
+        <v>-14.42772548853335</v>
       </c>
       <c r="P86">
-        <v>-38.74607448192008</v>
+        <v>-43.42201584480004</v>
       </c>
       <c r="Q86">
-        <v>123.2539255180799</v>
+        <v>118.5779841551999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2223444104153551</v>
+        <v>0.2341140377763788</v>
       </c>
       <c r="T86">
-        <v>4.077238115828062</v>
+        <v>4.3490539902166</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2247976940127556</v>
+        <v>0.2221530152596644</v>
       </c>
       <c r="W86">
-        <v>0.1137996985189275</v>
+        <v>0.1141879373598813</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9013540257127328</v>
+        <v>0.8907498607043478</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1321768524223559</v>
+        <v>0.1331868524223559</v>
       </c>
       <c r="C87">
-        <v>-896.8042533647599</v>
+        <v>-955.6048790069844</v>
       </c>
       <c r="D87">
-        <v>2199.35574663524</v>
+        <v>2182.991120993016</v>
       </c>
       <c r="E87">
-        <v>2367.16</v>
+        <v>2409.596</v>
       </c>
       <c r="F87">
-        <v>3607.06</v>
+        <v>3649.496</v>
       </c>
       <c r="G87">
         <v>510.9</v>
@@ -8415,37 +8415,37 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M87">
-        <v>529.5164080000001</v>
+        <v>535.7460128</v>
       </c>
       <c r="N87">
-        <v>-57.84974133333338</v>
+        <v>-64.07934613333333</v>
       </c>
       <c r="O87">
-        <v>-14.42772548853335</v>
+        <v>-15.98138892565333</v>
       </c>
       <c r="P87">
-        <v>-43.42201584480004</v>
+        <v>-48.09795720768</v>
       </c>
       <c r="Q87">
-        <v>118.5779841551999</v>
+        <v>113.9020427923199</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2341140377763788</v>
+        <v>0.2475650404746916</v>
       </c>
       <c r="T87">
-        <v>4.3490539902166</v>
+        <v>4.6597007038035</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2221530152596644</v>
+        <v>0.2195698406636218</v>
       </c>
       <c r="W87">
-        <v>0.1141879373598813</v>
+        <v>0.1145671473905803</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8907498607043478</v>
+        <v>0.88039230418453</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1331868524223559</v>
+        <v>0.1341968524223559</v>
       </c>
       <c r="C88">
-        <v>-955.6048790069844</v>
+        <v>-1014.163776518023</v>
       </c>
       <c r="D88">
-        <v>2182.991120993016</v>
+        <v>2166.868223481977</v>
       </c>
       <c r="E88">
-        <v>2409.596</v>
+        <v>2452.032</v>
       </c>
       <c r="F88">
-        <v>3649.496</v>
+        <v>3691.932</v>
       </c>
       <c r="G88">
         <v>510.9</v>
@@ -8497,37 +8497,37 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M88">
-        <v>535.7460128</v>
+        <v>541.9756176000001</v>
       </c>
       <c r="N88">
-        <v>-64.07934613333333</v>
+        <v>-70.30895093333339</v>
       </c>
       <c r="O88">
-        <v>-15.98138892565333</v>
+        <v>-17.53505236277335</v>
       </c>
       <c r="P88">
-        <v>-48.09795720768</v>
+        <v>-52.77389857056004</v>
       </c>
       <c r="Q88">
-        <v>113.9020427923199</v>
+        <v>109.2261014294399</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2475650404746916</v>
+        <v>0.263085428203514</v>
       </c>
       <c r="T88">
-        <v>4.6597007038035</v>
+        <v>5.018139219480693</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2195698406636218</v>
+        <v>0.2170460493916261</v>
       </c>
       <c r="W88">
-        <v>0.1145671473905803</v>
+        <v>0.1149376399493093</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.88039230418453</v>
+        <v>0.8702728524122939</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1341968524223559</v>
+        <v>0.1352068524223559</v>
       </c>
       <c r="C89">
-        <v>-1014.163776518023</v>
+        <v>-1072.486262617955</v>
       </c>
       <c r="D89">
-        <v>2166.868223481977</v>
+        <v>2150.981737382046</v>
       </c>
       <c r="E89">
-        <v>2452.032</v>
+        <v>2494.468</v>
       </c>
       <c r="F89">
-        <v>3691.932</v>
+        <v>3734.368</v>
       </c>
       <c r="G89">
         <v>510.9</v>
@@ -8579,37 +8579,37 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M89">
-        <v>541.9756176000001</v>
+        <v>548.2052224000001</v>
       </c>
       <c r="N89">
-        <v>-70.30895093333339</v>
+        <v>-76.53855573333345</v>
       </c>
       <c r="O89">
-        <v>-17.53505236277335</v>
+        <v>-19.08871579989336</v>
       </c>
       <c r="P89">
-        <v>-52.77389857056004</v>
+        <v>-57.44983993344009</v>
       </c>
       <c r="Q89">
-        <v>109.2261014294399</v>
+        <v>104.5501600665599</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.263085428203514</v>
+        <v>0.2811925472204735</v>
       </c>
       <c r="T89">
-        <v>5.018139219480693</v>
+        <v>5.436317487770752</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2170460493916261</v>
+        <v>0.2145796170121758</v>
       </c>
       <c r="W89">
-        <v>0.1149376399493093</v>
+        <v>0.1152997122226126</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8702728524122939</v>
+        <v>0.8603833881803359</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1352068524223559</v>
+        <v>0.1362168524223559</v>
       </c>
       <c r="C90">
-        <v>-1072.486262617955</v>
+        <v>-1130.577499242628</v>
       </c>
       <c r="D90">
-        <v>2150.981737382046</v>
+        <v>2135.326500757373</v>
       </c>
       <c r="E90">
-        <v>2494.468</v>
+        <v>2536.904</v>
       </c>
       <c r="F90">
-        <v>3734.368</v>
+        <v>3776.804000000001</v>
       </c>
       <c r="G90">
         <v>510.9</v>
@@ -8661,37 +8661,37 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M90">
-        <v>548.2052224000001</v>
+        <v>554.4348272000001</v>
       </c>
       <c r="N90">
-        <v>-76.53855573333345</v>
+        <v>-82.7681605333334</v>
       </c>
       <c r="O90">
-        <v>-19.08871579989336</v>
+        <v>-20.64237923701335</v>
       </c>
       <c r="P90">
-        <v>-57.44983993344009</v>
+        <v>-62.12578129632005</v>
       </c>
       <c r="Q90">
-        <v>104.5501600665599</v>
+        <v>99.8742187036799</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2811925472204735</v>
+        <v>0.302591869695062</v>
       </c>
       <c r="T90">
-        <v>5.436317487770752</v>
+        <v>5.930528168477182</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2145796170121758</v>
+        <v>0.2121686100794547</v>
       </c>
       <c r="W90">
-        <v>0.1152997122226126</v>
+        <v>0.1156536480403361</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8603833881803359</v>
+        <v>0.850716159099658</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1362168524223559</v>
+        <v>0.1372268524223559</v>
       </c>
       <c r="C91">
-        <v>-1130.577499242628</v>
+        <v>-1188.442499135707</v>
       </c>
       <c r="D91">
-        <v>2135.326500757373</v>
+        <v>2119.897500864293</v>
       </c>
       <c r="E91">
-        <v>2536.904</v>
+        <v>2579.34</v>
       </c>
       <c r="F91">
-        <v>3776.804000000001</v>
+        <v>3819.24</v>
       </c>
       <c r="G91">
         <v>510.9</v>
@@ -8743,37 +8743,37 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M91">
-        <v>554.4348272000001</v>
+        <v>560.664432</v>
       </c>
       <c r="N91">
-        <v>-82.7681605333334</v>
+        <v>-88.99776533333335</v>
       </c>
       <c r="O91">
-        <v>-20.64237923701335</v>
+        <v>-22.19604267413334</v>
       </c>
       <c r="P91">
-        <v>-62.12578129632005</v>
+        <v>-66.80172265920001</v>
       </c>
       <c r="Q91">
-        <v>99.8742187036799</v>
+        <v>95.19827734079993</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.302591869695062</v>
+        <v>0.3282710566645682</v>
       </c>
       <c r="T91">
-        <v>5.930528168477182</v>
+        <v>6.523580985324902</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2121686100794547</v>
+        <v>0.2098111810785719</v>
       </c>
       <c r="W91">
-        <v>0.1156536480403361</v>
+        <v>0.1159997186176657</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.850716159099658</v>
+        <v>0.8412637573318842</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1372268524223559</v>
+        <v>0.1382368524223559</v>
       </c>
       <c r="C92">
-        <v>-1188.442499135707</v>
+        <v>-1246.086131200013</v>
       </c>
       <c r="D92">
-        <v>2119.897500864293</v>
+        <v>2104.689868799987</v>
       </c>
       <c r="E92">
-        <v>2579.34</v>
+        <v>2621.776</v>
       </c>
       <c r="F92">
-        <v>3819.24</v>
+        <v>3861.676</v>
       </c>
       <c r="G92">
         <v>510.9</v>
@@ -8825,37 +8825,37 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M92">
-        <v>560.664432</v>
+        <v>566.8940368000001</v>
       </c>
       <c r="N92">
-        <v>-88.99776533333335</v>
+        <v>-95.22737013333341</v>
       </c>
       <c r="O92">
-        <v>-22.19604267413334</v>
+        <v>-23.74970611125335</v>
       </c>
       <c r="P92">
-        <v>-66.80172265920001</v>
+        <v>-71.47766402208006</v>
       </c>
       <c r="Q92">
-        <v>95.19827734079993</v>
+        <v>90.52233597791988</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3282710566645682</v>
+        <v>0.359656729627298</v>
       </c>
       <c r="T92">
-        <v>6.523580985324902</v>
+        <v>7.248423317027668</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2098111810785719</v>
+        <v>0.2075055637040821</v>
       </c>
       <c r="W92">
-        <v>0.1159997186176657</v>
+        <v>0.1163381832482408</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8412637573318842</v>
+        <v>0.8320191006579073</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1382368524223559</v>
+        <v>0.1392468524223559</v>
       </c>
       <c r="C93">
-        <v>-1246.086131200013</v>
+        <v>-1303.513125620172</v>
       </c>
       <c r="D93">
-        <v>2104.689868799987</v>
+        <v>2089.698874379829</v>
       </c>
       <c r="E93">
-        <v>2621.776</v>
+        <v>2664.212</v>
       </c>
       <c r="F93">
-        <v>3861.676</v>
+        <v>3904.112000000001</v>
       </c>
       <c r="G93">
         <v>510.9</v>
@@ -8907,37 +8907,37 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M93">
-        <v>566.8940368000001</v>
+        <v>573.1236416000002</v>
       </c>
       <c r="N93">
-        <v>-95.22737013333341</v>
+        <v>-101.4569749333335</v>
       </c>
       <c r="O93">
-        <v>-23.74970611125335</v>
+        <v>-25.30336954837337</v>
       </c>
       <c r="P93">
-        <v>-71.47766402208006</v>
+        <v>-76.1536053849601</v>
       </c>
       <c r="Q93">
-        <v>90.52233597791988</v>
+        <v>85.84639461503984</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.359656729627298</v>
+        <v>0.3988888208307105</v>
       </c>
       <c r="T93">
-        <v>7.248423317027668</v>
+        <v>8.154476231656131</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2075055637040821</v>
+        <v>0.205250068446429</v>
       </c>
       <c r="W93">
-        <v>0.1163381832482408</v>
+        <v>0.1166692899520642</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8320191006579073</v>
+        <v>0.8229754147811909</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1392468524223559</v>
+        <v>0.1402568524223559</v>
       </c>
       <c r="C94">
-        <v>-1303.513125620172</v>
+        <v>-1360.728078767887</v>
       </c>
       <c r="D94">
-        <v>2089.698874379829</v>
+        <v>2074.919921232114</v>
       </c>
       <c r="E94">
-        <v>2664.212</v>
+        <v>2706.648000000001</v>
       </c>
       <c r="F94">
-        <v>3904.112000000001</v>
+        <v>3946.548000000001</v>
       </c>
       <c r="G94">
         <v>510.9</v>
@@ -8989,37 +8989,37 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M94">
-        <v>573.1236416000002</v>
+        <v>579.3532464000001</v>
       </c>
       <c r="N94">
-        <v>-101.4569749333335</v>
+        <v>-107.6865797333334</v>
       </c>
       <c r="O94">
-        <v>-25.30336954837337</v>
+        <v>-26.85703298549335</v>
       </c>
       <c r="P94">
-        <v>-76.1536053849601</v>
+        <v>-80.82954674784006</v>
       </c>
       <c r="Q94">
-        <v>85.84639461503984</v>
+        <v>81.17045325215989</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3988888208307105</v>
+        <v>0.4493300809493834</v>
       </c>
       <c r="T94">
-        <v>8.154476231656131</v>
+        <v>9.319401407607007</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.205250068446429</v>
+        <v>0.2030430784631341</v>
       </c>
       <c r="W94">
-        <v>0.1166692899520642</v>
+        <v>0.1169932760816119</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8229754147811909</v>
+        <v>0.814126216772791</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1402568524223559</v>
+        <v>0.1412668524223559</v>
       </c>
       <c r="C95">
-        <v>-1360.728078767887</v>
+        <v>-1417.735457900532</v>
       </c>
       <c r="D95">
-        <v>2074.919921232114</v>
+        <v>2060.348542099468</v>
       </c>
       <c r="E95">
-        <v>2706.648000000001</v>
+        <v>2749.084</v>
       </c>
       <c r="F95">
-        <v>3946.548000000001</v>
+        <v>3988.984</v>
       </c>
       <c r="G95">
         <v>510.9</v>
@@ -9071,37 +9071,37 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M95">
-        <v>579.3532464000001</v>
+        <v>585.5828512000002</v>
       </c>
       <c r="N95">
-        <v>-107.6865797333334</v>
+        <v>-113.9161845333335</v>
       </c>
       <c r="O95">
-        <v>-26.85703298549335</v>
+        <v>-28.41069642261337</v>
       </c>
       <c r="P95">
-        <v>-80.82954674784006</v>
+        <v>-85.50548811072011</v>
       </c>
       <c r="Q95">
-        <v>81.17045325215989</v>
+        <v>76.49451188927983</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4493300809493834</v>
+        <v>0.5165850944409474</v>
       </c>
       <c r="T95">
-        <v>9.319401407607007</v>
+        <v>10.87263497554151</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2030430784631341</v>
+        <v>0.2008830457135262</v>
       </c>
       <c r="W95">
-        <v>0.1169932760816119</v>
+        <v>0.1173103688892544</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.814126216772791</v>
+        <v>0.8054652995730804</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1412668524223559</v>
+        <v>0.1953451823498905</v>
       </c>
       <c r="C96">
-        <v>-1417.735457900532</v>
+        <v>-2023.186272285853</v>
       </c>
       <c r="D96">
-        <v>2060.348542099468</v>
+        <v>1497.333727714147</v>
       </c>
       <c r="E96">
-        <v>2749.084</v>
+        <v>2791.52</v>
       </c>
       <c r="F96">
-        <v>3988.984</v>
+        <v>4031.420000000001</v>
       </c>
       <c r="G96">
         <v>510.9</v>
@@ -9153,45 +9153,45 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M96">
-        <v>585.5828512000002</v>
+        <v>809.5091360000001</v>
       </c>
       <c r="N96">
-        <v>-113.9161845333335</v>
+        <v>-337.8424693333334</v>
       </c>
       <c r="O96">
-        <v>-28.41069642261337</v>
+        <v>-84.25791185173337</v>
       </c>
       <c r="P96">
-        <v>-85.50548811072011</v>
+        <v>-253.5845574816001</v>
       </c>
       <c r="Q96">
-        <v>76.49451188927983</v>
+        <v>-91.58455748160014</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5165850944409474</v>
+        <v>0.6461087118798294</v>
       </c>
       <c r="T96">
-        <v>10.87263497554151</v>
+        <v>13.8639425376404</v>
       </c>
       <c r="U96">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.2008830457135262</v>
+        <v>0.1453148104639386</v>
       </c>
       <c r="W96">
-        <v>0.1173103688892544</v>
+        <v>0.1716207860588412</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.8054652995730804</v>
+        <v>0.5826576201441001</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1953451823498905</v>
+        <v>0.1968951823498905</v>
       </c>
       <c r="C97">
-        <v>-2023.186272285853</v>
+        <v>-2077.258652489939</v>
       </c>
       <c r="D97">
-        <v>1497.333727714147</v>
+        <v>1485.697347510062</v>
       </c>
       <c r="E97">
-        <v>2791.52</v>
+        <v>2833.956000000001</v>
       </c>
       <c r="F97">
-        <v>4031.420000000001</v>
+        <v>4073.856000000001</v>
       </c>
       <c r="G97">
         <v>510.9</v>
@@ -9235,37 +9235,37 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M97">
-        <v>809.5091360000001</v>
+        <v>818.0302848000001</v>
       </c>
       <c r="N97">
-        <v>-337.8424693333334</v>
+        <v>-346.3636181333334</v>
       </c>
       <c r="O97">
-        <v>-84.25791185173337</v>
+        <v>-86.38308636245335</v>
       </c>
       <c r="P97">
-        <v>-253.5845574816001</v>
+        <v>-259.9805317708801</v>
       </c>
       <c r="Q97">
-        <v>-91.58455748160014</v>
+        <v>-97.98053177088013</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6461087118798294</v>
+        <v>0.7961858898497872</v>
       </c>
       <c r="T97">
-        <v>13.8639425376404</v>
+        <v>17.32992817205051</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1453148104639386</v>
+        <v>0.1438011145216059</v>
       </c>
       <c r="W97">
-        <v>0.1716207860588412</v>
+        <v>0.1719247362040616</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5826576201441001</v>
+        <v>0.5765882699342657</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1968951823498905</v>
+        <v>0.1984451823498905</v>
       </c>
       <c r="C98">
-        <v>-2077.258652489938</v>
+        <v>-2131.151565461978</v>
       </c>
       <c r="D98">
-        <v>1485.697347510062</v>
+        <v>1474.240434538023</v>
       </c>
       <c r="E98">
-        <v>2833.956</v>
+        <v>2876.392</v>
       </c>
       <c r="F98">
-        <v>4073.856</v>
+        <v>4116.292</v>
       </c>
       <c r="G98">
         <v>510.9</v>
@@ -9317,37 +9317,37 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M98">
-        <v>818.0302848000001</v>
+        <v>826.5514336000001</v>
       </c>
       <c r="N98">
-        <v>-346.3636181333334</v>
+        <v>-354.8847669333334</v>
       </c>
       <c r="O98">
-        <v>-86.38308636245335</v>
+        <v>-88.50826087317336</v>
       </c>
       <c r="P98">
-        <v>-259.9805317708801</v>
+        <v>-266.3765060601601</v>
       </c>
       <c r="Q98">
-        <v>-97.98053177088013</v>
+        <v>-104.3765060601601</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7961858898497852</v>
+        <v>1.046314519799714</v>
       </c>
       <c r="T98">
-        <v>17.32992817205047</v>
+        <v>23.10657089606729</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1438011145216059</v>
+        <v>0.1423186288048883</v>
       </c>
       <c r="W98">
-        <v>0.1719247362040616</v>
+        <v>0.1722224193359784</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5765882699342657</v>
+        <v>0.5706440609658712</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1984451823498905</v>
+        <v>0.1999951823498905</v>
       </c>
       <c r="C99">
-        <v>-2131.151565461978</v>
+        <v>-2184.869131299372</v>
       </c>
       <c r="D99">
-        <v>1474.240434538023</v>
+        <v>1462.958868700628</v>
       </c>
       <c r="E99">
-        <v>2876.392</v>
+        <v>2918.828</v>
       </c>
       <c r="F99">
-        <v>4116.292</v>
+        <v>4158.728</v>
       </c>
       <c r="G99">
         <v>510.9</v>
@@ -9399,37 +9399,37 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M99">
-        <v>826.5514336000001</v>
+        <v>835.0725824</v>
       </c>
       <c r="N99">
-        <v>-354.8847669333334</v>
+        <v>-363.4059157333333</v>
       </c>
       <c r="O99">
-        <v>-88.50826087317336</v>
+        <v>-90.63343538389333</v>
       </c>
       <c r="P99">
-        <v>-266.3765060601601</v>
+        <v>-272.77248034944</v>
       </c>
       <c r="Q99">
-        <v>-104.3765060601601</v>
+        <v>-110.7724803494401</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.046314519799714</v>
+        <v>1.546571779699571</v>
       </c>
       <c r="T99">
-        <v>23.10657089606729</v>
+        <v>34.65985634410094</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1423186288048883</v>
+        <v>0.140866397898716</v>
       </c>
       <c r="W99">
-        <v>0.1722224193359784</v>
+        <v>0.1725140273019379</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5706440609658712</v>
+        <v>0.5648211623845869</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1999951823498905</v>
+        <v>0.2015451823498906</v>
       </c>
       <c r="C100">
-        <v>-2184.869131299372</v>
+        <v>-2238.415344941765</v>
       </c>
       <c r="D100">
-        <v>1462.958868700628</v>
+        <v>1451.848655058235</v>
       </c>
       <c r="E100">
-        <v>2918.828</v>
+        <v>2961.264000000001</v>
       </c>
       <c r="F100">
-        <v>4158.728</v>
+        <v>4201.164000000001</v>
       </c>
       <c r="G100">
         <v>510.9</v>
@@ -9481,37 +9481,37 @@
         <v>471.6666666666667</v>
       </c>
       <c r="M100">
-        <v>835.0725824</v>
+        <v>843.5937312000002</v>
       </c>
       <c r="N100">
-        <v>-363.4059157333333</v>
+        <v>-371.9270645333335</v>
       </c>
       <c r="O100">
-        <v>-90.63343538389333</v>
+        <v>-92.75860989461339</v>
       </c>
       <c r="P100">
-        <v>-272.77248034944</v>
+        <v>-279.1684546387202</v>
       </c>
       <c r="Q100">
-        <v>-110.7724803494401</v>
+        <v>-117.1684546387202</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.546571779699571</v>
+        <v>3.047343559399141</v>
       </c>
       <c r="T100">
-        <v>34.65985634410094</v>
+        <v>69.31971268820188</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.140866397898716</v>
+        <v>0.1394435049906481</v>
       </c>
       <c r="W100">
-        <v>0.1725140273019379</v>
+        <v>0.1727997441978779</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5648211623845869</v>
+        <v>0.5591158981180757</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2015451823498906</v>
-      </c>
-      <c r="C101">
-        <v>-2238.415344941765</v>
-      </c>
-      <c r="D101">
-        <v>1451.848655058235</v>
-      </c>
-      <c r="E101">
-        <v>2961.264000000001</v>
-      </c>
-      <c r="F101">
-        <v>4201.164000000001</v>
-      </c>
-      <c r="G101">
-        <v>510.9</v>
-      </c>
-      <c r="H101">
-        <v>3003.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>633.6666666666666</v>
-      </c>
-      <c r="K101">
-        <v>161.9999999999999</v>
-      </c>
-      <c r="L101">
-        <v>471.6666666666667</v>
-      </c>
-      <c r="M101">
-        <v>843.5937312000002</v>
-      </c>
-      <c r="N101">
-        <v>-371.9270645333335</v>
-      </c>
-      <c r="O101">
-        <v>-92.75860989461339</v>
-      </c>
-      <c r="P101">
-        <v>-279.1684546387202</v>
-      </c>
-      <c r="Q101">
-        <v>-117.1684546387202</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.047343559399141</v>
-      </c>
-      <c r="T101">
-        <v>69.31971268820188</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1394435049906481</v>
-      </c>
-      <c r="W101">
-        <v>0.1727997441978779</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5591158981180757</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
